--- a/output/AGA_Dark_Targets.xlsx
+++ b/output/AGA_Dark_Targets.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1149"/>
+  <dimension ref="A1:F1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>paper_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>relevance_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pathway_diversity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>frequency_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>novelty_index</t>
         </is>
@@ -5215,20 +5203,20 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SLC7A1</t>
+          <t>Androgen production</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C218" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E218" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F218" t="n">
         <v>2.5</v>
@@ -5237,7 +5225,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ARG2</t>
+          <t>SLC7A1</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5259,7 +5247,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5-Alpha-Reductase</t>
+          <t>ARG2</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5281,7 +5269,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Wnt/Beta-catenin signaling pathway</t>
+          <t>5-Alpha-Reductase</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5303,7 +5291,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SFRP1 (Secreted Frizzled-Related Protein 1)</t>
+          <t>Wnt/Beta-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5325,7 +5313,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FZD1 (Frizzled Family Receptor 1)</t>
+          <t>SFRP1 (Secreted Frizzled-Related Protein 1)</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5347,7 +5335,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TGFB1</t>
+          <t>FZD1 (Frizzled Family Receptor 1)</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5369,7 +5357,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CTNNBIP1</t>
+          <t>TGFB1</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5391,7 +5379,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VEGFA</t>
+          <t>CTNNBIP1</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5413,7 +5401,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>IL-7 receptor (IL-7R)</t>
+          <t>VEGFA</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5435,7 +5423,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STAT5</t>
+          <t>IL-7 receptor (IL-7R)</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5457,7 +5445,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>IL-8</t>
+          <t>STAT5</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5479,20 +5467,20 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Hair follicle development and growth</t>
+          <t>IL-8</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>3.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="D230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F230" t="n">
         <v>2.5</v>
@@ -5501,20 +5489,20 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Androgen Receptor Degradation (ARD)</t>
+          <t>Hair follicle development and growth</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C231" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E231" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F231" t="n">
         <v>2.5</v>
@@ -5523,7 +5511,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Hair restoration</t>
+          <t>Androgen Receptor Degradation (ARD)</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5545,7 +5533,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Hair strengthening</t>
+          <t>Hair restoration</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5567,7 +5555,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AR protein degradation</t>
+          <t>Hair strengthening</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5589,7 +5577,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ACKR3</t>
+          <t>AR protein degradation</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5611,7 +5599,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CDK4</t>
+          <t>ACKR3</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5633,7 +5621,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CDK6</t>
+          <t>CDK4</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5655,7 +5643,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5-alpha reductase (SRD5A1)</t>
+          <t>CDK6</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5677,7 +5665,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>miRNA-29a-3p</t>
+          <t>5-alpha reductase (SRD5A1)</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5699,7 +5687,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>AR signaling</t>
+          <t>miRNA-29a-3p</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5721,7 +5709,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5-Reductase (implied through DHT reduction)</t>
+          <t>AR signaling</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5743,7 +5731,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>IGF-1 pathway</t>
+          <t>5-Reductase (implied through DHT reduction)</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5765,7 +5753,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>15-PGDH (15-hydroxyprostaglandin dehydrogenase)</t>
+          <t>IGF-1 pathway</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5787,7 +5775,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>COX-1 (Cyclooxygenase-1)</t>
+          <t>15-PGDH (15-hydroxyprostaglandin dehydrogenase)</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -5809,7 +5797,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MRP4 (Multidrug resistance-associated protein 4)</t>
+          <t>COX-1 (Cyclooxygenase-1)</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -5831,7 +5819,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PGT (Prostaglandin transporter)</t>
+          <t>MRP4 (Multidrug resistance-associated protein 4)</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -5853,7 +5841,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Akt/ERK signaling proteins</t>
+          <t>PGT (Prostaglandin transporter)</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -5875,7 +5863,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>miR-3139</t>
+          <t>Akt/ERK signaling proteins</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -5897,7 +5885,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>miR-3189</t>
+          <t>miR-3139</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -5919,7 +5907,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>miR-3199</t>
+          <t>miR-3189</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -5941,7 +5929,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>miR-8485</t>
+          <t>miR-3199</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -5963,7 +5951,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MITF</t>
+          <t>miR-8485</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -5985,7 +5973,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TYR</t>
+          <t>MITF</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6007,7 +5995,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TYRP1</t>
+          <t>TYR</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6029,7 +6017,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TYRP2</t>
+          <t>TYRP1</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6051,7 +6039,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Noggin (BMP antagonist)</t>
+          <t>TYRP2</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6073,7 +6061,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Telomerase reverse transcriptase (TERT)</t>
+          <t>Noggin (BMP antagonist)</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6095,7 +6083,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Janus Kinase 1 (JAK1)</t>
+          <t>Telomerase reverse transcriptase (TERT)</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6117,7 +6105,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Sonic Hedgehog (Shh) signaling pathway</t>
+          <t>Janus Kinase 1 (JAK1)</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6139,7 +6127,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Nrf2 pathway</t>
+          <t>Sonic Hedgehog (Shh) signaling pathway</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6161,7 +6149,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FGF-7</t>
+          <t>Nrf2 pathway</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6183,7 +6171,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Interleukin-1beta</t>
+          <t>FGF-7</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6205,7 +6193,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Prostate-Specific Antigen (PSA)</t>
+          <t>Interleukin-1beta</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6227,7 +6215,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Prostate-specific antigen (PSA)</t>
+          <t>Prostate-Specific Antigen (PSA)</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6249,7 +6237,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Steroid receptor coactivator-1 (SRC-1)</t>
+          <t>Prostate-specific antigen (PSA)</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6271,7 +6259,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5α-reductase Type 2 (5AR2)</t>
+          <t>Steroid receptor coactivator-1 (SRC-1)</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6293,7 +6281,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PCNA (Proliferating Cell Nuclear Antigen)</t>
+          <t>5α-reductase Type 2 (5AR2)</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6315,7 +6303,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Estrogen Receptors (ER)</t>
+          <t>PCNA (Proliferating Cell Nuclear Antigen)</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6337,7 +6325,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2 (5AR2)</t>
+          <t>Estrogen Receptors (ER)</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6359,7 +6347,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HIF-1</t>
+          <t>5-Alpha Reductase Type 2 (5AR2)</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6381,7 +6369,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Hair growth-related genes (Shh</t>
+          <t>HIF-1</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6403,7 +6391,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Prom1</t>
+          <t>Hair growth-related genes (Shh</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6425,7 +6413,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S100a9</t>
+          <t>Prom1</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6447,7 +6435,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Ptgfr)</t>
+          <t>S100a9</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6469,7 +6457,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>mTOR signaling</t>
+          <t>Ptgfr)</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6491,20 +6479,20 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Lipid metabolism</t>
+          <t>mTOR signaling</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>3.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F276" t="n">
         <v>2.5</v>
@@ -6513,20 +6501,20 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5-alpha Reductase (5α-reductase)</t>
+          <t>Lipid metabolism</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C277" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E277" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F277" t="n">
         <v>2.5</v>
@@ -6535,7 +6523,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Prostaglandin D2 receptor (DP2 receptor)</t>
+          <t>5-alpha Reductase (5α-reductase)</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6557,7 +6545,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>AC010789.1</t>
+          <t>Prostaglandin D2 receptor (DP2 receptor)</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6579,7 +6567,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>miR-21-5p</t>
+          <t>AC010789.1</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6601,7 +6589,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>BMP receptor</t>
+          <t>miR-21-5p</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6623,7 +6611,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>miR-324-3p</t>
+          <t>BMP receptor</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6645,7 +6633,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MAPK signaling</t>
+          <t>miR-324-3p</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6667,7 +6655,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ALK5</t>
+          <t>MAPK signaling</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6689,7 +6677,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BMP2</t>
+          <t>ALK5</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6711,7 +6699,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ephrin A3</t>
+          <t>BMP2</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6733,7 +6721,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Neurotrophin-4</t>
+          <t>Ephrin A3</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -6755,7 +6743,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5-alpha reductase Type 1</t>
+          <t>Neurotrophin-4</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -6777,7 +6765,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Growth factors (TGF</t>
+          <t>5-alpha reductase Type 1</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -6799,7 +6787,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CTGF)</t>
+          <t>Growth factors (TGF</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -6821,7 +6809,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5-alpha reductase Type I</t>
+          <t>CTGF)</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -6843,7 +6831,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Collagen XVII (COL17)</t>
+          <t>5-alpha reductase Type I</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -6865,7 +6853,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Thyroid hormone receptor beta (TRβ)</t>
+          <t>Collagen XVII (COL17)</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -6887,7 +6875,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Thyroid hormone receptor (TR)</t>
+          <t>Thyroid hormone receptor beta (TRβ)</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -6909,7 +6897,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5-alpha Reductase Type I</t>
+          <t>Thyroid hormone receptor (TR)</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -6931,7 +6919,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5-alpha Reductase Type II</t>
+          <t>5-alpha Reductase Type I</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -6953,7 +6941,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5-alpha Reductase Type III</t>
+          <t>5-alpha Reductase Type II</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -6975,7 +6963,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>T cells (IL-2 signaling)</t>
+          <t>5-alpha Reductase Type III</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -6997,7 +6985,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>PI3K-Akt pathway</t>
+          <t>T cells (IL-2 signaling)</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7019,7 +7007,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MAPK pathway</t>
+          <t>PI3K-Akt pathway</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7041,7 +7029,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Oxidative stress mediators</t>
+          <t>MAPK pathway</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7063,7 +7051,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Inflammatory cytokines (IL-1α</t>
+          <t>Oxidative stress mediators</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7085,7 +7073,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>TGF-β1)</t>
+          <t>Inflammatory cytokines (IL-1α</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7107,7 +7095,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ARA70/ELE1 (AR coactivator)</t>
+          <t>TGF-β1)</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7129,7 +7117,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Glucocorticoid receptor</t>
+          <t>ARA70/ELE1 (AR coactivator)</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7151,7 +7139,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Streptococcus bacterial culture</t>
+          <t>Glucocorticoid receptor</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7173,7 +7161,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>c-MET</t>
+          <t>Streptococcus bacterial culture</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7195,7 +7183,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>LEF1</t>
+          <t>c-MET</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7217,7 +7205,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TEC kinases</t>
+          <t>LEF1</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7239,7 +7227,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>gamma common chain cytokine signaling</t>
+          <t>TEC kinases</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7261,7 +7249,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>GSK-3β (Glycogen synthase kinase-3β)</t>
+          <t>gamma common chain cytokine signaling</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7283,7 +7271,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Zyxin (ZYX)</t>
+          <t>GSK-3β (Glycogen synthase kinase-3β)</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7305,7 +7293,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Focal adhesion proteins</t>
+          <t>Zyxin (ZYX)</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7327,20 +7315,20 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>NLRP3 inflammasome</t>
+          <t>Focal adhesion proteins</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>3.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="D314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E314" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F314" t="n">
         <v>2.5</v>
@@ -7349,7 +7337,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>NF-κB</t>
+          <t>NLRP3 inflammasome</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7371,7 +7359,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Gut microbiota</t>
+          <t>NF-κB</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7393,20 +7381,20 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>miR-214-5p</t>
+          <t>Gut microbiota</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C317" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E317" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F317" t="n">
         <v>2.5</v>
@@ -7415,7 +7403,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Androgen sensitivity biomarkers</t>
+          <t>miR-214-5p</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7437,7 +7425,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Gene expression profile markers</t>
+          <t>Androgen sensitivity biomarkers</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7459,7 +7447,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5-alpha reductase type 1</t>
+          <t>Gene expression profile markers</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7481,7 +7469,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>DHT-AR complex formation</t>
+          <t>5-alpha reductase type 1</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7503,7 +7491,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>AR nuclear translocation</t>
+          <t>DHT-AR complex formation</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7525,7 +7513,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Glycogen synthase kinase-3β (GSK-3β)</t>
+          <t>AR nuclear translocation</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7547,7 +7535,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Cell division cycle protein 42 (CDC42)</t>
+          <t>Glycogen synthase kinase-3β (GSK-3β)</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7569,7 +7557,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5-alpha reductase (5α-Reductase Type 2)</t>
+          <t>Cell division cycle protein 42 (CDC42)</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7591,7 +7579,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5α-환원효소</t>
+          <t>5-alpha reductase (5α-Reductase Type 2)</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7613,7 +7601,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Thyroid Hormone Receptor (TR)</t>
+          <t>5α-환원효소</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7635,7 +7623,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>TRβ1</t>
+          <t>Thyroid Hormone Receptor (TR)</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7657,7 +7645,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Autophagy</t>
+          <t>TRβ1</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7679,7 +7667,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>17β-Hydroxysteroid Dehydrogenase Type 1</t>
+          <t>Autophagy</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7701,7 +7689,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>17β-Hydroxysteroid Dehydrogenase Type 2</t>
+          <t>17β-Hydroxysteroid Dehydrogenase Type 1</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -7723,7 +7711,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>17β-Hydroxysteroid Dehydrogenase Type 3</t>
+          <t>17β-Hydroxysteroid Dehydrogenase Type 2</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -7745,7 +7733,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Estrogen Receptor α</t>
+          <t>17β-Hydroxysteroid Dehydrogenase Type 3</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -7767,7 +7755,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Estrogen Receptor β</t>
+          <t>Estrogen Receptor α</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -7789,7 +7777,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5-alpha reductase type 2 (SRD5A2)</t>
+          <t>Estrogen Receptor β</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -7811,7 +7799,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5-α reductase</t>
+          <t>5-alpha reductase type 2 (SRD5A2)</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -7833,7 +7821,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Inflammatory factors</t>
+          <t>5-α reductase</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -7855,7 +7843,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Follicle stem cell differentiation</t>
+          <t>Inflammatory factors</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -7877,7 +7865,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BMP-2</t>
+          <t>Follicle stem cell differentiation</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -7899,7 +7887,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BMP-4</t>
+          <t>BMP-2</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -7921,7 +7909,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>BMP-7</t>
+          <t>BMP-4</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -7943,7 +7931,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Noggin</t>
+          <t>BMP-7</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -7965,7 +7953,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5α-DHT (5-alpha-dihydrotestosterone)</t>
+          <t>Noggin</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -7987,7 +7975,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5-Alpha-Reductase Type 1</t>
+          <t>5α-DHT (5-alpha-dihydrotestosterone)</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8009,7 +7997,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>HIF-1alpha signaling pathway</t>
+          <t>5-Alpha-Reductase Type 1</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8031,7 +8019,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Hypoxia-mimetic effect</t>
+          <t>HIF-1alpha signaling pathway</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8053,7 +8041,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5α-Reductase (implied through DHT pathway)</t>
+          <t>Hypoxia-mimetic effect</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8075,7 +8063,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>PDGF (Platelet-Derived Growth Factor)</t>
+          <t>5α-Reductase (implied through DHT pathway)</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8097,7 +8085,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BMP2 (Bone Morphogenetic Protein 2)</t>
+          <t>PDGF (Platelet-Derived Growth Factor)</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8119,7 +8107,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>NOX (NADPH Oxidase)</t>
+          <t>BMP2 (Bone Morphogenetic Protein 2)</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8141,7 +8129,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>GPRC6A receptor</t>
+          <t>NOX (NADPH Oxidase)</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8163,7 +8151,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>PI3K signaling pathway</t>
+          <t>GPRC6A receptor</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8185,7 +8173,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Hair follicle dermal papilla cells (HFDPC)</t>
+          <t>PI3K signaling pathway</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8207,7 +8195,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Hair outer root sheath cells (HORSC)</t>
+          <t>Hair follicle dermal papilla cells (HFDPC)</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8229,7 +8217,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Hair matrix cells (HGMC)</t>
+          <t>Hair outer root sheath cells (HORSC)</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8251,7 +8239,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Akt/ERK signaling</t>
+          <t>Hair matrix cells (HGMC)</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8273,7 +8261,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5-Lipoxygenase (5-LO)</t>
+          <t>Akt/ERK signaling</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8295,7 +8283,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5-Lipoxygenase</t>
+          <t>5-Lipoxygenase (5-LO)</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8317,7 +8305,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Histamine</t>
+          <t>5-Lipoxygenase</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8339,7 +8327,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>SHH (Sonic Hedgehog)</t>
+          <t>Histamine</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8361,7 +8349,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>GLI1 (Glioma-associated hemolog1)</t>
+          <t>SHH (Sonic Hedgehog)</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8383,7 +8371,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>BMP4 (Bone morphogenetic protein 4)</t>
+          <t>GLI1 (Glioma-associated hemolog1)</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8405,7 +8393,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Smad1/5</t>
+          <t>BMP4 (Bone morphogenetic protein 4)</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8427,7 +8415,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>PI3K-AKT pathway</t>
+          <t>Smad1/5</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8449,7 +8437,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Wnt-β-catenin pathway</t>
+          <t>PI3K-AKT pathway</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8471,7 +8459,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Follicular keratinocytes</t>
+          <t>Wnt-β-catenin pathway</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8493,7 +8481,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Fibroblast Growth Factor-7 (FGF-7)</t>
+          <t>Follicular keratinocytes</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8515,7 +8503,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Prostaglandin F2a receptor</t>
+          <t>Fibroblast Growth Factor-7 (FGF-7)</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8537,7 +8525,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Prostamide F2a receptor</t>
+          <t>Prostaglandin F2a receptor</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8559,7 +8547,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Prostaglandin D synthase (PTGDS)</t>
+          <t>Prostamide F2a receptor</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8581,7 +8569,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>GPR44 (G protein-coupled receptor 44)</t>
+          <t>Prostaglandin D synthase (PTGDS)</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8603,7 +8591,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>PGD2 pathway</t>
+          <t>GPR44 (G protein-coupled receptor 44)</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8625,7 +8613,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Steroid Receptor Coactivator (SRC-1)</t>
+          <t>PGD2 pathway</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8647,7 +8635,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PI3K/Akt signaling</t>
+          <t>Steroid Receptor Coactivator (SRC-1)</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -8669,7 +8657,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>MAPK-ERK signaling pathway</t>
+          <t>PI3K/Akt signaling</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -8691,7 +8679,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Retinoic acid receptors (RARα</t>
+          <t>MAPK-ERK signaling pathway</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -8713,7 +8701,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>RARβ</t>
+          <t>Retinoic acid receptors (RARα</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -8735,7 +8723,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>RARγ)</t>
+          <t>RARβ</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -8757,7 +8745,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Oxidative Stress</t>
+          <t>RARγ)</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -8779,7 +8767,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>AR N-terminal domain (NTD)</t>
+          <t>Oxidative Stress</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -8801,7 +8789,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>AR-splice variants (AR-SV)</t>
+          <t>AR N-terminal domain (NTD)</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -8823,7 +8811,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>AR-V7</t>
+          <t>AR-splice variants (AR-SV)</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -8845,7 +8833,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>AR full-length (AR-FL)</t>
+          <t>AR-V7</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -8867,7 +8855,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>TGF-β (Transforming Growth Factor Beta)</t>
+          <t>AR full-length (AR-FL)</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -8889,7 +8877,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>JAK-STAT pathway</t>
+          <t>TGF-β (Transforming Growth Factor Beta)</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -8911,7 +8899,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>NKG2D+ CD8+ T cells</t>
+          <t>JAK-STAT pathway</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -8933,7 +8921,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>IGF-1 Receptor (IGF-1R)</t>
+          <t>NKG2D+ CD8+ T cells</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -8955,7 +8943,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Prostaglandin F2α receptor</t>
+          <t>IGF-1 Receptor (IGF-1R)</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -8977,7 +8965,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Hair follicle growth pathway</t>
+          <t>Prostaglandin F2α receptor</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -8999,7 +8987,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Dermal papilla cells (DPCs)</t>
+          <t>Hair follicle growth pathway</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9021,7 +9009,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Aldo-keto reductase 1C (Akr1c)</t>
+          <t>Dermal papilla cells (DPCs)</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9043,7 +9031,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Dehydrogenase/reductase 9 (Dhrs9)</t>
+          <t>Aldo-keto reductase 1C (Akr1c)</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -9065,7 +9053,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Nrf2/ARE pathway</t>
+          <t>Dehydrogenase/reductase 9 (Dhrs9)</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9087,7 +9075,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Aldo-Keto Reductase 1C2 (Akr1c2)</t>
+          <t>Nrf2/ARE pathway</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -9109,7 +9097,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Aldo-Keto Reductase 1C21 (Akr1c21)</t>
+          <t>Aldo-Keto Reductase 1C2 (Akr1c2)</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9131,7 +9119,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Dehydrogenase/reductase SDR family member 9 (Dhrs9)</t>
+          <t>Aldo-Keto Reductase 1C21 (Akr1c21)</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9153,7 +9141,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Inflammatory signaling (TNFα</t>
+          <t>Dehydrogenase/reductase SDR family member 9 (Dhrs9)</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9175,7 +9163,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>NFκB</t>
+          <t>Inflammatory signaling (TNFα</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9197,7 +9185,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>IL-1β)</t>
+          <t>NFκB</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9219,7 +9207,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5-alpha-Reductase Type 2</t>
+          <t>IL-1β)</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9241,7 +9229,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Retinoic Acid Receptors</t>
+          <t>5-alpha-Reductase Type 2</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -9263,7 +9251,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>miR-221</t>
+          <t>Retinoic Acid Receptors</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -9285,7 +9273,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>B7.1/B7.2 (CD80/CD86)</t>
+          <t>miR-221</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -9307,7 +9295,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CD44v10</t>
+          <t>B7.1/B7.2 (CD80/CD86)</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -9329,7 +9317,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>T-box21 (Tbx21)</t>
+          <t>CD44v10</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -9351,7 +9339,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>IFN-gamma</t>
+          <t>T-box21 (Tbx21)</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -9373,7 +9361,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>SRD5A2 (5α-Reductase Type II)</t>
+          <t>IFN-gamma</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -9395,7 +9383,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Adrenergic β2 receptor (ADRB2)</t>
+          <t>SRD5A2 (5α-Reductase Type II)</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -9417,7 +9405,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Gas6 (Growth arrest-specific protein 6)</t>
+          <t>Adrenergic β2 receptor (ADRB2)</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -9439,7 +9427,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>AXL receptor</t>
+          <t>Gas6 (Growth arrest-specific protein 6)</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -9461,7 +9449,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>TYRO3 receptor</t>
+          <t>AXL receptor</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -9483,7 +9471,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MER receptor</t>
+          <t>TYRO3 receptor</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -9505,7 +9493,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Plasminogen Activator Inhibitor-1 (PAI-1)</t>
+          <t>MER receptor</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -9527,7 +9515,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>PAI-1 (Plasminogen Activator Inhibitor-1)</t>
+          <t>Plasminogen Activator Inhibitor-1 (PAI-1)</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -9549,7 +9537,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha-reductase Type II)</t>
+          <t>PAI-1 (Plasminogen Activator Inhibitor-1)</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -9571,7 +9559,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Heat Shock Protein 27 (HSP27)</t>
+          <t>SRD5A2 (5-alpha-reductase Type II)</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -9593,7 +9581,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>miR-1</t>
+          <t>Heat Shock Protein 27 (HSP27)</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -9615,7 +9603,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MAPK signaling (p38 MAPK</t>
+          <t>miR-1</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -9637,7 +9625,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ERK1/2)</t>
+          <t>MAPK signaling (p38 MAPK</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -9659,7 +9647,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>SREBP-1</t>
+          <t>ERK1/2)</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -9681,7 +9669,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5α-reductase type 2</t>
+          <t>SREBP-1</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -9703,7 +9691,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ACC1</t>
+          <t>5α-reductase type 2</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -9725,7 +9713,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Prostaglandin D2 receptor</t>
+          <t>ACC1</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -9747,7 +9735,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Prostaglandin E2 receptor</t>
+          <t>Prostaglandin D2 receptor</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -9769,7 +9757,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>IGFBP-rP1</t>
+          <t>Prostaglandin E2 receptor</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -9791,7 +9779,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>IGF system</t>
+          <t>IGFBP-rP1</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -9813,7 +9801,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Androgen Receptor Dimerization</t>
+          <t>IGF system</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -9835,7 +9823,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TGF-β/Smad signaling</t>
+          <t>Androgen Receptor Dimerization</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -9857,7 +9845,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Sonic Hedgehog signaling</t>
+          <t>TGF-β/Smad signaling</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -9879,7 +9867,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>JAK (Janus Kinase)</t>
+          <t>Sonic Hedgehog signaling</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -9901,7 +9889,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>miR-29a</t>
+          <t>JAK (Janus Kinase)</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -9923,7 +9911,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SAHH</t>
+          <t>miR-29a</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -9945,7 +9933,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Type XVII collagen (COL17)</t>
+          <t>SAHH</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -9967,7 +9955,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>IGF-1 signaling pathway</t>
+          <t>Type XVII collagen (COL17)</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -9989,7 +9977,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>miR-22-3p</t>
+          <t>IGF-1 signaling pathway</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -10011,7 +9999,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CLIC4 (Chloride Intracellular Channel 4)</t>
+          <t>miR-22-3p</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -10033,7 +10021,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Sonic Hedgehog (SHH) pathway</t>
+          <t>CLIC4 (Chloride Intracellular Channel 4)</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -10055,7 +10043,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>SOD1</t>
+          <t>Sonic Hedgehog (SHH) pathway</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -10077,7 +10065,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>SOD1</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -10099,7 +10087,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>NT5E</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -10121,7 +10109,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SQLE</t>
+          <t>NT5E</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -10143,7 +10131,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>SQLE</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -10165,7 +10153,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -10187,7 +10175,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>LAMC1</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -10209,7 +10197,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>LAMC3</t>
+          <t>LAMC1</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -10231,7 +10219,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>PRLR</t>
+          <t>LAMC3</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -10253,7 +10241,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>BRAF</t>
+          <t>PRLR</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -10275,7 +10263,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Inflammatory signaling</t>
+          <t>BRAF</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -10297,7 +10285,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>HDAC1</t>
+          <t>Inflammatory signaling</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -10319,7 +10307,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>DHT-induced cytotoxicity</t>
+          <t>HDAC1</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -10341,7 +10329,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>PTGS2 (Prostaglandin-endoperoxide synthase 2)</t>
+          <t>DHT-induced cytotoxicity</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -10363,7 +10351,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>NFKBIZ</t>
+          <t>PTGS2 (Prostaglandin-endoperoxide synthase 2)</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -10385,7 +10373,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>mTORC2</t>
+          <t>NFKBIZ</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -10407,7 +10395,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>RICTOR</t>
+          <t>mTORC2</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -10429,7 +10417,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>DEPTOR</t>
+          <t>RICTOR</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -10451,7 +10439,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MMP9</t>
+          <t>DEPTOR</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -10473,7 +10461,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MMP3</t>
+          <t>MMP9</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -10495,7 +10483,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>MMP1</t>
+          <t>MMP3</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -10517,7 +10505,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>MMP1</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -10539,7 +10527,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CYP19A1 (Aromatase)</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -10561,7 +10549,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor (VEGF) signaling</t>
+          <t>CYP19A1 (Aromatase)</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -10583,7 +10571,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Mitochondrial activity</t>
+          <t>Vascular endothelial growth factor (VEGF) signaling</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -10605,7 +10593,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Transmembrane Protease Serine 2</t>
+          <t>Mitochondrial activity</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -10627,7 +10615,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>PIEZO1</t>
+          <t>Transmembrane Protease Serine 2</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -10649,7 +10637,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Myosin Light Chain Kinase (MLCK)</t>
+          <t>PIEZO1</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -10671,7 +10659,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Connective Tissue Sheath (CTS)</t>
+          <t>Myosin Light Chain Kinase (MLCK)</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -10693,7 +10681,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>DKK (Dickkopf)</t>
+          <t>Connective Tissue Sheath (CTS)</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -10715,7 +10703,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>sFRP (Secreted Frizzled-Related Protein)</t>
+          <t>DKK (Dickkopf)</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -10737,51 +10725,51 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CD8+ T cells</t>
+          <t>sFRP (Secreted Frizzled-Related Protein)</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C469" t="n">
-        <v>2.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="D469" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E469" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="F469" t="n">
-        <v>2.428571428571429</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Melanocortin-5 receptor (MC5R)</t>
+          <t>CD8+ T cells</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C470" t="n">
-        <v>3.5</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D470" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E470" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="F470" t="n">
-        <v>2.333333333333333</v>
+        <v>2.428571428571429</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Laminin-332</t>
+          <t>Melanocortin-5 receptor (MC5R)</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -10803,7 +10791,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Androgen production</t>
+          <t>Laminin-332</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -11001,29 +10989,29 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>21-hydroxylase</t>
+          <t>Estrogen receptor</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C481" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E481" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F481" t="n">
-        <v>2.25</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Insulin signaling</t>
+          <t>21-hydroxylase</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -11045,29 +11033,29 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Hair follicle mesenchymal stem cells (HF-MSCs)</t>
+          <t>Insulin signaling</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C483" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E483" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F483" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Dermal sheath cells</t>
+          <t>Hair follicle mesenchymal stem cells (HF-MSCs)</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -11089,7 +11077,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type I</t>
+          <t>Dermal sheath cells</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -11111,7 +11099,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Stress response system in scalp and hair follicles</t>
+          <t>5-Alpha Reductase Type I</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -11133,7 +11121,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Growth factors (VEGF</t>
+          <t>Stress response system in scalp and hair follicles</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -11155,7 +11143,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>PDGF)</t>
+          <t>Growth factors (VEGF</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -11177,7 +11165,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Anagen phase regulation</t>
+          <t>PDGF)</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -11199,7 +11187,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Apoptosis inhibition</t>
+          <t>Anagen phase regulation</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -11221,7 +11209,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Mitochondrial activation</t>
+          <t>Apoptosis inhibition</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -11243,7 +11231,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>TFAM (Mitochondrial transcription factor A)</t>
+          <t>Mitochondrial activation</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -11265,7 +11253,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ATP5A1 (ATP synthase F1 subunit alpha)</t>
+          <t>TFAM (Mitochondrial transcription factor A)</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -11287,7 +11275,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Fibrosis pathway</t>
+          <t>ATP5A1 (ATP synthase F1 subunit alpha)</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -11309,7 +11297,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Calcification pathway</t>
+          <t>Fibrosis pathway</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -11331,7 +11319,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>EDAR</t>
+          <t>Calcification pathway</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -11353,7 +11341,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Melanocyte</t>
+          <t>EDAR</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -11375,7 +11363,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Lama3 (Laminin alpha-3)</t>
+          <t>Melanocyte</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -11397,7 +11385,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Basement membrane signaling</t>
+          <t>Lama3 (Laminin alpha-3)</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -11419,7 +11407,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>5α-Reductase (DHT inhibition)</t>
+          <t>Basement membrane signaling</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -11441,7 +11429,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>CCHCR1</t>
+          <t>5α-Reductase (DHT inhibition)</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -11463,7 +11451,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Hair keratins</t>
+          <t>CCHCR1</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -11485,7 +11473,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Keratin-associated proteins (KRTAPs)</t>
+          <t>Hair keratins</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -11507,20 +11495,20 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Mast cells</t>
+          <t>Keratin-associated proteins (KRTAPs)</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C504" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E504" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F504" t="n">
         <v>2</v>
@@ -11529,20 +11517,20 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Polyamine metabolism</t>
+          <t>Mast cells</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C505" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E505" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F505" t="n">
         <v>2</v>
@@ -11551,7 +11539,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Ornithine decarboxylase</t>
+          <t>Polyamine metabolism</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -11573,7 +11561,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>hsa-miR-5193</t>
+          <t>Ornithine decarboxylase</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -11595,7 +11583,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>TP53</t>
+          <t>hsa-miR-5193</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -11617,7 +11605,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>LOXL1-AS1</t>
+          <t>TP53</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -11639,20 +11627,20 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Vascular smooth muscle cells</t>
+          <t>LOXL1-AS1</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C510" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D510" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E510" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F510" t="n">
         <v>2</v>
@@ -11661,20 +11649,20 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Hair Follicle Stem Cells</t>
+          <t>Vascular smooth muscle cells</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C511" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E511" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F511" t="n">
         <v>2</v>
@@ -11683,7 +11671,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Mesenchymal Stem Cells</t>
+          <t>Hair Follicle Stem Cells</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -11705,7 +11693,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Epithelial Stem Cells</t>
+          <t>Mesenchymal Stem Cells</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -11727,7 +11715,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>bFGF (Basic Fibroblast Growth Factor)</t>
+          <t>Epithelial Stem Cells</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -11749,7 +11737,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Fibroblast signaling</t>
+          <t>bFGF (Basic Fibroblast Growth Factor)</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -11771,7 +11759,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Tissue regeneration</t>
+          <t>Fibroblast signaling</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -11793,7 +11781,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>EGF (Epidermal Growth Factor)</t>
+          <t>Tissue regeneration</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -11815,7 +11803,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>FGF7 (Fibroblast Growth Factor 7)</t>
+          <t>EGF (Epidermal Growth Factor)</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -11837,7 +11825,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>ASS1 (Argininosuccinate synthase)</t>
+          <t>FGF7 (Fibroblast Growth Factor 7)</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -11859,7 +11847,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>PAICS (Phosphoribosyl aminoimidazole carboxylase)</t>
+          <t>ASS1 (Argininosuccinate synthase)</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -11881,7 +11869,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>CKAP4 (Cytoskeleton-associated protein 4)</t>
+          <t>PAICS (Phosphoribosyl aminoimidazole carboxylase)</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -11903,7 +11891,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>GSN (Gelsolin)</t>
+          <t>CKAP4 (Cytoskeleton-associated protein 4)</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -11925,7 +11913,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>IQGAP1 (Ras GTPase-activating-like protein 1)</t>
+          <t>GSN (Gelsolin)</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -11947,7 +11935,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SKP1 (S-phase kinase-associated protein 1)</t>
+          <t>IQGAP1 (Ras GTPase-activating-like protein 1)</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -11969,7 +11957,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>SPTAN1 (Spectrin alpha chain</t>
+          <t>SKP1 (S-phase kinase-associated protein 1)</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -11991,7 +11979,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>brain)</t>
+          <t>SPTAN1 (Spectrin alpha chain</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -12013,7 +12001,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>PLEC1 (Plectin-1)</t>
+          <t>brain)</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -12035,7 +12023,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Germinal matrix cells</t>
+          <t>PLEC1 (Plectin-1)</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -12057,7 +12045,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Dermal papilla cells (DPC)</t>
+          <t>Germinal matrix cells</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -12079,7 +12067,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Cell cycle regulators (Cyclin D1</t>
+          <t>Dermal papilla cells (DPC)</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -12101,7 +12089,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>C-Myc)</t>
+          <t>Cell cycle regulators (Cyclin D1</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -12123,7 +12111,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Hair growth factors (EGF</t>
+          <t>C-Myc)</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -12145,7 +12133,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Hair growth inhibitors (DKK-1</t>
+          <t>Hair growth factors (EGF</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -12167,7 +12155,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>TGF-α1)</t>
+          <t>Hair growth inhibitors (DKK-1</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -12189,20 +12177,20 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Hair loss prevention</t>
+          <t>TGF-α1)</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C535" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E535" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F535" t="n">
         <v>2</v>
@@ -12211,20 +12199,20 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>Hair loss prevention</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C536" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E536" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F536" t="n">
         <v>2</v>
@@ -12233,7 +12221,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Hair follicle growth promotion</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -12255,7 +12243,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>TGF-β1 pathway inhibition</t>
+          <t>Hair follicle growth promotion</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -12277,7 +12265,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CRF Receptor 1</t>
+          <t>TGF-β1 pathway inhibition</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -12299,7 +12287,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>CRF Receptor 2</t>
+          <t>CRF Receptor 1</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -12321,20 +12309,20 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CXCR3</t>
+          <t>CRF Receptor 2</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C541" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D541" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E541" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F541" t="n">
         <v>2</v>
@@ -12343,7 +12331,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>CXCL9</t>
+          <t>CXCR3</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -12365,7 +12353,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>CXCL10</t>
+          <t>CXCL9</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -12387,7 +12375,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CXCL11</t>
+          <t>CXCL10</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -12409,20 +12397,20 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Follicular bulge stem cells</t>
+          <t>CXCL11</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C545" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E545" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F545" t="n">
         <v>2</v>
@@ -12431,7 +12419,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>γ-Glutamyl transpeptidase (γ-GTP)</t>
+          <t>Follicular bulge stem cells</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -12453,7 +12441,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Alkaline phosphatase (ALP)</t>
+          <t>γ-Glutamyl transpeptidase (γ-GTP)</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -12475,7 +12463,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Epidermal growth factor (EGF)</t>
+          <t>Alkaline phosphatase (ALP)</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -12497,7 +12485,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Free radicals</t>
+          <t>Epidermal growth factor (EGF)</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -12519,7 +12507,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Antioxidant enzymes</t>
+          <t>Free radicals</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -12541,7 +12529,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Cytochrome c oxidase</t>
+          <t>Antioxidant enzymes</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -12563,7 +12551,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Mitochondrial cytochrome C oxidase</t>
+          <t>Cytochrome c oxidase</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -12585,7 +12573,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>ERK signaling</t>
+          <t>Mitochondrial cytochrome C oxidase</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -12607,7 +12595,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Hair follicle growth signaling</t>
+          <t>ERK signaling</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12629,7 +12617,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>ERK signaling pathway</t>
+          <t>Hair follicle growth signaling</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -12651,7 +12639,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Nitric oxide (NO)</t>
+          <t>ERK signaling pathway</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -12673,7 +12661,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>5-alpha reductase (referenced as current therapy)</t>
+          <t>Nitric oxide (NO)</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -12695,7 +12683,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Wnt10b (Wingless-type mouse mammary tumor virus integration site 10b)</t>
+          <t>5-alpha reductase (referenced as current therapy)</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -12717,7 +12705,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>TGF-β2 (Transforming growth factor beta 2)</t>
+          <t>Wnt10b (Wingless-type mouse mammary tumor virus integration site 10b)</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -12739,20 +12727,20 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Apoptosis in dermal papilla cells</t>
+          <t>TGF-β2 (Transforming growth factor beta 2)</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C560" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D560" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E560" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F560" t="n">
         <v>2</v>
@@ -12761,20 +12749,20 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Malassezia furfur</t>
+          <t>Apoptosis in dermal papilla cells</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C561" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D561" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E561" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F561" t="n">
         <v>2</v>
@@ -12783,7 +12771,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>TNF-alpha</t>
+          <t>Malassezia furfur</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -12805,7 +12793,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Hair follicle growth and survival</t>
+          <t>TNF-alpha</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -12827,7 +12815,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>PDE5 (Phosphodiesterase 5)</t>
+          <t>Hair follicle growth and survival</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -12849,7 +12837,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>PSA (Prostate Specific Antigen)</t>
+          <t>PDE5 (Phosphodiesterase 5)</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -12871,7 +12859,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Collagenase</t>
+          <t>PSA (Prostate Specific Antigen)</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -12893,7 +12881,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>IGF-1 (Insulin-like growth factor-1)</t>
+          <t>Collagenase</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -12915,7 +12903,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>TGF-beta1 (Transforming growth factor-beta1)</t>
+          <t>IGF-1 (Insulin-like growth factor-1)</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -12937,7 +12925,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Sonic Hedgehog pathway</t>
+          <t>TGF-beta1 (Transforming growth factor-beta1)</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -12959,7 +12947,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone synthesis</t>
+          <t>Sonic Hedgehog pathway</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -12981,7 +12969,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Cortisol production</t>
+          <t>Dihydrotestosterone synthesis</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -13003,7 +12991,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>DHT (Dihydrotestosterone) production</t>
+          <t>Cortisol production</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -13025,20 +13013,20 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Hair growth</t>
+          <t>DHT (Dihydrotestosterone) production</t>
         </is>
       </c>
       <c r="B573" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C573" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D573" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E573" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F573" t="n">
         <v>2</v>
@@ -13047,20 +13035,20 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Nrf-2 (Nuclear factor erythroid 2-related factor 2)</t>
+          <t>Hair growth</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C574" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D574" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E574" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F574" t="n">
         <v>2</v>
@@ -13069,7 +13057,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Nrf-2</t>
+          <t>Nrf-2 (Nuclear factor erythroid 2-related factor 2)</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -13091,7 +13079,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>ROCK (Rho-associated protein kinase)</t>
+          <t>Nrf-2</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -13113,7 +13101,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Basement membrane proteins</t>
+          <t>ROCK (Rho-associated protein kinase)</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -13135,7 +13123,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Placental Growth Factor (PlGF)</t>
+          <t>Basement membrane proteins</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -13157,7 +13145,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Hair matrix cell proliferation</t>
+          <t>Placental Growth Factor (PlGF)</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -13179,7 +13167,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Dermal papilla cell interaction</t>
+          <t>Hair matrix cell proliferation</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -13201,7 +13189,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Hair growth factors (IGF</t>
+          <t>Dermal papilla cell interaction</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -13223,7 +13211,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Antioxidant enzymes (HO-1</t>
+          <t>Hair growth factors (IGF</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -13245,7 +13233,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>NQO-1</t>
+          <t>Antioxidant enzymes (HO-1</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -13267,7 +13255,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>GSTpi)</t>
+          <t>NQO-1</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -13289,7 +13277,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Nrf-2 transcription factor</t>
+          <t>GSTpi)</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -13311,7 +13299,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Hair growth-related genes</t>
+          <t>Nrf-2 transcription factor</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -13333,7 +13321,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>DHT (dihydrotestosterone)</t>
+          <t>Hair growth-related genes</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -13355,7 +13343,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>IGF-I (Insulin-like Growth Factor)</t>
+          <t>DHT (dihydrotestosterone)</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -13377,7 +13365,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>PTEN (Phosphatase and Tensin Homolog)</t>
+          <t>IGF-I (Insulin-like Growth Factor)</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -13399,7 +13387,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CRH Receptor 1 (CRHR1)</t>
+          <t>PTEN (Phosphatase and Tensin Homolog)</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -13421,7 +13409,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CRH Receptor 2 (CRHR2)</t>
+          <t>CRH Receptor 1 (CRHR1)</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -13443,7 +13431,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>PI3K/Akt/mTOR pathway</t>
+          <t>CRH Receptor 2 (CRHR2)</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -13465,7 +13453,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Hyaluronidase</t>
+          <t>PI3K/Akt/mTOR pathway</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -13487,7 +13475,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>β-Catenin signaling pathway</t>
+          <t>Hyaluronidase</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -13509,7 +13497,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>TGF-beta</t>
+          <t>β-Catenin signaling pathway</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -13531,7 +13519,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>5-Alpha-Reductase Type 2 (5AR2)</t>
+          <t>TGF-beta</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -13553,7 +13541,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Epithelial-mesenchymal interactions</t>
+          <t>5-Alpha-Reductase Type 2 (5AR2)</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -13575,7 +13563,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>IGF-1 (Insulin-like Growth Factor-1)</t>
+          <t>Epithelial-mesenchymal interactions</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -13597,7 +13585,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>TGFβ1 (Transforming Growth Factor Beta 1)</t>
+          <t>IGF-1 (Insulin-like Growth Factor-1)</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -13619,7 +13607,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Cholesterol biosynthesis</t>
+          <t>TGFβ1 (Transforming Growth Factor Beta 1)</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -13641,7 +13629,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>7-DHCR (7-dehydrocholesterol reductase)</t>
+          <t>Cholesterol biosynthesis</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -13663,7 +13651,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>DHCR24</t>
+          <t>7-DHCR (7-dehydrocholesterol reductase)</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -13685,7 +13673,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>5α-reductase enzyme</t>
+          <t>DHCR24</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -13707,7 +13695,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>PGD2</t>
+          <t>5α-reductase enzyme</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -13729,7 +13717,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>PGE2</t>
+          <t>PGD2</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -13751,7 +13739,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Insulin-like growth factor-1</t>
+          <t>PGE2</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -13773,7 +13761,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Sebaceous glands</t>
+          <t>Insulin-like growth factor-1</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -13795,7 +13783,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Protein serine/threonine kinase</t>
+          <t>Sebaceous glands</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -13817,7 +13805,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Src protein</t>
+          <t>Protein serine/threonine kinase</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -13839,7 +13827,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Insulin-like growth factor 1 (IGF1)</t>
+          <t>Src protein</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -13861,7 +13849,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Glycogen synthase kinase-3β</t>
+          <t>Insulin-like growth factor 1 (IGF1)</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -13883,7 +13871,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Circulating androgens</t>
+          <t>Glycogen synthase kinase-3β</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -13905,7 +13893,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Inflammatory cytokines (IL-1β</t>
+          <t>Circulating androgens</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -13927,7 +13915,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Mesenchymal stem cells (MSCs)</t>
+          <t>Inflammatory cytokines (IL-1β</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -13949,7 +13937,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Adipose-derived stem cells (ADSCs)</t>
+          <t>Mesenchymal stem cells (MSCs)</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -13971,7 +13959,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Scalp muscle tension</t>
+          <t>Adipose-derived stem cells (ADSCs)</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -13993,7 +13981,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Blood flow regulation</t>
+          <t>Scalp muscle tension</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -14015,7 +14003,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>miR-22</t>
+          <t>Blood flow regulation</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -14037,7 +14025,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>TNF-α signaling pathway</t>
+          <t>miR-22</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -14059,7 +14047,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>PIK3CA</t>
+          <t>TNF-α signaling pathway</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -14081,7 +14069,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>PIK3CB</t>
+          <t>PIK3CA</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -14103,7 +14091,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>HRAS</t>
+          <t>PIK3CB</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -14125,7 +14113,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>RHOA</t>
+          <t>HRAS</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -14147,7 +14135,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Prostaglandin E2 production</t>
+          <t>RHOA</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -14169,7 +14157,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Phytoestrogen pathway</t>
+          <t>Prostaglandin E2 production</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -14191,7 +14179,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Indoleamine 2</t>
+          <t>Phytoestrogen pathway</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -14213,7 +14201,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>3-dioxygenase (IDO)</t>
+          <t>Indoleamine 2</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -14235,7 +14223,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Histone deacetylase</t>
+          <t>3-dioxygenase (IDO)</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -14257,7 +14245,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Hair growth cycle</t>
+          <t>Histone deacetylase</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -14279,7 +14267,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>DHT-induced signaling</t>
+          <t>Hair growth cycle</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -14301,7 +14289,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>JAK/STAT signaling pathway</t>
+          <t>DHT-induced signaling</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -14323,7 +14311,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Inflammatory mediators</t>
+          <t>JAK/STAT signaling pathway</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -14345,7 +14333,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Cytokines</t>
+          <t>Inflammatory mediators</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -14367,7 +14355,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Purinergic receptors (P2 receptors)</t>
+          <t>Cytokines</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -14389,7 +14377,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Circulation promotion</t>
+          <t>Purinergic receptors (P2 receptors)</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -14411,7 +14399,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Heat shock protein 70 (HSPA1A/B)</t>
+          <t>Circulation promotion</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -14433,7 +14421,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>T lymphocytes (CD8+</t>
+          <t>Heat shock protein 70 (HSPA1A/B)</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -14455,7 +14443,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>CD4+)</t>
+          <t>T lymphocytes (CD8+</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -14477,7 +14465,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Natural killer cells</t>
+          <t>CD4+)</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -14499,7 +14487,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Dendritic cells</t>
+          <t>Natural killer cells</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -14521,7 +14509,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>IL-12/IL-23 p40 subunit</t>
+          <t>Dendritic cells</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -14543,7 +14531,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>IL-23 p19 subunit</t>
+          <t>IL-12/IL-23 p40 subunit</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -14565,7 +14553,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Estrogen Receptor Beta</t>
+          <t>IL-23 p19 subunit</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -14587,7 +14575,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Prostaglandin D2 Synthase</t>
+          <t>Estrogen Receptor Beta</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -14609,7 +14597,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Gamma chain cytokines</t>
+          <t>Prostaglandin D2 Synthase</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -14631,7 +14619,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>IFN-gamma signaling</t>
+          <t>Gamma chain cytokines</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -14653,7 +14641,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Hair follicle immune privilege</t>
+          <t>IFN-gamma signaling</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -14675,7 +14663,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>CD3+ T cells</t>
+          <t>Hair follicle immune privilege</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -14697,7 +14685,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Antigen presenting cells</t>
+          <t>CD3+ T cells</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -14719,7 +14707,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>T helper cells</t>
+          <t>Antigen presenting cells</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -14741,7 +14729,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>NF-kB pathway</t>
+          <t>T helper cells</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -14763,7 +14751,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Growth Factor Signaling</t>
+          <t>NF-kB pathway</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14785,7 +14773,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>VEGFR-2</t>
+          <t>Growth Factor Signaling</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -14807,7 +14795,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Notch signaling pathway</t>
+          <t>VEGFR-2</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -14829,7 +14817,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>VCAN (Versican)</t>
+          <t>Notch signaling pathway</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -14851,7 +14839,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>miR-221-3p</t>
+          <t>VCAN (Versican)</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -14873,7 +14861,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>JNK</t>
+          <t>miR-221-3p</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -14895,7 +14883,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>p38 MAPK</t>
+          <t>JNK</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -14917,7 +14905,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Wnt5A</t>
+          <t>p38 MAPK</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -14939,7 +14927,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Dickkopf-1 (Dkk1)</t>
+          <t>Wnt5A</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -14961,7 +14949,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>TGF-β2/Smad signaling</t>
+          <t>Dickkopf-1 (Dkk1)</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -14983,7 +14971,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Hedgehog signaling</t>
+          <t>TGF-β2/Smad signaling</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -15005,20 +14993,20 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Keratin 17</t>
+          <t>Hedgehog signaling</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C663" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D663" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E663" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F663" t="n">
         <v>2</v>
@@ -15027,7 +15015,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Keratin 16</t>
+          <t>Keratin 17</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -15049,7 +15037,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Keratin 6</t>
+          <t>Keratin 16</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -15071,20 +15059,20 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Malassezia spp.</t>
+          <t>Keratin 6</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C666" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E666" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F666" t="n">
         <v>2</v>
@@ -15093,7 +15081,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Staphylococcus spp.</t>
+          <t>Malassezia spp.</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -15115,7 +15103,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Scalp microflora</t>
+          <t>Staphylococcus spp.</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -15137,7 +15125,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Inflammatory pathway</t>
+          <t>Scalp microflora</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -15159,7 +15147,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>PPARα (Peroxisome Proliferator-Activated Receptor alpha)</t>
+          <t>Inflammatory pathway</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -15181,7 +15169,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>T effector cells</t>
+          <t>PPARα (Peroxisome Proliferator-Activated Receptor alpha)</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -15203,7 +15191,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>JAK-STAT signaling pathway</t>
+          <t>T effector cells</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -15225,7 +15213,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>5-alpha Reductase Type 1</t>
+          <t>JAK-STAT signaling pathway</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -15247,7 +15235,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Calcification regulators</t>
+          <t>5-alpha Reductase Type 1</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -15269,20 +15257,20 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>IFN-γ</t>
+          <t>Calcification regulators</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C675" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E675" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F675" t="n">
         <v>2</v>
@@ -15291,20 +15279,20 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Testosterone binding protein</t>
+          <t>IFN-γ</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C676" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D676" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E676" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F676" t="n">
         <v>2</v>
@@ -15313,7 +15301,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>IFN-γR</t>
+          <t>Testosterone binding protein</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -15335,7 +15323,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Patched2 (Ptc2)</t>
+          <t>IFN-γR</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -15357,7 +15345,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Hedgehog signaling pathway</t>
+          <t>Patched2 (Ptc2)</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -15379,7 +15367,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Smoothened (Smo)</t>
+          <t>Hedgehog signaling pathway</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -15401,7 +15389,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Insulin-like Growth Factor-1 (IGF-1)</t>
+          <t>Smoothened (Smo)</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -15423,7 +15411,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Osteopontin</t>
+          <t>Insulin-like Growth Factor-1 (IGF-1)</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -15445,7 +15433,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Integrin (RGD domain binding)</t>
+          <t>Osteopontin</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -15467,7 +15455,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>miR-485-3p</t>
+          <t>Integrin (RGD domain binding)</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -15489,7 +15477,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Dermal papilla signals</t>
+          <t>miR-485-3p</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -15511,7 +15499,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>PDGFA</t>
+          <t>Dermal papilla signals</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -15533,7 +15521,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Hair stem cells</t>
+          <t>PDGFA</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -15555,7 +15543,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Dipeptidyl Peptidase IV (DPPIV)</t>
+          <t>Hair stem cells</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -15577,7 +15565,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DPPIV-Related Protein-1 (DPRP-1)</t>
+          <t>Dipeptidyl Peptidase IV (DPPIV)</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -15599,7 +15587,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DPPIV-Related Protein-2 (DPRP-2)</t>
+          <t>DPPIV-Related Protein-1 (DPRP-1)</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -15621,7 +15609,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DPPIV-Related Protein-3 (DPRP-3)</t>
+          <t>DPPIV-Related Protein-2 (DPRP-2)</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -15643,7 +15631,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Serine Protease</t>
+          <t>DPPIV-Related Protein-3 (DPRP-3)</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -15665,7 +15653,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Prolyl Oligopeptidase Family</t>
+          <t>Serine Protease</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -15687,7 +15675,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Hair follicle growth phase</t>
+          <t>Prolyl Oligopeptidase Family</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -15709,7 +15697,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>5-α-Reductase Type 1</t>
+          <t>Hair follicle growth phase</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -15731,7 +15719,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Sebaceous gland lipogenesis</t>
+          <t>5-α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -15753,7 +15741,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>CDK5</t>
+          <t>Sebaceous gland lipogenesis</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -15775,7 +15763,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Bcl-x(L)</t>
+          <t>CDK5</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -15797,7 +15785,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Caspase</t>
+          <t>Bcl-x(L)</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -15819,7 +15807,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>MYB transcription factor</t>
+          <t>Caspase</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -15841,7 +15829,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>OX40</t>
+          <t>MYB transcription factor</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -15863,7 +15851,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>γδ T cells</t>
+          <t>OX40</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -15885,7 +15873,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>IL-17</t>
+          <t>γδ T cells</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -15907,20 +15895,20 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Hair follicle cycling</t>
+          <t>IL-17</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C704" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E704" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F704" t="n">
         <v>2</v>
@@ -15929,20 +15917,20 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>PGD2 synthase</t>
+          <t>Hair follicle cycling</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C705" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D705" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E705" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F705" t="n">
         <v>2</v>
@@ -15951,7 +15939,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>5α-reductase Type II</t>
+          <t>PGD2 synthase</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -15973,7 +15961,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Luteinizing Hormone (LH)</t>
+          <t>5α-reductase Type II</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -15995,7 +15983,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Follicle-Stimulating Hormone (FSH)</t>
+          <t>Luteinizing Hormone (LH)</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -16017,7 +16005,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Hypothalamic-Pituitary-Testicular Axis</t>
+          <t>Follicle-Stimulating Hormone (FSH)</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -16039,7 +16027,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Sex Hormone Binding Globulin (SHBG)</t>
+          <t>Hypothalamic-Pituitary-Testicular Axis</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -16061,7 +16049,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Platelet-derived growth factor (PDGF)</t>
+          <t>Sex Hormone Binding Globulin (SHBG)</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -16083,7 +16071,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Transforming growth factor (TGF)</t>
+          <t>Platelet-derived growth factor (PDGF)</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -16105,7 +16093,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Growth factor signaling pathways</t>
+          <t>Transforming growth factor (TGF)</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -16127,7 +16115,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>5-alpha reductase type II</t>
+          <t>Growth factor signaling pathways</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -16149,7 +16137,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>NF-κβ</t>
+          <t>5-alpha reductase type II</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -16171,7 +16159,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Hair follicle inflammation</t>
+          <t>NF-κβ</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -16193,7 +16181,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Microbial infection of hair follicles</t>
+          <t>Hair follicle inflammation</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -16215,7 +16203,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DNA Methyltransferase 1 (DNMT1)</t>
+          <t>Microbial infection of hair follicles</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -16237,7 +16225,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Stem cell activation</t>
+          <t>DNA Methyltransferase 1 (DNMT1)</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -16259,7 +16247,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>RAGE</t>
+          <t>Stem cell activation</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -16281,7 +16269,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>HIF-1α</t>
+          <t>RAGE</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -16303,7 +16291,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>MAPK</t>
+          <t>HIF-1α</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -16325,7 +16313,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>CREB</t>
+          <t>MAPK</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -16347,7 +16335,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Lactobacillus</t>
+          <t>CREB</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -16369,7 +16357,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Biotin availability</t>
+          <t>Lactobacillus</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -16391,7 +16379,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Blood flow to scalp</t>
+          <t>Biotin availability</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -16413,7 +16401,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Hypothalamic-pituitary-adrenal (HPA) axis</t>
+          <t>Blood flow to scalp</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -16435,7 +16423,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>T helper cells (Th1/Th2)</t>
+          <t>Hypothalamic-pituitary-adrenal (HPA) axis</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -16457,7 +16445,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>T helper 17 cells (Th17)</t>
+          <t>T helper cells (Th1/Th2)</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -16479,7 +16467,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Regulatory T cells (Treg)</t>
+          <t>T helper 17 cells (Th17)</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -16501,7 +16489,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Corticotropin-releasing hormone (CRH)</t>
+          <t>Regulatory T cells (Treg)</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -16523,7 +16511,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Adrenocorticotropic hormone (ACTH)</t>
+          <t>Corticotropin-releasing hormone (CRH)</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -16545,7 +16533,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>P450 aromatase</t>
+          <t>Adrenocorticotropic hormone (ACTH)</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -16567,7 +16555,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>TMPRSS2</t>
+          <t>P450 aromatase</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -16589,7 +16577,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>ACE-2</t>
+          <t>TMPRSS2</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -16611,7 +16599,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Growth factors (TGF-β</t>
+          <t>ACE-2</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -16633,7 +16621,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>IGF)</t>
+          <t>Growth factors (TGF-β</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -16655,7 +16643,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Cytokines (IL-3</t>
+          <t>IGF)</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -16677,7 +16665,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>IL-8)</t>
+          <t>Cytokines (IL-3</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -16699,7 +16687,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>SOCS3 (Suppressor of Cytokine Signaling-3)</t>
+          <t>IL-8)</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -16721,7 +16709,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>Fas</t>
+          <t>SOCS3 (Suppressor of Cytokine Signaling-3)</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -16743,7 +16731,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>MHC I</t>
+          <t>Fas</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -16765,7 +16753,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>5-alpha-reductase Type 1</t>
+          <t>MHC I</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -16787,7 +16775,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>5-alpha-reductase Type 2</t>
+          <t>5-alpha-reductase Type 1</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -16809,7 +16797,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>Ferroptosis pathway</t>
+          <t>5-alpha-reductase Type 2</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -16831,7 +16819,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>Antioxidant system</t>
+          <t>Ferroptosis pathway</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -16853,7 +16841,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>Secretory phospholipase A2 Group-IIA (sPLA2-IIA)</t>
+          <t>Antioxidant system</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -16875,7 +16863,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>EGFR signaling</t>
+          <t>Secretory phospholipase A2 Group-IIA (sPLA2-IIA)</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -16897,7 +16885,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Shh signaling</t>
+          <t>EGFR signaling</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -16919,7 +16907,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Regulatory T cells (Tregs)</t>
+          <t>Shh signaling</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -16941,7 +16929,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>IL-2 signaling</t>
+          <t>Regulatory T cells (Tregs)</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -16963,7 +16951,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>NKG2D-expressing CD8 T cells</t>
+          <t>IL-2 signaling</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -16985,7 +16973,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>JAK/STAT signaling</t>
+          <t>NKG2D-expressing CD8 T cells</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -17007,7 +16995,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>Mechanotransduction</t>
+          <t>JAK/STAT signaling</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -17029,7 +17017,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>DHT (Dihydrotestosterone)</t>
+          <t>Mechanotransduction</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -17051,7 +17039,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>Angiogenesis/Neovascularization</t>
+          <t>DHT (Dihydrotestosterone)</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -17073,7 +17061,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>Testosterone 5-Alpha Reductase</t>
+          <t>Angiogenesis/Neovascularization</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -17095,7 +17083,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>IGF-1 Receptor</t>
+          <t>Testosterone 5-Alpha Reductase</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -17117,7 +17105,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>Lactotroph cells</t>
+          <t>IGF-1 Receptor</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -17139,7 +17127,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>Hypothalamic-pituitary-gonadal axis</t>
+          <t>Lactotroph cells</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -17161,7 +17149,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>IGF (Insulin-like Growth Factor)</t>
+          <t>Hypothalamic-pituitary-gonadal axis</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -17183,7 +17171,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>Oxidative stress markers</t>
+          <t>IGF (Insulin-like Growth Factor)</t>
         </is>
       </c>
       <c r="B762" t="n">
@@ -17205,7 +17193,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>Malondialdehyde (MDA)</t>
+          <t>Oxidative stress markers</t>
         </is>
       </c>
       <c r="B763" t="n">
@@ -17227,7 +17215,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>Ceruloplasmin (CER)</t>
+          <t>Malondialdehyde (MDA)</t>
         </is>
       </c>
       <c r="B764" t="n">
@@ -17249,7 +17237,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>Paraoxonase 1 (PON1)</t>
+          <t>Ceruloplasmin (CER)</t>
         </is>
       </c>
       <c r="B765" t="n">
@@ -17271,7 +17259,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>NRF2</t>
+          <t>Paraoxonase 1 (PON1)</t>
         </is>
       </c>
       <c r="B766" t="n">
@@ -17293,7 +17281,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>IκBζ-ATF3 axis</t>
+          <t>NRF2</t>
         </is>
       </c>
       <c r="B767" t="n">
@@ -17315,7 +17303,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>JAK-STAT signaling</t>
+          <t>IκBζ-ATF3 axis</t>
         </is>
       </c>
       <c r="B768" t="n">
@@ -17337,7 +17325,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>Albumin (plasma protein binding)</t>
+          <t>JAK-STAT signaling</t>
         </is>
       </c>
       <c r="B769" t="n">
@@ -17359,7 +17347,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>Macrophage polarization</t>
+          <t>Albumin (plasma protein binding)</t>
         </is>
       </c>
       <c r="B770" t="n">
@@ -17381,7 +17369,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>Dermal papilla cell apoptosis</t>
+          <t>Macrophage polarization</t>
         </is>
       </c>
       <c r="B771" t="n">
@@ -17403,7 +17391,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>Mesenchymal stem cells (umbilical cord-derived)</t>
+          <t>Dermal papilla cell apoptosis</t>
         </is>
       </c>
       <c r="B772" t="n">
@@ -17425,20 +17413,20 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>Androgen biosynthesis pathway</t>
+          <t>Mesenchymal stem cells (umbilical cord-derived)</t>
         </is>
       </c>
       <c r="B773" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C773" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D773" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E773" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F773" t="n">
         <v>2</v>
@@ -17447,20 +17435,20 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>11b-Hydroxylase</t>
+          <t>Androgen biosynthesis pathway</t>
         </is>
       </c>
       <c r="B774" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C774" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D774" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E774" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F774" t="n">
         <v>2</v>
@@ -17469,7 +17457,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>Scalp perimeter muscles</t>
+          <t>11b-Hydroxylase</t>
         </is>
       </c>
       <c r="B775" t="n">
@@ -17491,7 +17479,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>Whn/Foxn1 transcription factor</t>
+          <t>Scalp perimeter muscles</t>
         </is>
       </c>
       <c r="B776" t="n">
@@ -17513,7 +17501,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>Keratin genes</t>
+          <t>Whn/Foxn1 transcription factor</t>
         </is>
       </c>
       <c r="B777" t="n">
@@ -17535,7 +17523,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>Vitamin D Receptor</t>
+          <t>Keratin genes</t>
         </is>
       </c>
       <c r="B778" t="n">
@@ -17557,7 +17545,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>Hair follicle keratinocytes</t>
+          <t>Vitamin D Receptor</t>
         </is>
       </c>
       <c r="B779" t="n">
@@ -17579,7 +17567,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>Keratin 81 (Krt81)</t>
+          <t>Hair follicle keratinocytes</t>
         </is>
       </c>
       <c r="B780" t="n">
@@ -17601,7 +17589,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>Keratin 34 (Krt34)</t>
+          <t>Keratin 81 (Krt81)</t>
         </is>
       </c>
       <c r="B781" t="n">
@@ -17623,7 +17611,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>Keratin 33a (Krt33a)</t>
+          <t>Keratin 34 (Krt34)</t>
         </is>
       </c>
       <c r="B782" t="n">
@@ -17645,7 +17633,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>Sma and MAD-related protein 3 (Smad3)</t>
+          <t>Keratin 33a (Krt33a)</t>
         </is>
       </c>
       <c r="B783" t="n">
@@ -17667,7 +17655,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>Keratins (Krt81</t>
+          <t>Sma and MAD-related protein 3 (Smad3)</t>
         </is>
       </c>
       <c r="B784" t="n">
@@ -17689,7 +17677,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>Krt34</t>
+          <t>Keratins (Krt81</t>
         </is>
       </c>
       <c r="B785" t="n">
@@ -17711,7 +17699,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>Krt33a)</t>
+          <t>Krt34</t>
         </is>
       </c>
       <c r="B786" t="n">
@@ -17733,7 +17721,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>TGF-β/Smad3 pathway</t>
+          <t>Krt33a)</t>
         </is>
       </c>
       <c r="B787" t="n">
@@ -17755,7 +17743,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>Smad3</t>
+          <t>TGF-β/Smad3 pathway</t>
         </is>
       </c>
       <c r="B788" t="n">
@@ -17777,7 +17765,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>miR-133b</t>
+          <t>Smad3</t>
         </is>
       </c>
       <c r="B789" t="n">
@@ -17799,7 +17787,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>Msx2</t>
+          <t>miR-133b</t>
         </is>
       </c>
       <c r="B790" t="n">
@@ -17821,7 +17809,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Foxn1</t>
+          <t>Msx2</t>
         </is>
       </c>
       <c r="B791" t="n">
@@ -17843,7 +17831,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>Ha3</t>
+          <t>Foxn1</t>
         </is>
       </c>
       <c r="B792" t="n">
@@ -17865,7 +17853,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>Lef1</t>
+          <t>Ha3</t>
         </is>
       </c>
       <c r="B793" t="n">
@@ -17887,7 +17875,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>Dermal papilla paracrine factors</t>
+          <t>Lef1</t>
         </is>
       </c>
       <c r="B794" t="n">
@@ -17909,7 +17897,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Mitogenic factors for dermal papilla cells</t>
+          <t>Dermal papilla paracrine factors</t>
         </is>
       </c>
       <c r="B795" t="n">
@@ -17931,7 +17919,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Bcl-2/Bax</t>
+          <t>Mitogenic factors for dermal papilla cells</t>
         </is>
       </c>
       <c r="B796" t="n">
@@ -17953,7 +17941,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Melanocyte function</t>
+          <t>Bcl-2/Bax</t>
         </is>
       </c>
       <c r="B797" t="n">
@@ -17975,7 +17963,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Hair follicle aging</t>
+          <t>Melanocyte function</t>
         </is>
       </c>
       <c r="B798" t="n">
@@ -17997,7 +17985,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Erk signaling</t>
+          <t>Hair follicle aging</t>
         </is>
       </c>
       <c r="B799" t="n">
@@ -18019,7 +18007,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Minoxidil target (KATP channel opener)</t>
+          <t>Erk signaling</t>
         </is>
       </c>
       <c r="B800" t="n">
@@ -18041,7 +18029,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Hair follicle growth stimulation</t>
+          <t>Minoxidil target (KATP channel opener)</t>
         </is>
       </c>
       <c r="B801" t="n">
@@ -18063,7 +18051,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>Wnt signaling components</t>
+          <t>Hair follicle growth stimulation</t>
         </is>
       </c>
       <c r="B802" t="n">
@@ -18085,7 +18073,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>GABA receptors</t>
+          <t>Wnt signaling components</t>
         </is>
       </c>
       <c r="B803" t="n">
@@ -18107,7 +18095,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>NMDA receptors</t>
+          <t>GABA receptors</t>
         </is>
       </c>
       <c r="B804" t="n">
@@ -18129,7 +18117,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>KATP channel</t>
+          <t>NMDA receptors</t>
         </is>
       </c>
       <c r="B805" t="n">
@@ -18151,7 +18139,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor signaling</t>
+          <t>KATP channel</t>
         </is>
       </c>
       <c r="B806" t="n">
@@ -18173,7 +18161,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Dermal papilla stem cells</t>
+          <t>Vascular endothelial growth factor signaling</t>
         </is>
       </c>
       <c r="B807" t="n">
@@ -18195,7 +18183,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>Growth factors</t>
+          <t>Dermal papilla stem cells</t>
         </is>
       </c>
       <c r="B808" t="n">
@@ -18217,7 +18205,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor</t>
+          <t>Growth factors</t>
         </is>
       </c>
       <c r="B809" t="n">
@@ -18239,7 +18227,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor (VEGF) pathway</t>
+          <t>Vascular endothelial growth factor</t>
         </is>
       </c>
       <c r="B810" t="n">
@@ -18261,7 +18249,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>Hic-5</t>
+          <t>Vascular endothelial growth factor (VEGF) pathway</t>
         </is>
       </c>
       <c r="B811" t="n">
@@ -18283,7 +18271,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>Hair growth stimulation</t>
+          <t>Hic-5</t>
         </is>
       </c>
       <c r="B812" t="n">
@@ -18305,7 +18293,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>Anagen phase induction</t>
+          <t>Hair growth stimulation</t>
         </is>
       </c>
       <c r="B813" t="n">
@@ -18327,7 +18315,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>Microinflammation pathways</t>
+          <t>Anagen phase induction</t>
         </is>
       </c>
       <c r="B814" t="n">
@@ -18349,20 +18337,20 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>Phosphodiesterase</t>
+          <t>Microinflammation pathways</t>
         </is>
       </c>
       <c r="B815" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C815" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D815" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E815" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F815" t="n">
         <v>2</v>
@@ -18371,20 +18359,20 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>Sulfotransferase</t>
+          <t>Phosphodiesterase</t>
         </is>
       </c>
       <c r="B816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C816" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E816" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F816" t="n">
         <v>2</v>
@@ -18393,7 +18381,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>Minoxidil metabolism</t>
+          <t>Sulfotransferase</t>
         </is>
       </c>
       <c r="B817" t="n">
@@ -18415,7 +18403,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>Nitric Oxide (NO) production</t>
+          <t>Minoxidil metabolism</t>
         </is>
       </c>
       <c r="B818" t="n">
@@ -18437,7 +18425,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>Reactive Oxygen Species (ROS) modulation</t>
+          <t>Nitric Oxide (NO) production</t>
         </is>
       </c>
       <c r="B819" t="n">
@@ -18459,7 +18447,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>Redox-related signaling pathways</t>
+          <t>Reactive Oxygen Species (ROS) modulation</t>
         </is>
       </c>
       <c r="B820" t="n">
@@ -18481,7 +18469,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth</t>
+          <t>Redox-related signaling pathways</t>
         </is>
       </c>
       <c r="B821" t="n">
@@ -18503,7 +18491,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>TGF-beta pathway</t>
+          <t>Vascular endothelial growth</t>
         </is>
       </c>
       <c r="B822" t="n">
@@ -18525,7 +18513,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>Prostaglandin signaling</t>
+          <t>TGF-beta pathway</t>
         </is>
       </c>
       <c r="B823" t="n">
@@ -18547,7 +18535,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>VEGF receptor</t>
+          <t>Prostaglandin signaling</t>
         </is>
       </c>
       <c r="B824" t="n">
@@ -18569,7 +18557,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>Potassium channel</t>
+          <t>VEGF receptor</t>
         </is>
       </c>
       <c r="B825" t="n">
@@ -18591,7 +18579,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>Glucocorticoid Receptor (GR)</t>
+          <t>Potassium channel</t>
         </is>
       </c>
       <c r="B826" t="n">
@@ -18613,7 +18601,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>Aldosterone Receptor</t>
+          <t>Glucocorticoid Receptor (GR)</t>
         </is>
       </c>
       <c r="B827" t="n">
@@ -18635,7 +18623,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>CB1 receptor</t>
+          <t>Aldosterone Receptor</t>
         </is>
       </c>
       <c r="B828" t="n">
@@ -18657,7 +18645,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>TRPV1</t>
+          <t>CB1 receptor</t>
         </is>
       </c>
       <c r="B829" t="n">
@@ -18679,7 +18667,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>TRPV4</t>
+          <t>TRPV1</t>
         </is>
       </c>
       <c r="B830" t="n">
@@ -18701,7 +18689,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>Fibroblast Growth Factor 9 (FGF9)</t>
+          <t>TRPV4</t>
         </is>
       </c>
       <c r="B831" t="n">
@@ -18723,7 +18711,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>HOXB13</t>
+          <t>Fibroblast Growth Factor 9 (FGF9)</t>
         </is>
       </c>
       <c r="B832" t="n">
@@ -18745,7 +18733,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>PTGDS</t>
+          <t>HOXB13</t>
         </is>
       </c>
       <c r="B833" t="n">
@@ -18767,7 +18755,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>SFRP4</t>
+          <t>PTGDS</t>
         </is>
       </c>
       <c r="B834" t="n">
@@ -18789,7 +18777,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>SOD3</t>
+          <t>SFRP4</t>
         </is>
       </c>
       <c r="B835" t="n">
@@ -18811,7 +18799,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>DCN</t>
+          <t>SOD3</t>
         </is>
       </c>
       <c r="B836" t="n">
@@ -18833,7 +18821,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>Apoptosis pathways</t>
+          <t>DCN</t>
         </is>
       </c>
       <c r="B837" t="n">
@@ -18855,7 +18843,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Hair follicle dermal papilla</t>
+          <t>Apoptosis pathways</t>
         </is>
       </c>
       <c r="B838" t="n">
@@ -18877,7 +18865,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Hair growth factors</t>
+          <t>Hair follicle dermal papilla</t>
         </is>
       </c>
       <c r="B839" t="n">
@@ -18899,7 +18887,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Wnt/β-Catenin signaling</t>
+          <t>Hair growth factors</t>
         </is>
       </c>
       <c r="B840" t="n">
@@ -18921,7 +18909,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Transforming Growth Factor signaling</t>
+          <t>Wnt/β-Catenin signaling</t>
         </is>
       </c>
       <c r="B841" t="n">
@@ -18943,7 +18931,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Prostaglandin F (FP) receptor</t>
+          <t>Transforming Growth Factor signaling</t>
         </is>
       </c>
       <c r="B842" t="n">
@@ -18965,7 +18953,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Hair growth cycle regulation</t>
+          <t>Prostaglandin F (FP) receptor</t>
         </is>
       </c>
       <c r="B843" t="n">
@@ -18987,7 +18975,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Glucocorticoid Receptor</t>
+          <t>Hair growth cycle regulation</t>
         </is>
       </c>
       <c r="B844" t="n">
@@ -19009,7 +18997,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Potassium channels (KATP)</t>
+          <t>Glucocorticoid Receptor</t>
         </is>
       </c>
       <c r="B845" t="n">
@@ -19031,7 +19019,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Cell migration</t>
+          <t>Potassium channels (KATP)</t>
         </is>
       </c>
       <c r="B846" t="n">
@@ -19053,7 +19041,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>Growth signaling pathways</t>
+          <t>Cell migration</t>
         </is>
       </c>
       <c r="B847" t="n">
@@ -19075,7 +19063,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>Sulfotransferase enzyme</t>
+          <t>Growth signaling pathways</t>
         </is>
       </c>
       <c r="B848" t="n">
@@ -19097,7 +19085,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>Hair follicle potassium channels</t>
+          <t>Sulfotransferase enzyme</t>
         </is>
       </c>
       <c r="B849" t="n">
@@ -19119,7 +19107,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>H1 histamine receptor</t>
+          <t>Hair follicle potassium channels</t>
         </is>
       </c>
       <c r="B850" t="n">
@@ -19141,7 +19129,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>SPRY1</t>
+          <t>H1 histamine receptor</t>
         </is>
       </c>
       <c r="B851" t="n">
@@ -19163,7 +19151,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>NRP2</t>
+          <t>SPRY1</t>
         </is>
       </c>
       <c r="B852" t="n">
@@ -19185,7 +19173,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>Finasteride response pathway</t>
+          <t>NRP2</t>
         </is>
       </c>
       <c r="B853" t="n">
@@ -19207,7 +19195,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>Follicular stem cells</t>
+          <t>Finasteride response pathway</t>
         </is>
       </c>
       <c r="B854" t="n">
@@ -19229,7 +19217,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>Nrf2</t>
+          <t>Follicular stem cells</t>
         </is>
       </c>
       <c r="B855" t="n">
@@ -19251,7 +19239,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>TGFβ1</t>
+          <t>Nrf2</t>
         </is>
       </c>
       <c r="B856" t="n">
@@ -19273,7 +19261,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>Fungal targets</t>
+          <t>TGFβ1</t>
         </is>
       </c>
       <c r="B857" t="n">
@@ -19295,7 +19283,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>Androgen-mediated pathways</t>
+          <t>Fungal targets</t>
         </is>
       </c>
       <c r="B858" t="n">
@@ -19317,7 +19305,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>Skin microbiome</t>
+          <t>Androgen-mediated pathways</t>
         </is>
       </c>
       <c r="B859" t="n">
@@ -19339,7 +19327,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>Malassezia species</t>
+          <t>Skin microbiome</t>
         </is>
       </c>
       <c r="B860" t="n">
@@ -19361,7 +19349,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Malassezia species</t>
         </is>
       </c>
       <c r="B861" t="n">
@@ -19383,7 +19371,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>Cutibacterium</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B862" t="n">
@@ -19405,7 +19393,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Corynebacterium</t>
+          <t>Cutibacterium</t>
         </is>
       </c>
       <c r="B863" t="n">
@@ -19427,7 +19415,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Nitric oxide pathway</t>
+          <t>Corynebacterium</t>
         </is>
       </c>
       <c r="B864" t="n">
@@ -19449,7 +19437,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Vascular growth factors</t>
+          <t>Nitric oxide pathway</t>
         </is>
       </c>
       <c r="B865" t="n">
@@ -19471,7 +19459,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Oxidative stress-related genes</t>
+          <t>Vascular growth factors</t>
         </is>
       </c>
       <c r="B866" t="n">
@@ -19493,7 +19481,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Expression quantitative trait loci (eQTL) genes</t>
+          <t>Oxidative stress-related genes</t>
         </is>
       </c>
       <c r="B867" t="n">
@@ -19515,7 +19503,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Protein quantitative trait loci (pQTL) genes</t>
+          <t>Expression quantitative trait loci (eQTL) genes</t>
         </is>
       </c>
       <c r="B868" t="n">
@@ -19537,7 +19525,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Potassium channel (KATP)</t>
+          <t>Protein quantitative trait loci (pQTL) genes</t>
         </is>
       </c>
       <c r="B869" t="n">
@@ -19559,7 +19547,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Mitochondrial cytochrome c oxidase</t>
+          <t>Potassium channel (KATP)</t>
         </is>
       </c>
       <c r="B870" t="n">
@@ -19581,7 +19569,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>T cell apoptosis pathway</t>
+          <t>Mitochondrial cytochrome c oxidase</t>
         </is>
       </c>
       <c r="B871" t="n">
@@ -19603,7 +19591,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Hair follicle angiogenesis</t>
+          <t>T cell apoptosis pathway</t>
         </is>
       </c>
       <c r="B872" t="n">
@@ -19625,7 +19613,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>Protein phosphatase 2A</t>
+          <t>Hair follicle angiogenesis</t>
         </is>
       </c>
       <c r="B873" t="n">
@@ -19647,7 +19635,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>Protein phosphatase 2A</t>
         </is>
       </c>
       <c r="B874" t="n">
@@ -19669,7 +19657,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>MAPK8</t>
+          <t>BCL2</t>
         </is>
       </c>
       <c r="B875" t="n">
@@ -19691,7 +19679,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>MMP13</t>
+          <t>MAPK8</t>
         </is>
       </c>
       <c r="B876" t="n">
@@ -19713,7 +19701,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>AURKB</t>
+          <t>MMP13</t>
         </is>
       </c>
       <c r="B877" t="n">
@@ -19735,7 +19723,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>Nitric Oxide pathway</t>
+          <t>AURKB</t>
         </is>
       </c>
       <c r="B878" t="n">
@@ -19757,7 +19745,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>Hair follicle growth phase regulation</t>
+          <t>Nitric Oxide pathway</t>
         </is>
       </c>
       <c r="B879" t="n">
@@ -19779,7 +19767,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>Anagen phase promotion</t>
+          <t>Hair follicle growth phase regulation</t>
         </is>
       </c>
       <c r="B880" t="n">
@@ -19801,7 +19789,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>IL-1β</t>
+          <t>Anagen phase promotion</t>
         </is>
       </c>
       <c r="B881" t="n">
@@ -19823,7 +19811,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>VEGF-A</t>
+          <t>IL-1β</t>
         </is>
       </c>
       <c r="B882" t="n">
@@ -19845,7 +19833,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>Hair cycle regulation</t>
+          <t>VEGF-A</t>
         </is>
       </c>
       <c r="B883" t="n">
@@ -19867,7 +19855,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>Cell subpopulations in hair follicle</t>
+          <t>Hair cycle regulation</t>
         </is>
       </c>
       <c r="B884" t="n">
@@ -19889,7 +19877,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>Follicular miniaturization</t>
+          <t>Cell subpopulations in hair follicle</t>
         </is>
       </c>
       <c r="B885" t="n">
@@ -19911,7 +19899,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>Microinflammation</t>
+          <t>Follicular miniaturization</t>
         </is>
       </c>
       <c r="B886" t="n">
@@ -19933,7 +19921,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>Hair follicle papilla cells</t>
+          <t>Microinflammation</t>
         </is>
       </c>
       <c r="B887" t="n">
@@ -19955,7 +19943,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>Androgenetic alopecia pathway</t>
+          <t>Hair follicle papilla cells</t>
         </is>
       </c>
       <c r="B888" t="n">
@@ -19977,7 +19965,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>Estrogen receptor</t>
+          <t>Androgenetic alopecia pathway</t>
         </is>
       </c>
       <c r="B889" t="n">
@@ -22507,95 +22495,95 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>Natural antisense transcripts of SIRT</t>
+          <t>Sex hormone binding globulin</t>
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1004" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="D1004" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1004" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F1004" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>SIRT (Sirtuin)</t>
+          <t>Progesterone receptor</t>
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1005" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="D1005" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1005" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F1005" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>Epidermal Growth Factor Receptor (EGFR)</t>
+          <t>Natural antisense transcripts of SIRT</t>
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1006" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="D1006" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1006" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="F1006" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>DNA methyltransferase (DNMT)</t>
+          <t>SIRT (Sirtuin)</t>
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1007" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="D1007" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1007" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="F1007" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>Parathyroid Hormone Receptor (PTH1R)</t>
+          <t>Epidermal Growth Factor Receptor (EGFR)</t>
         </is>
       </c>
       <c r="B1008" t="n">
@@ -22617,73 +22605,73 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>Cereblon (CRBN)</t>
+          <t>DNA methyltransferase (DNMT)</t>
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1009" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D1009" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1009" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1009" t="n">
-        <v>1.25</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Dermal blood vessels</t>
+          <t>Parathyroid Hormone Receptor (PTH1R)</t>
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1010" t="n">
         <v>2</v>
       </c>
       <c r="D1010" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1010" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1010" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>Alpha-adrenergic receptors</t>
+          <t>Cereblon (CRBN)</t>
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1011" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D1011" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1011" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F1011" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>Testosterone synthesis</t>
+          <t>Dermal blood vessels</t>
         </is>
       </c>
       <c r="B1012" t="n">
@@ -22705,7 +22693,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>HSP90</t>
+          <t>Alpha-adrenergic receptors</t>
         </is>
       </c>
       <c r="B1013" t="n">
@@ -22727,7 +22715,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>Chondroitin-4-sulfate (C4S) proteoglycan</t>
+          <t>Testosterone synthesis</t>
         </is>
       </c>
       <c r="B1014" t="n">
@@ -22749,7 +22737,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>SHBG (Sex Hormone Binding Globulin)</t>
+          <t>HSP90</t>
         </is>
       </c>
       <c r="B1015" t="n">
@@ -22771,7 +22759,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>Nitric oxide (NO) synthesis</t>
+          <t>Chondroitin-4-sulfate (C4S) proteoglycan</t>
         </is>
       </c>
       <c r="B1016" t="n">
@@ -22793,7 +22781,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>Lipid peroxidation</t>
+          <t>SHBG (Sex Hormone Binding Globulin)</t>
         </is>
       </c>
       <c r="B1017" t="n">
@@ -22815,7 +22803,7 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>Constitutive Androstane Receptor (CAR)</t>
+          <t>Nitric oxide (NO) synthesis</t>
         </is>
       </c>
       <c r="B1018" t="n">
@@ -22837,7 +22825,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>Peroxisome Proliferator-Activated Receptor Gamma (PPARγ)</t>
+          <t>Lipid peroxidation</t>
         </is>
       </c>
       <c r="B1019" t="n">
@@ -22859,7 +22847,7 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>Pregnane X Receptor (PXR)</t>
+          <t>Constitutive Androstane Receptor (CAR)</t>
         </is>
       </c>
       <c r="B1020" t="n">
@@ -22881,7 +22869,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette (ABC) Transporters</t>
+          <t>Peroxisome Proliferator-Activated Receptor Gamma (PPARγ)</t>
         </is>
       </c>
       <c r="B1021" t="n">
@@ -22903,7 +22891,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>FKBP (FK506 Binding Protein)</t>
+          <t>Pregnane X Receptor (PXR)</t>
         </is>
       </c>
       <c r="B1022" t="n">
@@ -22925,7 +22913,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>FKBP-12</t>
+          <t>ATP-Binding Cassette (ABC) Transporters</t>
         </is>
       </c>
       <c r="B1023" t="n">
@@ -22947,7 +22935,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>Peptidyl-prolyl isomerase (Rotamase)</t>
+          <t>FKBP (FK506 Binding Protein)</t>
         </is>
       </c>
       <c r="B1024" t="n">
@@ -22969,7 +22957,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>B7.1</t>
+          <t>FKBP-12</t>
         </is>
       </c>
       <c r="B1025" t="n">
@@ -22991,7 +22979,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>B7.2</t>
+          <t>Peptidyl-prolyl isomerase (Rotamase)</t>
         </is>
       </c>
       <c r="B1026" t="n">
@@ -23013,7 +23001,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>CTLA-4</t>
+          <t>B7.1</t>
         </is>
       </c>
       <c r="B1027" t="n">
@@ -23035,7 +23023,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>Antigen-presenting cells</t>
+          <t>B7.2</t>
         </is>
       </c>
       <c r="B1028" t="n">
@@ -23057,7 +23045,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>Iron chelation</t>
+          <t>CTLA-4</t>
         </is>
       </c>
       <c r="B1029" t="n">
@@ -23079,7 +23067,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>ROS (Reactive Oxygen Species)</t>
+          <t>Antigen-presenting cells</t>
         </is>
       </c>
       <c r="B1030" t="n">
@@ -23101,7 +23089,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>TSH receptor</t>
+          <t>Iron chelation</t>
         </is>
       </c>
       <c r="B1031" t="n">
@@ -23123,7 +23111,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>FSH receptor</t>
+          <t>ROS (Reactive Oxygen Species)</t>
         </is>
       </c>
       <c r="B1032" t="n">
@@ -23145,7 +23133,7 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>LH receptor</t>
+          <t>TSH receptor</t>
         </is>
       </c>
       <c r="B1033" t="n">
@@ -23167,7 +23155,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>CG receptor</t>
+          <t>FSH receptor</t>
         </is>
       </c>
       <c r="B1034" t="n">
@@ -23189,7 +23177,7 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>Glycoprotein hormone receptors</t>
+          <t>LH receptor</t>
         </is>
       </c>
       <c r="B1035" t="n">
@@ -23211,7 +23199,7 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>Myeloid-Derived Suppressor Cells</t>
+          <t>CG receptor</t>
         </is>
       </c>
       <c r="B1036" t="n">
@@ -23233,7 +23221,7 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>Regulatory T cells</t>
+          <t>Glycoprotein hormone receptors</t>
         </is>
       </c>
       <c r="B1037" t="n">
@@ -23255,7 +23243,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>TH17 cells</t>
+          <t>Myeloid-Derived Suppressor Cells</t>
         </is>
       </c>
       <c r="B1038" t="n">
@@ -23277,20 +23265,20 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>SALL4</t>
+          <t>Regulatory T cells</t>
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1039" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D1039" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1039" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F1039" t="n">
         <v>1</v>
@@ -23299,7 +23287,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>Ikaros (IKZF1)</t>
+          <t>TH17 cells</t>
         </is>
       </c>
       <c r="B1040" t="n">
@@ -23321,20 +23309,20 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>Aiolos (IKZF3)</t>
+          <t>SALL4</t>
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1041" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D1041" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1041" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1041" t="n">
         <v>1</v>
@@ -23343,7 +23331,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>BRD4 (Bromodomain-containing protein 4)</t>
+          <t>Ikaros (IKZF1)</t>
         </is>
       </c>
       <c r="B1042" t="n">
@@ -23365,7 +23353,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>VEGFR (Vascular Endothelial Growth Factor Receptor)</t>
+          <t>Aiolos (IKZF3)</t>
         </is>
       </c>
       <c r="B1043" t="n">
@@ -23387,7 +23375,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>CD80</t>
+          <t>BRD4 (Bromodomain-containing protein 4)</t>
         </is>
       </c>
       <c r="B1044" t="n">
@@ -23409,7 +23397,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>CD86</t>
+          <t>VEGFR (Vascular Endothelial Growth Factor Receptor)</t>
         </is>
       </c>
       <c r="B1045" t="n">
@@ -23431,7 +23419,7 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>ULBP1</t>
+          <t>CD80</t>
         </is>
       </c>
       <c r="B1046" t="n">
@@ -23453,7 +23441,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>T cell receptors</t>
+          <t>CD86</t>
         </is>
       </c>
       <c r="B1047" t="n">
@@ -23475,7 +23463,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>Effector T cells</t>
+          <t>ULBP1</t>
         </is>
       </c>
       <c r="B1048" t="n">
@@ -23497,7 +23485,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>IL-2</t>
+          <t>T cell receptors</t>
         </is>
       </c>
       <c r="B1049" t="n">
@@ -23519,7 +23507,7 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>Nuclear Receptor</t>
+          <t>Effector T cells</t>
         </is>
       </c>
       <c r="B1050" t="n">
@@ -23541,7 +23529,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>PTCH1</t>
+          <t>IL-2</t>
         </is>
       </c>
       <c r="B1051" t="n">
@@ -23563,7 +23551,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>Sonic hedgehog signaling</t>
+          <t>Nuclear Receptor</t>
         </is>
       </c>
       <c r="B1052" t="n">
@@ -23585,7 +23573,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>Collagen binding</t>
+          <t>PTCH1</t>
         </is>
       </c>
       <c r="B1053" t="n">
@@ -23607,7 +23595,7 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>Tal1 (T-cell acute lymphocytic leukemia 1)</t>
+          <t>Sonic hedgehog signaling</t>
         </is>
       </c>
       <c r="B1054" t="n">
@@ -23629,7 +23617,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>IKZF2 (Helios)</t>
+          <t>Collagen binding</t>
         </is>
       </c>
       <c r="B1055" t="n">
@@ -23651,7 +23639,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>CRBN (Cereblon)</t>
+          <t>Tal1 (T-cell acute lymphocytic leukemia 1)</t>
         </is>
       </c>
       <c r="B1056" t="n">
@@ -23673,7 +23661,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>IKZF1 (Ikaros)</t>
+          <t>IKZF2 (Helios)</t>
         </is>
       </c>
       <c r="B1057" t="n">
@@ -23695,7 +23683,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>GSPT1</t>
+          <t>CRBN (Cereblon)</t>
         </is>
       </c>
       <c r="B1058" t="n">
@@ -23717,7 +23705,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>Steroid Receptors</t>
+          <t>IKZF1 (Ikaros)</t>
         </is>
       </c>
       <c r="B1059" t="n">
@@ -23739,7 +23727,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>SIRT (Sirtuins)</t>
+          <t>GSPT1</t>
         </is>
       </c>
       <c r="B1060" t="n">
@@ -23761,7 +23749,7 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>SIRT7</t>
+          <t>Steroid Receptors</t>
         </is>
       </c>
       <c r="B1061" t="n">
@@ -23783,7 +23771,7 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>SIRT4 (Sirtuin 4)</t>
+          <t>SIRT (Sirtuins)</t>
         </is>
       </c>
       <c r="B1062" t="n">
@@ -23805,7 +23793,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>SIRT3 (Sirtuin 3)</t>
+          <t>SIRT7</t>
         </is>
       </c>
       <c r="B1063" t="n">
@@ -23827,7 +23815,7 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>Natural antisense polynucleotides of SIRT</t>
+          <t>SIRT4 (Sirtuin 4)</t>
         </is>
       </c>
       <c r="B1064" t="n">
@@ -23849,7 +23837,7 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>CCHCR1 (Coiled-coil alpha-helical rod protein 1)</t>
+          <t>SIRT3 (Sirtuin 3)</t>
         </is>
       </c>
       <c r="B1065" t="n">
@@ -23871,7 +23859,7 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>Parathyroid hormone receptor</t>
+          <t>Natural antisense polynucleotides of SIRT</t>
         </is>
       </c>
       <c r="B1066" t="n">
@@ -23893,7 +23881,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>Collagen</t>
+          <t>CCHCR1 (Coiled-coil alpha-helical rod protein 1)</t>
         </is>
       </c>
       <c r="B1067" t="n">
@@ -23915,7 +23903,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>PTH/PTHrP receptor</t>
+          <t>Parathyroid hormone receptor</t>
         </is>
       </c>
       <c r="B1068" t="n">
@@ -23937,7 +23925,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>Hairless Gene (HR)</t>
+          <t>Collagen</t>
         </is>
       </c>
       <c r="B1069" t="n">
@@ -23959,7 +23947,7 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>Osteoblasts</t>
+          <t>PTH/PTHrP receptor</t>
         </is>
       </c>
       <c r="B1070" t="n">
@@ -23981,7 +23969,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>Androgen pathway</t>
+          <t>Hairless Gene (HR)</t>
         </is>
       </c>
       <c r="B1071" t="n">
@@ -24003,7 +23991,7 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>Hyperandrogenism</t>
+          <t>Osteoblasts</t>
         </is>
       </c>
       <c r="B1072" t="n">
@@ -24025,36 +24013,36 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>CD19</t>
+          <t>Androgen pathway</t>
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1073" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1073" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1073" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F1073" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>IL-18</t>
+          <t>Hyperandrogenism</t>
         </is>
       </c>
       <c r="B1074" t="n">
         <v>1</v>
       </c>
       <c r="C1074" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1074" t="n">
         <v>1</v>
@@ -24063,35 +24051,35 @@
         <v>0.5</v>
       </c>
       <c r="F1074" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>PI3K (Phosphoinositide 3-kinase)</t>
+          <t>CD19</t>
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1075" t="n">
         <v>1</v>
       </c>
       <c r="D1075" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1075" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F1075" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>CD25</t>
+          <t>IL-18</t>
         </is>
       </c>
       <c r="B1076" t="n">
@@ -24113,7 +24101,7 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>BCL-2</t>
+          <t>PI3K (Phosphoinositide 3-kinase)</t>
         </is>
       </c>
       <c r="B1077" t="n">
@@ -24135,20 +24123,20 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>EGFR (Epidermal Growth Factor Receptor)</t>
+          <t>CD25</t>
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1078" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1078" t="n">
         <v>1</v>
       </c>
       <c r="E1078" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F1078" t="n">
         <v>0.5</v>
@@ -24157,7 +24145,7 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>IKZF2</t>
+          <t>BCL-2</t>
         </is>
       </c>
       <c r="B1079" t="n">
@@ -24179,20 +24167,20 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>CK1α</t>
+          <t>EGFR (Epidermal Growth Factor Receptor)</t>
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1080" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1080" t="n">
         <v>1</v>
       </c>
       <c r="E1080" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F1080" t="n">
         <v>0.5</v>
@@ -24201,7 +24189,7 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>FAM83F</t>
+          <t>IKZF2</t>
         </is>
       </c>
       <c r="B1081" t="n">
@@ -24223,7 +24211,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>DTWD1</t>
+          <t>CK1α</t>
         </is>
       </c>
       <c r="B1082" t="n">
@@ -24245,7 +24233,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>ZFP91</t>
+          <t>FAM83F</t>
         </is>
       </c>
       <c r="B1083" t="n">
@@ -24267,7 +24255,7 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>ZFP62</t>
+          <t>DTWD1</t>
         </is>
       </c>
       <c r="B1084" t="n">
@@ -24289,7 +24277,7 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>ZFP36L2</t>
+          <t>ZFP91</t>
         </is>
       </c>
       <c r="B1085" t="n">
@@ -24311,7 +24299,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>RNF166</t>
+          <t>ZFP62</t>
         </is>
       </c>
       <c r="B1086" t="n">
@@ -24333,7 +24321,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>IKZF1</t>
+          <t>ZFP36L2</t>
         </is>
       </c>
       <c r="B1087" t="n">
@@ -24355,7 +24343,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>IKZF3</t>
+          <t>RNF166</t>
         </is>
       </c>
       <c r="B1088" t="n">
@@ -24377,7 +24365,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>IKZF4</t>
+          <t>IKZF1</t>
         </is>
       </c>
       <c r="B1089" t="n">
@@ -24399,7 +24387,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>IKZF5</t>
+          <t>IKZF3</t>
         </is>
       </c>
       <c r="B1090" t="n">
@@ -24421,7 +24409,7 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>RAB28</t>
+          <t>IKZF4</t>
         </is>
       </c>
       <c r="B1091" t="n">
@@ -24443,7 +24431,7 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>GSTP1</t>
+          <t>IKZF5</t>
         </is>
       </c>
       <c r="B1092" t="n">
@@ -24465,7 +24453,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>GSPT2</t>
+          <t>RAB28</t>
         </is>
       </c>
       <c r="B1093" t="n">
@@ -24487,7 +24475,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>TIMM10</t>
+          <t>GSTP1</t>
         </is>
       </c>
       <c r="B1094" t="n">
@@ -24509,7 +24497,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>GZF1</t>
+          <t>GSPT2</t>
         </is>
       </c>
       <c r="B1095" t="n">
@@ -24531,7 +24519,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>EGR1</t>
+          <t>TIMM10</t>
         </is>
       </c>
       <c r="B1096" t="n">
@@ -24553,7 +24541,7 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>HIC1</t>
+          <t>GZF1</t>
         </is>
       </c>
       <c r="B1097" t="n">
@@ -24575,7 +24563,7 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>HIC2</t>
+          <t>EGR1</t>
         </is>
       </c>
       <c r="B1098" t="n">
@@ -24597,7 +24585,7 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>INSM2</t>
+          <t>HIC1</t>
         </is>
       </c>
       <c r="B1099" t="n">
@@ -24619,7 +24607,7 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>OSR2</t>
+          <t>HIC2</t>
         </is>
       </c>
       <c r="B1100" t="n">
@@ -24641,7 +24629,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>INSM2</t>
         </is>
       </c>
       <c r="B1101" t="n">
@@ -24663,7 +24651,7 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>PRD15</t>
+          <t>OSR2</t>
         </is>
       </c>
       <c r="B1102" t="n">
@@ -24685,7 +24673,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>SALL1</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="B1103" t="n">
@@ -24707,7 +24695,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>SALL3</t>
+          <t>PRD15</t>
         </is>
       </c>
       <c r="B1104" t="n">
@@ -24729,7 +24717,7 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>WIZ</t>
+          <t>SALL1</t>
         </is>
       </c>
       <c r="B1105" t="n">
@@ -24751,7 +24739,7 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>ZBT17</t>
+          <t>SALL3</t>
         </is>
       </c>
       <c r="B1106" t="n">
@@ -24773,7 +24761,7 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>ZBT41</t>
+          <t>WIZ</t>
         </is>
       </c>
       <c r="B1107" t="n">
@@ -24795,7 +24783,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>ZBT49</t>
+          <t>ZBT17</t>
         </is>
       </c>
       <c r="B1108" t="n">
@@ -24817,7 +24805,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>ZBT7A</t>
+          <t>ZBT41</t>
         </is>
       </c>
       <c r="B1109" t="n">
@@ -24839,7 +24827,7 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>ZBT7B</t>
+          <t>ZBT49</t>
         </is>
       </c>
       <c r="B1110" t="n">
@@ -24861,7 +24849,7 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>ZBTB2</t>
+          <t>ZBT7A</t>
         </is>
       </c>
       <c r="B1111" t="n">
@@ -24883,7 +24871,7 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>ZBTB39</t>
+          <t>ZBT7B</t>
         </is>
       </c>
       <c r="B1112" t="n">
@@ -24905,7 +24893,7 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>ZIK1</t>
+          <t>ZBTB2</t>
         </is>
       </c>
       <c r="B1113" t="n">
@@ -24927,7 +24915,7 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>ZNF3</t>
+          <t>ZBTB39</t>
         </is>
       </c>
       <c r="B1114" t="n">
@@ -24949,7 +24937,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>ZNF217</t>
+          <t>ZIK1</t>
         </is>
       </c>
       <c r="B1115" t="n">
@@ -24971,7 +24959,7 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>ZNF276</t>
+          <t>ZNF3</t>
         </is>
       </c>
       <c r="B1116" t="n">
@@ -24993,7 +24981,7 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>ZNF316</t>
+          <t>ZNF217</t>
         </is>
       </c>
       <c r="B1117" t="n">
@@ -25015,7 +25003,7 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>ZNF324B</t>
+          <t>ZNF276</t>
         </is>
       </c>
       <c r="B1118" t="n">
@@ -25037,7 +25025,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>ZNF335</t>
+          <t>ZNF316</t>
         </is>
       </c>
       <c r="B1119" t="n">
@@ -25059,7 +25047,7 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>ZNF397</t>
+          <t>ZNF324B</t>
         </is>
       </c>
       <c r="B1120" t="n">
@@ -25081,7 +25069,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>ZNF407</t>
+          <t>ZNF335</t>
         </is>
       </c>
       <c r="B1121" t="n">
@@ -25103,7 +25091,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>ZNF408</t>
+          <t>ZNF397</t>
         </is>
       </c>
       <c r="B1122" t="n">
@@ -25125,7 +25113,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>ZNF462</t>
+          <t>ZNF407</t>
         </is>
       </c>
       <c r="B1123" t="n">
@@ -25147,7 +25135,7 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>ZNF483</t>
+          <t>ZNF408</t>
         </is>
       </c>
       <c r="B1124" t="n">
@@ -25169,7 +25157,7 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>SNF517</t>
+          <t>ZNF462</t>
         </is>
       </c>
       <c r="B1125" t="n">
@@ -25191,7 +25179,7 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>ZNF526</t>
+          <t>ZNF483</t>
         </is>
       </c>
       <c r="B1126" t="n">
@@ -25213,7 +25201,7 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>ZNF581</t>
+          <t>SNF517</t>
         </is>
       </c>
       <c r="B1127" t="n">
@@ -25235,7 +25223,7 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>ZNF587</t>
+          <t>ZNF526</t>
         </is>
       </c>
       <c r="B1128" t="n">
@@ -25257,7 +25245,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>ZNF589</t>
+          <t>ZNF581</t>
         </is>
       </c>
       <c r="B1129" t="n">
@@ -25279,7 +25267,7 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>ZNF618</t>
+          <t>ZNF587</t>
         </is>
       </c>
       <c r="B1130" t="n">
@@ -25301,7 +25289,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>ZNF644</t>
+          <t>ZNF589</t>
         </is>
       </c>
       <c r="B1131" t="n">
@@ -25323,7 +25311,7 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>ZNF646</t>
+          <t>ZNF618</t>
         </is>
       </c>
       <c r="B1132" t="n">
@@ -25345,7 +25333,7 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>ZNF653</t>
+          <t>ZNF644</t>
         </is>
       </c>
       <c r="B1133" t="n">
@@ -25367,7 +25355,7 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>ZNF654</t>
+          <t>ZNF646</t>
         </is>
       </c>
       <c r="B1134" t="n">
@@ -25389,7 +25377,7 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>ZNF692</t>
+          <t>ZNF653</t>
         </is>
       </c>
       <c r="B1135" t="n">
@@ -25411,7 +25399,7 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>ZNF724</t>
+          <t>ZNF654</t>
         </is>
       </c>
       <c r="B1136" t="n">
@@ -25433,7 +25421,7 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>ZNF771</t>
+          <t>ZNF692</t>
         </is>
       </c>
       <c r="B1137" t="n">
@@ -25455,7 +25443,7 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>ZNF782</t>
+          <t>ZNF724</t>
         </is>
       </c>
       <c r="B1138" t="n">
@@ -25477,7 +25465,7 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>ZNF784</t>
+          <t>ZNF771</t>
         </is>
       </c>
       <c r="B1139" t="n">
@@ -25499,7 +25487,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>ZNF814</t>
+          <t>ZNF782</t>
         </is>
       </c>
       <c r="B1140" t="n">
@@ -25521,7 +25509,7 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>ZSC10</t>
+          <t>ZNF784</t>
         </is>
       </c>
       <c r="B1141" t="n">
@@ -25543,7 +25531,7 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>ZSC22</t>
+          <t>ZNF814</t>
         </is>
       </c>
       <c r="B1142" t="n">
@@ -25565,7 +25553,7 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>ZC827</t>
+          <t>ZSC10</t>
         </is>
       </c>
       <c r="B1143" t="n">
@@ -25587,7 +25575,7 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>ZUFSP</t>
+          <t>ZSC22</t>
         </is>
       </c>
       <c r="B1144" t="n">
@@ -25609,7 +25597,7 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>DNMT1</t>
+          <t>ZC827</t>
         </is>
       </c>
       <c r="B1145" t="n">
@@ -25631,7 +25619,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>SIRT5 (Sirtuin 5)</t>
+          <t>ZUFSP</t>
         </is>
       </c>
       <c r="B1146" t="n">
@@ -25653,7 +25641,7 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>VISTA (V-domain Ig suppressor of T cell activation)</t>
+          <t>DNMT1</t>
         </is>
       </c>
       <c r="B1147" t="n">
@@ -25675,7 +25663,7 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>PD-L3</t>
+          <t>SIRT5 (Sirtuin 5)</t>
         </is>
       </c>
       <c r="B1148" t="n">
@@ -25697,22 +25685,66 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
+          <t>VISTA (V-domain Ig suppressor of T cell activation)</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>PD-L3</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
           <t>T cell activation pathway</t>
         </is>
       </c>
-      <c r="B1149" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1149" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1149" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F1149" t="n">
+      <c r="B1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1151" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/AGA_Dark_Targets.xlsx
+++ b/output/AGA_Dark_Targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1151"/>
+  <dimension ref="A1:F1159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C33" t="n">
-        <v>4.171428571428572</v>
+        <v>4.176136363636363</v>
       </c>
       <c r="D33" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E33" t="n">
-        <v>0.005681818181818182</v>
+        <v>0.005649717514124294</v>
       </c>
       <c r="F33" t="n">
-        <v>3.768506493506494</v>
+        <v>3.775038520801232</v>
       </c>
     </row>
     <row r="34">
@@ -10747,95 +10747,95 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CD8+ T cells</t>
+          <t>Leptin Receptor</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C470" t="n">
-        <v>2.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="D470" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E470" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="F470" t="n">
-        <v>2.428571428571429</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Melanocortin-5 receptor (MC5R)</t>
+          <t>Reactive Oxygen Species</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C471" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D471" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E471" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F471" t="n">
-        <v>2.333333333333333</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Laminin-332</t>
+          <t>p16/pRb senescence markers</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C472" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E472" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F472" t="n">
-        <v>2.333333333333333</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Sebum production</t>
+          <t>CD8+ T cells</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C473" t="n">
-        <v>3.5</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E473" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="F473" t="n">
-        <v>2.333333333333333</v>
+        <v>2.428571428571429</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CD4 T cells</t>
+          <t>Melanocortin-5 receptor (MC5R)</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -10857,7 +10857,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Growth factor signaling</t>
+          <t>Laminin-332</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -10879,7 +10879,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>IL-6)</t>
+          <t>Sebum production</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -10901,7 +10901,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CD200</t>
+          <t>CD4 T cells</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -10923,7 +10923,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Prolactin</t>
+          <t>Growth factor signaling</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -10945,7 +10945,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>TLR3</t>
+          <t>IL-6)</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -10967,7 +10967,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Inflammatory cytokines</t>
+          <t>CD200</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -10989,7 +10989,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Estrogen receptor</t>
+          <t>Prolactin</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -11011,117 +11011,117 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>21-hydroxylase</t>
+          <t>TLR3</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C482" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E482" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F482" t="n">
-        <v>2.25</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Insulin signaling</t>
+          <t>Inflammatory cytokines</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C483" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D483" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E483" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F483" t="n">
-        <v>2.25</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Hair follicle mesenchymal stem cells (HF-MSCs)</t>
+          <t>Estrogen receptor</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C484" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E484" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F484" t="n">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Dermal sheath cells</t>
+          <t>21-hydroxylase</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C485" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D485" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E485" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type I</t>
+          <t>Insulin signaling</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C486" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D486" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E486" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F486" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Stress response system in scalp and hair follicles</t>
+          <t>Hair follicle mesenchymal stem cells (HF-MSCs)</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -11143,7 +11143,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Growth factors (VEGF</t>
+          <t>Dermal sheath cells</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -11165,7 +11165,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>PDGF)</t>
+          <t>5-Alpha Reductase Type I</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -11187,7 +11187,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Anagen phase regulation</t>
+          <t>Stress response system in scalp and hair follicles</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -11209,7 +11209,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Apoptosis inhibition</t>
+          <t>Growth factors (VEGF</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -11231,7 +11231,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Mitochondrial activation</t>
+          <t>PDGF)</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -11253,7 +11253,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>TFAM (Mitochondrial transcription factor A)</t>
+          <t>Anagen phase regulation</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -11275,7 +11275,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>ATP5A1 (ATP synthase F1 subunit alpha)</t>
+          <t>Apoptosis inhibition</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -11297,7 +11297,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Fibrosis pathway</t>
+          <t>Mitochondrial activation</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -11319,7 +11319,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Calcification pathway</t>
+          <t>TFAM (Mitochondrial transcription factor A)</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -11341,7 +11341,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>EDAR</t>
+          <t>ATP5A1 (ATP synthase F1 subunit alpha)</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -11363,7 +11363,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Melanocyte</t>
+          <t>Fibrosis pathway</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -11385,7 +11385,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Lama3 (Laminin alpha-3)</t>
+          <t>Calcification pathway</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -11407,7 +11407,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Basement membrane signaling</t>
+          <t>EDAR</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -11429,7 +11429,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>5α-Reductase (DHT inhibition)</t>
+          <t>Melanocyte</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -11451,7 +11451,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>CCHCR1</t>
+          <t>Lama3 (Laminin alpha-3)</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -11473,7 +11473,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Hair keratins</t>
+          <t>Basement membrane signaling</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -11495,7 +11495,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Keratin-associated proteins (KRTAPs)</t>
+          <t>5α-Reductase (DHT inhibition)</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -11517,20 +11517,20 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Mast cells</t>
+          <t>CCHCR1</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C505" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E505" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F505" t="n">
         <v>2</v>
@@ -11539,7 +11539,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Polyamine metabolism</t>
+          <t>Hair keratins</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -11561,7 +11561,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Ornithine decarboxylase</t>
+          <t>Keratin-associated proteins (KRTAPs)</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -11583,20 +11583,20 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>hsa-miR-5193</t>
+          <t>Mast cells</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C508" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D508" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E508" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F508" t="n">
         <v>2</v>
@@ -11605,7 +11605,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>TP53</t>
+          <t>Polyamine metabolism</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -11627,7 +11627,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>LOXL1-AS1</t>
+          <t>Ornithine decarboxylase</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -11649,20 +11649,20 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Vascular smooth muscle cells</t>
+          <t>hsa-miR-5193</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C511" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E511" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F511" t="n">
         <v>2</v>
@@ -11671,7 +11671,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Hair Follicle Stem Cells</t>
+          <t>TP53</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -11693,7 +11693,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Mesenchymal Stem Cells</t>
+          <t>LOXL1-AS1</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -11715,20 +11715,20 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Epithelial Stem Cells</t>
+          <t>Vascular smooth muscle cells</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E514" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F514" t="n">
         <v>2</v>
@@ -11737,7 +11737,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>bFGF (Basic Fibroblast Growth Factor)</t>
+          <t>Hair Follicle Stem Cells</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -11759,7 +11759,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Fibroblast signaling</t>
+          <t>Mesenchymal Stem Cells</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -11781,7 +11781,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Tissue regeneration</t>
+          <t>Epithelial Stem Cells</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -11803,7 +11803,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>EGF (Epidermal Growth Factor)</t>
+          <t>bFGF (Basic Fibroblast Growth Factor)</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -11825,7 +11825,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>FGF7 (Fibroblast Growth Factor 7)</t>
+          <t>Fibroblast signaling</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -11847,7 +11847,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>ASS1 (Argininosuccinate synthase)</t>
+          <t>Tissue regeneration</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -11869,7 +11869,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>PAICS (Phosphoribosyl aminoimidazole carboxylase)</t>
+          <t>EGF (Epidermal Growth Factor)</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -11891,7 +11891,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>CKAP4 (Cytoskeleton-associated protein 4)</t>
+          <t>FGF7 (Fibroblast Growth Factor 7)</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -11913,7 +11913,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>GSN (Gelsolin)</t>
+          <t>ASS1 (Argininosuccinate synthase)</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -11935,7 +11935,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>IQGAP1 (Ras GTPase-activating-like protein 1)</t>
+          <t>PAICS (Phosphoribosyl aminoimidazole carboxylase)</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -11957,7 +11957,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>SKP1 (S-phase kinase-associated protein 1)</t>
+          <t>CKAP4 (Cytoskeleton-associated protein 4)</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -11979,7 +11979,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>SPTAN1 (Spectrin alpha chain</t>
+          <t>GSN (Gelsolin)</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -12001,7 +12001,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>brain)</t>
+          <t>IQGAP1 (Ras GTPase-activating-like protein 1)</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -12023,7 +12023,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>PLEC1 (Plectin-1)</t>
+          <t>SKP1 (S-phase kinase-associated protein 1)</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -12045,7 +12045,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Germinal matrix cells</t>
+          <t>SPTAN1 (Spectrin alpha chain</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -12067,7 +12067,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Dermal papilla cells (DPC)</t>
+          <t>brain)</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -12089,7 +12089,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Cell cycle regulators (Cyclin D1</t>
+          <t>PLEC1 (Plectin-1)</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -12111,7 +12111,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>C-Myc)</t>
+          <t>Germinal matrix cells</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -12133,7 +12133,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Hair growth factors (EGF</t>
+          <t>Dermal papilla cells (DPC)</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -12155,7 +12155,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Hair growth inhibitors (DKK-1</t>
+          <t>Cell cycle regulators (Cyclin D1</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -12177,7 +12177,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>TGF-α1)</t>
+          <t>C-Myc)</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -12199,20 +12199,20 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Hair loss prevention</t>
+          <t>Hair growth factors (EGF</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C536" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D536" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E536" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F536" t="n">
         <v>2</v>
@@ -12221,7 +12221,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>Hair growth inhibitors (DKK-1</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -12243,7 +12243,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Hair follicle growth promotion</t>
+          <t>TGF-α1)</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -12265,20 +12265,20 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>TGF-β1 pathway inhibition</t>
+          <t>Hair loss prevention</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C539" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D539" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E539" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F539" t="n">
         <v>2</v>
@@ -12287,7 +12287,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>CRF Receptor 1</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -12309,7 +12309,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CRF Receptor 2</t>
+          <t>Hair follicle growth promotion</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -12331,20 +12331,20 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>CXCR3</t>
+          <t>TGF-β1 pathway inhibition</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C542" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E542" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F542" t="n">
         <v>2</v>
@@ -12353,20 +12353,20 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>CXCL9</t>
+          <t>CRF Receptor 1</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C543" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D543" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E543" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F543" t="n">
         <v>2</v>
@@ -12375,20 +12375,20 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CXCL10</t>
+          <t>CRF Receptor 2</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C544" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E544" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F544" t="n">
         <v>2</v>
@@ -12397,7 +12397,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>CXCL11</t>
+          <t>CXCR3</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -12419,20 +12419,20 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Follicular bulge stem cells</t>
+          <t>CXCL9</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C546" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E546" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F546" t="n">
         <v>2</v>
@@ -12441,20 +12441,20 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>γ-Glutamyl transpeptidase (γ-GTP)</t>
+          <t>CXCL10</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C547" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D547" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E547" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F547" t="n">
         <v>2</v>
@@ -12463,20 +12463,20 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Alkaline phosphatase (ALP)</t>
+          <t>CXCL11</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C548" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E548" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F548" t="n">
         <v>2</v>
@@ -12485,7 +12485,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Epidermal growth factor (EGF)</t>
+          <t>Follicular bulge stem cells</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -12507,7 +12507,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Free radicals</t>
+          <t>γ-Glutamyl transpeptidase (γ-GTP)</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -12529,7 +12529,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Antioxidant enzymes</t>
+          <t>Alkaline phosphatase (ALP)</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -12551,7 +12551,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Cytochrome c oxidase</t>
+          <t>Epidermal growth factor (EGF)</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -12573,7 +12573,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Mitochondrial cytochrome C oxidase</t>
+          <t>Free radicals</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -12595,7 +12595,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>ERK signaling</t>
+          <t>Antioxidant enzymes</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12617,7 +12617,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Hair follicle growth signaling</t>
+          <t>Cytochrome c oxidase</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -12639,7 +12639,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>ERK signaling pathway</t>
+          <t>Mitochondrial cytochrome C oxidase</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -12661,7 +12661,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Nitric oxide (NO)</t>
+          <t>ERK signaling</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -12683,7 +12683,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>5-alpha reductase (referenced as current therapy)</t>
+          <t>Hair follicle growth signaling</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -12705,7 +12705,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Wnt10b (Wingless-type mouse mammary tumor virus integration site 10b)</t>
+          <t>ERK signaling pathway</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -12727,7 +12727,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>TGF-β2 (Transforming growth factor beta 2)</t>
+          <t>Nitric oxide (NO)</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -12749,20 +12749,20 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Apoptosis in dermal papilla cells</t>
+          <t>5-alpha reductase (referenced as current therapy)</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C561" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D561" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E561" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F561" t="n">
         <v>2</v>
@@ -12771,7 +12771,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Malassezia furfur</t>
+          <t>Wnt10b (Wingless-type mouse mammary tumor virus integration site 10b)</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -12793,7 +12793,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>TNF-alpha</t>
+          <t>TGF-β2 (Transforming growth factor beta 2)</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -12815,20 +12815,20 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Hair follicle growth and survival</t>
+          <t>Apoptosis in dermal papilla cells</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C564" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D564" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E564" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F564" t="n">
         <v>2</v>
@@ -12837,7 +12837,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>PDE5 (Phosphodiesterase 5)</t>
+          <t>Malassezia furfur</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -12859,7 +12859,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>PSA (Prostate Specific Antigen)</t>
+          <t>TNF-alpha</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -12881,7 +12881,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Collagenase</t>
+          <t>Hair follicle growth and survival</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -12903,7 +12903,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>IGF-1 (Insulin-like growth factor-1)</t>
+          <t>PDE5 (Phosphodiesterase 5)</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -12925,7 +12925,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>TGF-beta1 (Transforming growth factor-beta1)</t>
+          <t>PSA (Prostate Specific Antigen)</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -12947,7 +12947,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Sonic Hedgehog pathway</t>
+          <t>Collagenase</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -12969,7 +12969,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone synthesis</t>
+          <t>IGF-1 (Insulin-like growth factor-1)</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -12991,7 +12991,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Cortisol production</t>
+          <t>TGF-beta1 (Transforming growth factor-beta1)</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -13013,7 +13013,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>DHT (Dihydrotestosterone) production</t>
+          <t>Sonic Hedgehog pathway</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -13035,20 +13035,20 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Hair growth</t>
+          <t>Dihydrotestosterone synthesis</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C574" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D574" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E574" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F574" t="n">
         <v>2</v>
@@ -13057,7 +13057,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Nrf-2 (Nuclear factor erythroid 2-related factor 2)</t>
+          <t>Cortisol production</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -13079,7 +13079,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Nrf-2</t>
+          <t>DHT (Dihydrotestosterone) production</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -13101,20 +13101,20 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>ROCK (Rho-associated protein kinase)</t>
+          <t>Hair growth</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C577" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D577" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E577" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F577" t="n">
         <v>2</v>
@@ -13123,7 +13123,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Basement membrane proteins</t>
+          <t>Nrf-2 (Nuclear factor erythroid 2-related factor 2)</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -13145,7 +13145,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Placental Growth Factor (PlGF)</t>
+          <t>Nrf-2</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -13167,7 +13167,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Hair matrix cell proliferation</t>
+          <t>ROCK (Rho-associated protein kinase)</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -13189,7 +13189,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Dermal papilla cell interaction</t>
+          <t>Basement membrane proteins</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -13211,7 +13211,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Hair growth factors (IGF</t>
+          <t>Placental Growth Factor (PlGF)</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -13233,7 +13233,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Antioxidant enzymes (HO-1</t>
+          <t>Hair matrix cell proliferation</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -13255,7 +13255,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>NQO-1</t>
+          <t>Dermal papilla cell interaction</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -13277,7 +13277,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>GSTpi)</t>
+          <t>Hair growth factors (IGF</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -13299,7 +13299,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Nrf-2 transcription factor</t>
+          <t>Antioxidant enzymes (HO-1</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -13321,7 +13321,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Hair growth-related genes</t>
+          <t>NQO-1</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -13343,7 +13343,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>DHT (dihydrotestosterone)</t>
+          <t>GSTpi)</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -13365,7 +13365,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>IGF-I (Insulin-like Growth Factor)</t>
+          <t>Nrf-2 transcription factor</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -13387,7 +13387,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>PTEN (Phosphatase and Tensin Homolog)</t>
+          <t>Hair growth-related genes</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -13409,7 +13409,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CRH Receptor 1 (CRHR1)</t>
+          <t>DHT (dihydrotestosterone)</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -13431,7 +13431,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CRH Receptor 2 (CRHR2)</t>
+          <t>IGF-I (Insulin-like Growth Factor)</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -13453,7 +13453,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>PI3K/Akt/mTOR pathway</t>
+          <t>PTEN (Phosphatase and Tensin Homolog)</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -13475,7 +13475,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Hyaluronidase</t>
+          <t>CRH Receptor 1 (CRHR1)</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -13497,7 +13497,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>β-Catenin signaling pathway</t>
+          <t>CRH Receptor 2 (CRHR2)</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -13519,7 +13519,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>TGF-beta</t>
+          <t>PI3K/Akt/mTOR pathway</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -13541,7 +13541,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>5-Alpha-Reductase Type 2 (5AR2)</t>
+          <t>Hyaluronidase</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -13563,7 +13563,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Epithelial-mesenchymal interactions</t>
+          <t>β-Catenin signaling pathway</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -13585,7 +13585,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>IGF-1 (Insulin-like Growth Factor-1)</t>
+          <t>TGF-beta</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -13607,7 +13607,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>TGFβ1 (Transforming Growth Factor Beta 1)</t>
+          <t>5-Alpha-Reductase Type 2 (5AR2)</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -13629,7 +13629,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Cholesterol biosynthesis</t>
+          <t>Epithelial-mesenchymal interactions</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -13651,7 +13651,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>7-DHCR (7-dehydrocholesterol reductase)</t>
+          <t>IGF-1 (Insulin-like Growth Factor-1)</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -13673,7 +13673,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>DHCR24</t>
+          <t>TGFβ1 (Transforming Growth Factor Beta 1)</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -13695,7 +13695,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>5α-reductase enzyme</t>
+          <t>Cholesterol biosynthesis</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -13717,7 +13717,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>PGD2</t>
+          <t>7-DHCR (7-dehydrocholesterol reductase)</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -13739,7 +13739,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>PGE2</t>
+          <t>DHCR24</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -13761,7 +13761,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Insulin-like growth factor-1</t>
+          <t>5α-reductase enzyme</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -13783,7 +13783,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Sebaceous glands</t>
+          <t>PGD2</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -13805,7 +13805,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Protein serine/threonine kinase</t>
+          <t>PGE2</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -13827,7 +13827,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Src protein</t>
+          <t>Insulin-like growth factor-1</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -13849,7 +13849,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Insulin-like growth factor 1 (IGF1)</t>
+          <t>Sebaceous glands</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -13871,7 +13871,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Glycogen synthase kinase-3β</t>
+          <t>Protein serine/threonine kinase</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -13893,7 +13893,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Circulating androgens</t>
+          <t>Src protein</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -13915,7 +13915,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Inflammatory cytokines (IL-1β</t>
+          <t>Insulin-like growth factor 1 (IGF1)</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -13937,7 +13937,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Mesenchymal stem cells (MSCs)</t>
+          <t>Glycogen synthase kinase-3β</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -13959,7 +13959,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Adipose-derived stem cells (ADSCs)</t>
+          <t>Circulating androgens</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -13981,7 +13981,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Scalp muscle tension</t>
+          <t>Inflammatory cytokines (IL-1β</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -14003,7 +14003,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Blood flow regulation</t>
+          <t>Mesenchymal stem cells (MSCs)</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -14025,7 +14025,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>miR-22</t>
+          <t>Adipose-derived stem cells (ADSCs)</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -14047,7 +14047,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>TNF-α signaling pathway</t>
+          <t>Scalp muscle tension</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -14069,7 +14069,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>PIK3CA</t>
+          <t>Blood flow regulation</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -14091,7 +14091,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>PIK3CB</t>
+          <t>miR-22</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -14113,7 +14113,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>HRAS</t>
+          <t>TNF-α signaling pathway</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -14135,7 +14135,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>RHOA</t>
+          <t>PIK3CA</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -14157,7 +14157,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Prostaglandin E2 production</t>
+          <t>PIK3CB</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -14179,7 +14179,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Phytoestrogen pathway</t>
+          <t>HRAS</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -14201,7 +14201,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Indoleamine 2</t>
+          <t>RHOA</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -14223,7 +14223,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>3-dioxygenase (IDO)</t>
+          <t>Prostaglandin E2 production</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -14245,7 +14245,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Histone deacetylase</t>
+          <t>Phytoestrogen pathway</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -14267,7 +14267,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Hair growth cycle</t>
+          <t>Indoleamine 2</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -14289,7 +14289,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>DHT-induced signaling</t>
+          <t>3-dioxygenase (IDO)</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -14311,7 +14311,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>JAK/STAT signaling pathway</t>
+          <t>Histone deacetylase</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -14333,7 +14333,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Inflammatory mediators</t>
+          <t>Hair growth cycle</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -14355,7 +14355,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Cytokines</t>
+          <t>DHT-induced signaling</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -14377,7 +14377,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Purinergic receptors (P2 receptors)</t>
+          <t>JAK/STAT signaling pathway</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -14399,7 +14399,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Circulation promotion</t>
+          <t>Inflammatory mediators</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -14421,7 +14421,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Heat shock protein 70 (HSPA1A/B)</t>
+          <t>Cytokines</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -14443,7 +14443,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>T lymphocytes (CD8+</t>
+          <t>Purinergic receptors (P2 receptors)</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -14465,7 +14465,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>CD4+)</t>
+          <t>Circulation promotion</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -14487,7 +14487,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Natural killer cells</t>
+          <t>Heat shock protein 70 (HSPA1A/B)</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -14509,7 +14509,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Dendritic cells</t>
+          <t>T lymphocytes (CD8+</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -14531,7 +14531,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>IL-12/IL-23 p40 subunit</t>
+          <t>CD4+)</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -14553,7 +14553,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>IL-23 p19 subunit</t>
+          <t>Natural killer cells</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -14575,7 +14575,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Estrogen Receptor Beta</t>
+          <t>Dendritic cells</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -14597,7 +14597,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Prostaglandin D2 Synthase</t>
+          <t>IL-12/IL-23 p40 subunit</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -14619,7 +14619,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Gamma chain cytokines</t>
+          <t>IL-23 p19 subunit</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -14641,7 +14641,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>IFN-gamma signaling</t>
+          <t>Estrogen Receptor Beta</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -14663,7 +14663,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Hair follicle immune privilege</t>
+          <t>Prostaglandin D2 Synthase</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -14685,7 +14685,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>CD3+ T cells</t>
+          <t>Gamma chain cytokines</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -14707,7 +14707,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Antigen presenting cells</t>
+          <t>IFN-gamma signaling</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -14729,7 +14729,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>T helper cells</t>
+          <t>Hair follicle immune privilege</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -14751,7 +14751,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>NF-kB pathway</t>
+          <t>CD3+ T cells</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14773,7 +14773,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Growth Factor Signaling</t>
+          <t>Antigen presenting cells</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -14795,7 +14795,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>VEGFR-2</t>
+          <t>T helper cells</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -14817,7 +14817,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Notch signaling pathway</t>
+          <t>NF-kB pathway</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -14839,7 +14839,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>VCAN (Versican)</t>
+          <t>Growth Factor Signaling</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -14861,7 +14861,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>miR-221-3p</t>
+          <t>VEGFR-2</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -14883,7 +14883,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>JNK</t>
+          <t>Notch signaling pathway</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -14905,7 +14905,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>p38 MAPK</t>
+          <t>VCAN (Versican)</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -14927,7 +14927,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Wnt5A</t>
+          <t>miR-221-3p</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -14949,7 +14949,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Dickkopf-1 (Dkk1)</t>
+          <t>JNK</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -14971,7 +14971,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>TGF-β2/Smad signaling</t>
+          <t>p38 MAPK</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -14993,7 +14993,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Hedgehog signaling</t>
+          <t>Wnt5A</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -15015,20 +15015,20 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Keratin 17</t>
+          <t>Dickkopf-1 (Dkk1)</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C664" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D664" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E664" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F664" t="n">
         <v>2</v>
@@ -15037,20 +15037,20 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Keratin 16</t>
+          <t>TGF-β2/Smad signaling</t>
         </is>
       </c>
       <c r="B665" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C665" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D665" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E665" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F665" t="n">
         <v>2</v>
@@ -15059,20 +15059,20 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Keratin 6</t>
+          <t>Hedgehog signaling</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C666" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D666" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E666" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F666" t="n">
         <v>2</v>
@@ -15081,20 +15081,20 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Malassezia spp.</t>
+          <t>Keratin 17</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C667" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E667" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F667" t="n">
         <v>2</v>
@@ -15103,20 +15103,20 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Staphylococcus spp.</t>
+          <t>Keratin 16</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C668" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D668" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E668" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F668" t="n">
         <v>2</v>
@@ -15125,20 +15125,20 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Scalp microflora</t>
+          <t>Keratin 6</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C669" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D669" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E669" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F669" t="n">
         <v>2</v>
@@ -15147,7 +15147,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Inflammatory pathway</t>
+          <t>Malassezia spp.</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -15169,7 +15169,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>PPARα (Peroxisome Proliferator-Activated Receptor alpha)</t>
+          <t>Staphylococcus spp.</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -15191,7 +15191,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>T effector cells</t>
+          <t>Scalp microflora</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -15213,7 +15213,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>JAK-STAT signaling pathway</t>
+          <t>Inflammatory pathway</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -15235,7 +15235,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>5-alpha Reductase Type 1</t>
+          <t>PPARα (Peroxisome Proliferator-Activated Receptor alpha)</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -15257,7 +15257,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Calcification regulators</t>
+          <t>T effector cells</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -15279,20 +15279,20 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>IFN-γ</t>
+          <t>JAK-STAT signaling pathway</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C676" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E676" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F676" t="n">
         <v>2</v>
@@ -15301,7 +15301,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Testosterone binding protein</t>
+          <t>5-alpha Reductase Type 1</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -15323,7 +15323,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>IFN-γR</t>
+          <t>Calcification regulators</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -15345,20 +15345,20 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Patched2 (Ptc2)</t>
+          <t>IFN-γ</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C679" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D679" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E679" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F679" t="n">
         <v>2</v>
@@ -15367,7 +15367,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Hedgehog signaling pathway</t>
+          <t>Testosterone binding protein</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -15389,7 +15389,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Smoothened (Smo)</t>
+          <t>IFN-γR</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -15411,7 +15411,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Insulin-like Growth Factor-1 (IGF-1)</t>
+          <t>Patched2 (Ptc2)</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -15433,7 +15433,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Osteopontin</t>
+          <t>Hedgehog signaling pathway</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -15455,7 +15455,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Integrin (RGD domain binding)</t>
+          <t>Smoothened (Smo)</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -15477,7 +15477,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>miR-485-3p</t>
+          <t>Insulin-like Growth Factor-1 (IGF-1)</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -15499,7 +15499,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Dermal papilla signals</t>
+          <t>Osteopontin</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -15521,7 +15521,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>PDGFA</t>
+          <t>Integrin (RGD domain binding)</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -15543,7 +15543,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Hair stem cells</t>
+          <t>miR-485-3p</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -15565,7 +15565,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Dipeptidyl Peptidase IV (DPPIV)</t>
+          <t>Dermal papilla signals</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -15587,7 +15587,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DPPIV-Related Protein-1 (DPRP-1)</t>
+          <t>PDGFA</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -15609,7 +15609,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DPPIV-Related Protein-2 (DPRP-2)</t>
+          <t>Hair stem cells</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -15631,7 +15631,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>DPPIV-Related Protein-3 (DPRP-3)</t>
+          <t>Dipeptidyl Peptidase IV (DPPIV)</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -15653,7 +15653,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Serine Protease</t>
+          <t>DPPIV-Related Protein-1 (DPRP-1)</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -15675,7 +15675,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Prolyl Oligopeptidase Family</t>
+          <t>DPPIV-Related Protein-2 (DPRP-2)</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -15697,7 +15697,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Hair follicle growth phase</t>
+          <t>DPPIV-Related Protein-3 (DPRP-3)</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -15719,7 +15719,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>5-α-Reductase Type 1</t>
+          <t>Serine Protease</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -15741,7 +15741,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Sebaceous gland lipogenesis</t>
+          <t>Prolyl Oligopeptidase Family</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -15763,7 +15763,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>CDK5</t>
+          <t>Hair follicle growth phase</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -15785,7 +15785,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Bcl-x(L)</t>
+          <t>5-α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -15807,7 +15807,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Caspase</t>
+          <t>Sebaceous gland lipogenesis</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -15829,7 +15829,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>MYB transcription factor</t>
+          <t>CDK5</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -15851,7 +15851,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>OX40</t>
+          <t>Bcl-x(L)</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -15873,7 +15873,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>γδ T cells</t>
+          <t>Caspase</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -15895,7 +15895,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>IL-17</t>
+          <t>MYB transcription factor</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -15917,20 +15917,20 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Hair follicle cycling</t>
+          <t>OX40</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D705" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E705" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F705" t="n">
         <v>2</v>
@@ -15939,7 +15939,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>PGD2 synthase</t>
+          <t>γδ T cells</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -15961,7 +15961,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>5α-reductase Type II</t>
+          <t>IL-17</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -15983,20 +15983,20 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Luteinizing Hormone (LH)</t>
+          <t>Hair follicle cycling</t>
         </is>
       </c>
       <c r="B708" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C708" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D708" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E708" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F708" t="n">
         <v>2</v>
@@ -16005,7 +16005,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Follicle-Stimulating Hormone (FSH)</t>
+          <t>PGD2 synthase</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -16027,7 +16027,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Hypothalamic-Pituitary-Testicular Axis</t>
+          <t>5α-reductase Type II</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -16049,7 +16049,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Sex Hormone Binding Globulin (SHBG)</t>
+          <t>Luteinizing Hormone (LH)</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -16071,7 +16071,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Platelet-derived growth factor (PDGF)</t>
+          <t>Follicle-Stimulating Hormone (FSH)</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -16093,7 +16093,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Transforming growth factor (TGF)</t>
+          <t>Hypothalamic-Pituitary-Testicular Axis</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -16115,7 +16115,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Growth factor signaling pathways</t>
+          <t>Sex Hormone Binding Globulin (SHBG)</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -16137,7 +16137,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>5-alpha reductase type II</t>
+          <t>Platelet-derived growth factor (PDGF)</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -16159,7 +16159,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>NF-κβ</t>
+          <t>Transforming growth factor (TGF)</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -16181,7 +16181,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Hair follicle inflammation</t>
+          <t>Growth factor signaling pathways</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -16203,7 +16203,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Microbial infection of hair follicles</t>
+          <t>5-alpha reductase type II</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -16225,7 +16225,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DNA Methyltransferase 1 (DNMT1)</t>
+          <t>NF-κβ</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -16247,7 +16247,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Stem cell activation</t>
+          <t>Hair follicle inflammation</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -16269,7 +16269,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>RAGE</t>
+          <t>Microbial infection of hair follicles</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -16291,7 +16291,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>HIF-1α</t>
+          <t>DNA Methyltransferase 1 (DNMT1)</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -16313,7 +16313,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>MAPK</t>
+          <t>Stem cell activation</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -16335,7 +16335,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>CREB</t>
+          <t>RAGE</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -16357,7 +16357,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Lactobacillus</t>
+          <t>HIF-1α</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -16379,7 +16379,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Biotin availability</t>
+          <t>MAPK</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -16401,7 +16401,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Blood flow to scalp</t>
+          <t>CREB</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -16423,7 +16423,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Hypothalamic-pituitary-adrenal (HPA) axis</t>
+          <t>Lactobacillus</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -16445,7 +16445,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>T helper cells (Th1/Th2)</t>
+          <t>Biotin availability</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -16467,7 +16467,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>T helper 17 cells (Th17)</t>
+          <t>Blood flow to scalp</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -16489,7 +16489,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Regulatory T cells (Treg)</t>
+          <t>Hypothalamic-pituitary-adrenal (HPA) axis</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -16511,7 +16511,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Corticotropin-releasing hormone (CRH)</t>
+          <t>T helper cells (Th1/Th2)</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -16533,7 +16533,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Adrenocorticotropic hormone (ACTH)</t>
+          <t>T helper 17 cells (Th17)</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -16555,7 +16555,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>P450 aromatase</t>
+          <t>Regulatory T cells (Treg)</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -16577,7 +16577,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>TMPRSS2</t>
+          <t>Corticotropin-releasing hormone (CRH)</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -16599,7 +16599,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>ACE-2</t>
+          <t>Adrenocorticotropic hormone (ACTH)</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -16621,7 +16621,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Growth factors (TGF-β</t>
+          <t>P450 aromatase</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -16643,7 +16643,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>IGF)</t>
+          <t>TMPRSS2</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -16665,7 +16665,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Cytokines (IL-3</t>
+          <t>ACE-2</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -16687,7 +16687,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>IL-8)</t>
+          <t>Growth factors (TGF-β</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -16709,7 +16709,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>SOCS3 (Suppressor of Cytokine Signaling-3)</t>
+          <t>IGF)</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -16731,7 +16731,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Fas</t>
+          <t>Cytokines (IL-3</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -16753,7 +16753,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>MHC I</t>
+          <t>IL-8)</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -16775,7 +16775,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>5-alpha-reductase Type 1</t>
+          <t>SOCS3 (Suppressor of Cytokine Signaling-3)</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -16797,7 +16797,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>5-alpha-reductase Type 2</t>
+          <t>Fas</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -16819,7 +16819,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>Ferroptosis pathway</t>
+          <t>MHC I</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -16841,7 +16841,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>Antioxidant system</t>
+          <t>5-alpha-reductase Type 1</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -16863,7 +16863,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>Secretory phospholipase A2 Group-IIA (sPLA2-IIA)</t>
+          <t>5-alpha-reductase Type 2</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -16885,7 +16885,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>EGFR signaling</t>
+          <t>Ferroptosis pathway</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -16907,7 +16907,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Shh signaling</t>
+          <t>Antioxidant system</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -16929,7 +16929,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>Regulatory T cells (Tregs)</t>
+          <t>Secretory phospholipase A2 Group-IIA (sPLA2-IIA)</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -16951,7 +16951,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>IL-2 signaling</t>
+          <t>EGFR signaling</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -16973,7 +16973,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>NKG2D-expressing CD8 T cells</t>
+          <t>Shh signaling</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -16995,7 +16995,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>JAK/STAT signaling</t>
+          <t>Regulatory T cells (Tregs)</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -17017,7 +17017,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>Mechanotransduction</t>
+          <t>IL-2 signaling</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -17039,7 +17039,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>DHT (Dihydrotestosterone)</t>
+          <t>NKG2D-expressing CD8 T cells</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -17061,7 +17061,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>Angiogenesis/Neovascularization</t>
+          <t>JAK/STAT signaling</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -17083,7 +17083,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>Testosterone 5-Alpha Reductase</t>
+          <t>Mechanotransduction</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -17105,7 +17105,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>IGF-1 Receptor</t>
+          <t>DHT (Dihydrotestosterone)</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -17127,7 +17127,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>Lactotroph cells</t>
+          <t>Angiogenesis/Neovascularization</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -17149,7 +17149,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>Hypothalamic-pituitary-gonadal axis</t>
+          <t>Testosterone 5-Alpha Reductase</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -17171,7 +17171,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>IGF (Insulin-like Growth Factor)</t>
+          <t>IGF-1 Receptor</t>
         </is>
       </c>
       <c r="B762" t="n">
@@ -17193,7 +17193,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>Oxidative stress markers</t>
+          <t>Lactotroph cells</t>
         </is>
       </c>
       <c r="B763" t="n">
@@ -17215,7 +17215,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>Malondialdehyde (MDA)</t>
+          <t>Hypothalamic-pituitary-gonadal axis</t>
         </is>
       </c>
       <c r="B764" t="n">
@@ -17237,7 +17237,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>Ceruloplasmin (CER)</t>
+          <t>IGF (Insulin-like Growth Factor)</t>
         </is>
       </c>
       <c r="B765" t="n">
@@ -17259,7 +17259,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>Paraoxonase 1 (PON1)</t>
+          <t>Oxidative stress markers</t>
         </is>
       </c>
       <c r="B766" t="n">
@@ -17281,7 +17281,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>NRF2</t>
+          <t>Malondialdehyde (MDA)</t>
         </is>
       </c>
       <c r="B767" t="n">
@@ -17303,7 +17303,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>IκBζ-ATF3 axis</t>
+          <t>Ceruloplasmin (CER)</t>
         </is>
       </c>
       <c r="B768" t="n">
@@ -17325,7 +17325,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>JAK-STAT signaling</t>
+          <t>Paraoxonase 1 (PON1)</t>
         </is>
       </c>
       <c r="B769" t="n">
@@ -17347,7 +17347,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>Albumin (plasma protein binding)</t>
+          <t>NRF2</t>
         </is>
       </c>
       <c r="B770" t="n">
@@ -17369,7 +17369,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>Macrophage polarization</t>
+          <t>IκBζ-ATF3 axis</t>
         </is>
       </c>
       <c r="B771" t="n">
@@ -17391,7 +17391,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>Dermal papilla cell apoptosis</t>
+          <t>JAK-STAT signaling</t>
         </is>
       </c>
       <c r="B772" t="n">
@@ -17413,7 +17413,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>Mesenchymal stem cells (umbilical cord-derived)</t>
+          <t>Albumin (plasma protein binding)</t>
         </is>
       </c>
       <c r="B773" t="n">
@@ -17435,20 +17435,20 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>Androgen biosynthesis pathway</t>
+          <t>Macrophage polarization</t>
         </is>
       </c>
       <c r="B774" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C774" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D774" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E774" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F774" t="n">
         <v>2</v>
@@ -17457,7 +17457,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>11b-Hydroxylase</t>
+          <t>Dermal papilla cell apoptosis</t>
         </is>
       </c>
       <c r="B775" t="n">
@@ -17479,7 +17479,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>Scalp perimeter muscles</t>
+          <t>Mesenchymal stem cells (umbilical cord-derived)</t>
         </is>
       </c>
       <c r="B776" t="n">
@@ -17501,20 +17501,20 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>Whn/Foxn1 transcription factor</t>
+          <t>Androgen biosynthesis pathway</t>
         </is>
       </c>
       <c r="B777" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C777" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D777" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E777" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F777" t="n">
         <v>2</v>
@@ -17523,7 +17523,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>Keratin genes</t>
+          <t>11b-Hydroxylase</t>
         </is>
       </c>
       <c r="B778" t="n">
@@ -17545,7 +17545,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>Vitamin D Receptor</t>
+          <t>Scalp perimeter muscles</t>
         </is>
       </c>
       <c r="B779" t="n">
@@ -17567,7 +17567,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>Hair follicle keratinocytes</t>
+          <t>Whn/Foxn1 transcription factor</t>
         </is>
       </c>
       <c r="B780" t="n">
@@ -17589,7 +17589,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>Keratin 81 (Krt81)</t>
+          <t>Keratin genes</t>
         </is>
       </c>
       <c r="B781" t="n">
@@ -17611,7 +17611,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>Keratin 34 (Krt34)</t>
+          <t>Vitamin D Receptor</t>
         </is>
       </c>
       <c r="B782" t="n">
@@ -17633,7 +17633,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>Keratin 33a (Krt33a)</t>
+          <t>Hair follicle keratinocytes</t>
         </is>
       </c>
       <c r="B783" t="n">
@@ -17655,7 +17655,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>Sma and MAD-related protein 3 (Smad3)</t>
+          <t>Keratin 81 (Krt81)</t>
         </is>
       </c>
       <c r="B784" t="n">
@@ -17677,7 +17677,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>Keratins (Krt81</t>
+          <t>Keratin 34 (Krt34)</t>
         </is>
       </c>
       <c r="B785" t="n">
@@ -17699,7 +17699,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>Krt34</t>
+          <t>Keratin 33a (Krt33a)</t>
         </is>
       </c>
       <c r="B786" t="n">
@@ -17721,7 +17721,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>Krt33a)</t>
+          <t>Sma and MAD-related protein 3 (Smad3)</t>
         </is>
       </c>
       <c r="B787" t="n">
@@ -17743,7 +17743,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>TGF-β/Smad3 pathway</t>
+          <t>Keratins (Krt81</t>
         </is>
       </c>
       <c r="B788" t="n">
@@ -17765,7 +17765,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>Smad3</t>
+          <t>Krt34</t>
         </is>
       </c>
       <c r="B789" t="n">
@@ -17787,7 +17787,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>miR-133b</t>
+          <t>Krt33a)</t>
         </is>
       </c>
       <c r="B790" t="n">
@@ -17809,7 +17809,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Msx2</t>
+          <t>TGF-β/Smad3 pathway</t>
         </is>
       </c>
       <c r="B791" t="n">
@@ -17831,7 +17831,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>Foxn1</t>
+          <t>Smad3</t>
         </is>
       </c>
       <c r="B792" t="n">
@@ -17853,7 +17853,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>Ha3</t>
+          <t>miR-133b</t>
         </is>
       </c>
       <c r="B793" t="n">
@@ -17875,7 +17875,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>Lef1</t>
+          <t>Msx2</t>
         </is>
       </c>
       <c r="B794" t="n">
@@ -17897,7 +17897,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Dermal papilla paracrine factors</t>
+          <t>Foxn1</t>
         </is>
       </c>
       <c r="B795" t="n">
@@ -17919,7 +17919,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Mitogenic factors for dermal papilla cells</t>
+          <t>Ha3</t>
         </is>
       </c>
       <c r="B796" t="n">
@@ -17941,7 +17941,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Bcl-2/Bax</t>
+          <t>Lef1</t>
         </is>
       </c>
       <c r="B797" t="n">
@@ -17963,7 +17963,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Melanocyte function</t>
+          <t>Dermal papilla paracrine factors</t>
         </is>
       </c>
       <c r="B798" t="n">
@@ -17985,7 +17985,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Hair follicle aging</t>
+          <t>Mitogenic factors for dermal papilla cells</t>
         </is>
       </c>
       <c r="B799" t="n">
@@ -18007,7 +18007,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Erk signaling</t>
+          <t>Bcl-2/Bax</t>
         </is>
       </c>
       <c r="B800" t="n">
@@ -18029,7 +18029,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Minoxidil target (KATP channel opener)</t>
+          <t>Melanocyte function</t>
         </is>
       </c>
       <c r="B801" t="n">
@@ -18051,7 +18051,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>Hair follicle growth stimulation</t>
+          <t>Hair follicle aging</t>
         </is>
       </c>
       <c r="B802" t="n">
@@ -18073,7 +18073,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>Wnt signaling components</t>
+          <t>Erk signaling</t>
         </is>
       </c>
       <c r="B803" t="n">
@@ -18095,7 +18095,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>GABA receptors</t>
+          <t>Minoxidil target (KATP channel opener)</t>
         </is>
       </c>
       <c r="B804" t="n">
@@ -18117,7 +18117,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>NMDA receptors</t>
+          <t>Hair follicle growth stimulation</t>
         </is>
       </c>
       <c r="B805" t="n">
@@ -18139,7 +18139,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>KATP channel</t>
+          <t>Wnt signaling components</t>
         </is>
       </c>
       <c r="B806" t="n">
@@ -18161,7 +18161,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor signaling</t>
+          <t>GABA receptors</t>
         </is>
       </c>
       <c r="B807" t="n">
@@ -18183,7 +18183,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>Dermal papilla stem cells</t>
+          <t>NMDA receptors</t>
         </is>
       </c>
       <c r="B808" t="n">
@@ -18205,7 +18205,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>Growth factors</t>
+          <t>KATP channel</t>
         </is>
       </c>
       <c r="B809" t="n">
@@ -18227,7 +18227,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor</t>
+          <t>Vascular endothelial growth factor signaling</t>
         </is>
       </c>
       <c r="B810" t="n">
@@ -18249,7 +18249,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth factor (VEGF) pathway</t>
+          <t>Dermal papilla stem cells</t>
         </is>
       </c>
       <c r="B811" t="n">
@@ -18271,7 +18271,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>Hic-5</t>
+          <t>Growth factors</t>
         </is>
       </c>
       <c r="B812" t="n">
@@ -18293,7 +18293,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>Hair growth stimulation</t>
+          <t>Vascular endothelial growth factor</t>
         </is>
       </c>
       <c r="B813" t="n">
@@ -18315,7 +18315,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>Anagen phase induction</t>
+          <t>Vascular endothelial growth factor (VEGF) pathway</t>
         </is>
       </c>
       <c r="B814" t="n">
@@ -18337,7 +18337,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>Microinflammation pathways</t>
+          <t>Hic-5</t>
         </is>
       </c>
       <c r="B815" t="n">
@@ -18359,20 +18359,20 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>Phosphodiesterase</t>
+          <t>Hair growth stimulation</t>
         </is>
       </c>
       <c r="B816" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C816" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D816" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E816" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F816" t="n">
         <v>2</v>
@@ -18381,7 +18381,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>Sulfotransferase</t>
+          <t>Anagen phase induction</t>
         </is>
       </c>
       <c r="B817" t="n">
@@ -18403,7 +18403,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>Minoxidil metabolism</t>
+          <t>Microinflammation pathways</t>
         </is>
       </c>
       <c r="B818" t="n">
@@ -18425,20 +18425,20 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>Nitric Oxide (NO) production</t>
+          <t>Phosphodiesterase</t>
         </is>
       </c>
       <c r="B819" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C819" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D819" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E819" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F819" t="n">
         <v>2</v>
@@ -18447,7 +18447,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>Reactive Oxygen Species (ROS) modulation</t>
+          <t>Sulfotransferase</t>
         </is>
       </c>
       <c r="B820" t="n">
@@ -18469,7 +18469,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>Redox-related signaling pathways</t>
+          <t>Minoxidil metabolism</t>
         </is>
       </c>
       <c r="B821" t="n">
@@ -18491,7 +18491,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>Vascular endothelial growth</t>
+          <t>Nitric Oxide (NO) production</t>
         </is>
       </c>
       <c r="B822" t="n">
@@ -18513,7 +18513,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>TGF-beta pathway</t>
+          <t>Reactive Oxygen Species (ROS) modulation</t>
         </is>
       </c>
       <c r="B823" t="n">
@@ -18535,7 +18535,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Prostaglandin signaling</t>
+          <t>Redox-related signaling pathways</t>
         </is>
       </c>
       <c r="B824" t="n">
@@ -18557,7 +18557,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>VEGF receptor</t>
+          <t>Vascular endothelial growth</t>
         </is>
       </c>
       <c r="B825" t="n">
@@ -18579,7 +18579,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>Potassium channel</t>
+          <t>TGF-beta pathway</t>
         </is>
       </c>
       <c r="B826" t="n">
@@ -18601,7 +18601,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>Glucocorticoid Receptor (GR)</t>
+          <t>Prostaglandin signaling</t>
         </is>
       </c>
       <c r="B827" t="n">
@@ -18623,7 +18623,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>Aldosterone Receptor</t>
+          <t>VEGF receptor</t>
         </is>
       </c>
       <c r="B828" t="n">
@@ -18645,7 +18645,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>CB1 receptor</t>
+          <t>Potassium channel</t>
         </is>
       </c>
       <c r="B829" t="n">
@@ -18667,7 +18667,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>TRPV1</t>
+          <t>Glucocorticoid Receptor (GR)</t>
         </is>
       </c>
       <c r="B830" t="n">
@@ -18689,7 +18689,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>TRPV4</t>
+          <t>Aldosterone Receptor</t>
         </is>
       </c>
       <c r="B831" t="n">
@@ -18711,7 +18711,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>Fibroblast Growth Factor 9 (FGF9)</t>
+          <t>CB1 receptor</t>
         </is>
       </c>
       <c r="B832" t="n">
@@ -18733,7 +18733,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>HOXB13</t>
+          <t>TRPV1</t>
         </is>
       </c>
       <c r="B833" t="n">
@@ -18755,7 +18755,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>PTGDS</t>
+          <t>TRPV4</t>
         </is>
       </c>
       <c r="B834" t="n">
@@ -18777,7 +18777,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>SFRP4</t>
+          <t>Fibroblast Growth Factor 9 (FGF9)</t>
         </is>
       </c>
       <c r="B835" t="n">
@@ -18799,7 +18799,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>SOD3</t>
+          <t>HOXB13</t>
         </is>
       </c>
       <c r="B836" t="n">
@@ -18821,7 +18821,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>DCN</t>
+          <t>PTGDS</t>
         </is>
       </c>
       <c r="B837" t="n">
@@ -18843,7 +18843,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Apoptosis pathways</t>
+          <t>SFRP4</t>
         </is>
       </c>
       <c r="B838" t="n">
@@ -18865,7 +18865,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Hair follicle dermal papilla</t>
+          <t>SOD3</t>
         </is>
       </c>
       <c r="B839" t="n">
@@ -18887,7 +18887,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Hair growth factors</t>
+          <t>DCN</t>
         </is>
       </c>
       <c r="B840" t="n">
@@ -18909,7 +18909,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Wnt/β-Catenin signaling</t>
+          <t>Apoptosis pathways</t>
         </is>
       </c>
       <c r="B841" t="n">
@@ -18931,7 +18931,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Transforming Growth Factor signaling</t>
+          <t>Hair follicle dermal papilla</t>
         </is>
       </c>
       <c r="B842" t="n">
@@ -18953,7 +18953,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Prostaglandin F (FP) receptor</t>
+          <t>Hair growth factors</t>
         </is>
       </c>
       <c r="B843" t="n">
@@ -18975,7 +18975,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Hair growth cycle regulation</t>
+          <t>Wnt/β-Catenin signaling</t>
         </is>
       </c>
       <c r="B844" t="n">
@@ -18997,7 +18997,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Glucocorticoid Receptor</t>
+          <t>Transforming Growth Factor signaling</t>
         </is>
       </c>
       <c r="B845" t="n">
@@ -19019,7 +19019,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Potassium channels (KATP)</t>
+          <t>Prostaglandin F (FP) receptor</t>
         </is>
       </c>
       <c r="B846" t="n">
@@ -19041,7 +19041,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>Cell migration</t>
+          <t>Hair growth cycle regulation</t>
         </is>
       </c>
       <c r="B847" t="n">
@@ -19063,7 +19063,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>Growth signaling pathways</t>
+          <t>Glucocorticoid Receptor</t>
         </is>
       </c>
       <c r="B848" t="n">
@@ -19085,7 +19085,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>Sulfotransferase enzyme</t>
+          <t>Potassium channels (KATP)</t>
         </is>
       </c>
       <c r="B849" t="n">
@@ -19107,7 +19107,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>Hair follicle potassium channels</t>
+          <t>Cell migration</t>
         </is>
       </c>
       <c r="B850" t="n">
@@ -19129,7 +19129,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>H1 histamine receptor</t>
+          <t>Growth signaling pathways</t>
         </is>
       </c>
       <c r="B851" t="n">
@@ -19151,7 +19151,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>SPRY1</t>
+          <t>Sulfotransferase enzyme</t>
         </is>
       </c>
       <c r="B852" t="n">
@@ -19173,7 +19173,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>NRP2</t>
+          <t>Hair follicle potassium channels</t>
         </is>
       </c>
       <c r="B853" t="n">
@@ -19195,7 +19195,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>Finasteride response pathway</t>
+          <t>H1 histamine receptor</t>
         </is>
       </c>
       <c r="B854" t="n">
@@ -19217,7 +19217,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>Follicular stem cells</t>
+          <t>SPRY1</t>
         </is>
       </c>
       <c r="B855" t="n">
@@ -19239,7 +19239,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>Nrf2</t>
+          <t>NRP2</t>
         </is>
       </c>
       <c r="B856" t="n">
@@ -19261,7 +19261,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>TGFβ1</t>
+          <t>Finasteride response pathway</t>
         </is>
       </c>
       <c r="B857" t="n">
@@ -19283,7 +19283,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>Fungal targets</t>
+          <t>Follicular stem cells</t>
         </is>
       </c>
       <c r="B858" t="n">
@@ -19305,7 +19305,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>Androgen-mediated pathways</t>
+          <t>Nrf2</t>
         </is>
       </c>
       <c r="B859" t="n">
@@ -19327,7 +19327,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>Skin microbiome</t>
+          <t>TGFβ1</t>
         </is>
       </c>
       <c r="B860" t="n">
@@ -19349,7 +19349,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Malassezia species</t>
+          <t>Fungal targets</t>
         </is>
       </c>
       <c r="B861" t="n">
@@ -19371,7 +19371,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Androgen-mediated pathways</t>
         </is>
       </c>
       <c r="B862" t="n">
@@ -19393,7 +19393,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Cutibacterium</t>
+          <t>Skin microbiome</t>
         </is>
       </c>
       <c r="B863" t="n">
@@ -19415,7 +19415,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Corynebacterium</t>
+          <t>Malassezia species</t>
         </is>
       </c>
       <c r="B864" t="n">
@@ -19437,7 +19437,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Nitric oxide pathway</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B865" t="n">
@@ -19459,7 +19459,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Vascular growth factors</t>
+          <t>Cutibacterium</t>
         </is>
       </c>
       <c r="B866" t="n">
@@ -19481,7 +19481,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Oxidative stress-related genes</t>
+          <t>Corynebacterium</t>
         </is>
       </c>
       <c r="B867" t="n">
@@ -19503,7 +19503,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Expression quantitative trait loci (eQTL) genes</t>
+          <t>Nitric oxide pathway</t>
         </is>
       </c>
       <c r="B868" t="n">
@@ -19525,7 +19525,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Protein quantitative trait loci (pQTL) genes</t>
+          <t>Vascular growth factors</t>
         </is>
       </c>
       <c r="B869" t="n">
@@ -19547,7 +19547,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Potassium channel (KATP)</t>
+          <t>Oxidative stress-related genes</t>
         </is>
       </c>
       <c r="B870" t="n">
@@ -19569,7 +19569,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>Mitochondrial cytochrome c oxidase</t>
+          <t>Expression quantitative trait loci (eQTL) genes</t>
         </is>
       </c>
       <c r="B871" t="n">
@@ -19591,7 +19591,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>T cell apoptosis pathway</t>
+          <t>Protein quantitative trait loci (pQTL) genes</t>
         </is>
       </c>
       <c r="B872" t="n">
@@ -19613,7 +19613,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>Hair follicle angiogenesis</t>
+          <t>Potassium channel (KATP)</t>
         </is>
       </c>
       <c r="B873" t="n">
@@ -19635,7 +19635,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Protein phosphatase 2A</t>
+          <t>Mitochondrial cytochrome c oxidase</t>
         </is>
       </c>
       <c r="B874" t="n">
@@ -19657,7 +19657,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>T cell apoptosis pathway</t>
         </is>
       </c>
       <c r="B875" t="n">
@@ -19679,7 +19679,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>MAPK8</t>
+          <t>Hair follicle angiogenesis</t>
         </is>
       </c>
       <c r="B876" t="n">
@@ -19701,7 +19701,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>MMP13</t>
+          <t>Protein phosphatase 2A</t>
         </is>
       </c>
       <c r="B877" t="n">
@@ -19723,7 +19723,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>AURKB</t>
+          <t>BCL2</t>
         </is>
       </c>
       <c r="B878" t="n">
@@ -19745,7 +19745,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>Nitric Oxide pathway</t>
+          <t>MAPK8</t>
         </is>
       </c>
       <c r="B879" t="n">
@@ -19767,7 +19767,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>Hair follicle growth phase regulation</t>
+          <t>MMP13</t>
         </is>
       </c>
       <c r="B880" t="n">
@@ -19789,7 +19789,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>Anagen phase promotion</t>
+          <t>AURKB</t>
         </is>
       </c>
       <c r="B881" t="n">
@@ -19811,7 +19811,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>IL-1β</t>
+          <t>Nitric Oxide pathway</t>
         </is>
       </c>
       <c r="B882" t="n">
@@ -19833,7 +19833,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>VEGF-A</t>
+          <t>Hair follicle growth phase regulation</t>
         </is>
       </c>
       <c r="B883" t="n">
@@ -19855,7 +19855,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>Hair cycle regulation</t>
+          <t>Anagen phase promotion</t>
         </is>
       </c>
       <c r="B884" t="n">
@@ -19877,7 +19877,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>Cell subpopulations in hair follicle</t>
+          <t>IL-1β</t>
         </is>
       </c>
       <c r="B885" t="n">
@@ -19899,7 +19899,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>Follicular miniaturization</t>
+          <t>VEGF-A</t>
         </is>
       </c>
       <c r="B886" t="n">
@@ -19921,7 +19921,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>Microinflammation</t>
+          <t>Hair cycle regulation</t>
         </is>
       </c>
       <c r="B887" t="n">
@@ -19943,7 +19943,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>Hair follicle papilla cells</t>
+          <t>Cell subpopulations in hair follicle</t>
         </is>
       </c>
       <c r="B888" t="n">
@@ -19965,7 +19965,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>Androgenetic alopecia pathway</t>
+          <t>Follicular miniaturization</t>
         </is>
       </c>
       <c r="B889" t="n">
@@ -19987,124 +19987,124 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>Estrogen Receptor Beta (ER-β)</t>
+          <t>Microinflammation</t>
         </is>
       </c>
       <c r="B890" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C890" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="D890" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E890" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F890" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>Estrogen Receptor Alpha (ER-α)</t>
+          <t>Hair follicle papilla cells</t>
         </is>
       </c>
       <c r="B891" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C891" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="D891" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E891" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F891" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>Testosterone production</t>
+          <t>Androgenetic alopecia pathway</t>
         </is>
       </c>
       <c r="B892" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C892" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D892" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E892" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F892" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>BRD4</t>
+          <t>Acidic Fibroblast Growth Factor (aFGF)</t>
         </is>
       </c>
       <c r="B893" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C893" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D893" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E893" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F893" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>Nuclear Receptors</t>
+          <t>Hair follicle regeneration pathway</t>
         </is>
       </c>
       <c r="B894" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C894" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D894" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E894" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F894" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>CD8+ T lymphocytes</t>
+          <t>TLR2</t>
         </is>
       </c>
       <c r="B895" t="n">
         <v>1</v>
       </c>
       <c r="C895" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D895" t="n">
         <v>1</v>
@@ -20113,20 +20113,20 @@
         <v>0.5</v>
       </c>
       <c r="F895" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>Class I MHC</t>
+          <t>NLRP3</t>
         </is>
       </c>
       <c r="B896" t="n">
         <v>1</v>
       </c>
       <c r="C896" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D896" t="n">
         <v>1</v>
@@ -20135,20 +20135,20 @@
         <v>0.5</v>
       </c>
       <c r="F896" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>11-beta-hydroxysteroid dehydrogenase</t>
+          <t>Innate immune pathways</t>
         </is>
       </c>
       <c r="B897" t="n">
         <v>1</v>
       </c>
       <c r="C897" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D897" t="n">
         <v>1</v>
@@ -20157,123 +20157,123 @@
         <v>0.5</v>
       </c>
       <c r="F897" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>Hair follicle apoptosis</t>
+          <t>Estrogen Receptor Beta (ER-β)</t>
         </is>
       </c>
       <c r="B898" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C898" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="D898" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E898" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F898" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>c-Kit</t>
+          <t>Estrogen Receptor Alpha (ER-α)</t>
         </is>
       </c>
       <c r="B899" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C899" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="D899" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E899" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F899" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>IL-10</t>
+          <t>Testosterone production</t>
         </is>
       </c>
       <c r="B900" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C900" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D900" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E900" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F900" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>mK6irs1 (Keratin Type II)</t>
+          <t>BRD4</t>
         </is>
       </c>
       <c r="B901" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C901" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D901" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E901" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F901" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>Intermediate filament proteins</t>
+          <t>Nuclear Receptors</t>
         </is>
       </c>
       <c r="B902" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C902" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D902" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E902" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F902" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>Phospholipase C Delta 1 (PLCD1)</t>
+          <t>CD8+ T lymphocytes</t>
         </is>
       </c>
       <c r="B903" t="n">
@@ -20295,7 +20295,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Phospholipase C Delta 3 (PLCD3)</t>
+          <t>Class I MHC</t>
         </is>
       </c>
       <c r="B904" t="n">
@@ -20317,7 +20317,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>Stearoyl CoA desaturase-1 (Scd1)</t>
+          <t>11-beta-hydroxysteroid dehydrogenase</t>
         </is>
       </c>
       <c r="B905" t="n">
@@ -20339,7 +20339,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>Sebaceous gland function</t>
+          <t>Hair follicle apoptosis</t>
         </is>
       </c>
       <c r="B906" t="n">
@@ -20361,7 +20361,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>FKBP12</t>
+          <t>c-Kit</t>
         </is>
       </c>
       <c r="B907" t="n">
@@ -20383,7 +20383,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>Immunophilins</t>
+          <t>IL-10</t>
         </is>
       </c>
       <c r="B908" t="n">
@@ -20405,7 +20405,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>Calcineurin</t>
+          <t>mK6irs1 (Keratin Type II)</t>
         </is>
       </c>
       <c r="B909" t="n">
@@ -20427,7 +20427,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>CDK4/6</t>
+          <t>Intermediate filament proteins</t>
         </is>
       </c>
       <c r="B910" t="n">
@@ -20449,7 +20449,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>Microtubules</t>
+          <t>Phospholipase C Delta 1 (PLCD1)</t>
         </is>
       </c>
       <c r="B911" t="n">
@@ -20471,7 +20471,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>Androgen receptor (indirect)</t>
+          <t>Phospholipase C Delta 3 (PLCD3)</t>
         </is>
       </c>
       <c r="B912" t="n">
@@ -20493,7 +20493,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Pilosebaceous unit (털피지샘 단위)</t>
+          <t>Stearoyl CoA desaturase-1 (Scd1)</t>
         </is>
       </c>
       <c r="B913" t="n">
@@ -20515,7 +20515,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Hair follicle (모낭)</t>
+          <t>Sebaceous gland function</t>
         </is>
       </c>
       <c r="B914" t="n">
@@ -20537,7 +20537,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>Dermal delivery</t>
+          <t>FKBP12</t>
         </is>
       </c>
       <c r="B915" t="n">
@@ -20559,7 +20559,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>HMG-CoA reductase</t>
+          <t>Immunophilins</t>
         </is>
       </c>
       <c r="B916" t="n">
@@ -20581,20 +20581,20 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>3α-Hydroxysteroid Dehydrogenase</t>
+          <t>Calcineurin</t>
         </is>
       </c>
       <c r="B917" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C917" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D917" t="n">
         <v>1</v>
       </c>
       <c r="E917" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F917" t="n">
         <v>1.5</v>
@@ -20603,7 +20603,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Collagen synthesis</t>
+          <t>CDK4/6</t>
         </is>
       </c>
       <c r="B918" t="n">
@@ -20625,7 +20625,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Human dermal papilla cells</t>
+          <t>Microtubules</t>
         </is>
       </c>
       <c r="B919" t="n">
@@ -20647,7 +20647,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Hair follicle differentiation</t>
+          <t>Androgen receptor (indirect)</t>
         </is>
       </c>
       <c r="B920" t="n">
@@ -20669,7 +20669,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>T-box21 (Tbx21/T-bet)</t>
+          <t>Pilosebaceous unit (털피지샘 단위)</t>
         </is>
       </c>
       <c r="B921" t="n">
@@ -20691,7 +20691,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Interferon-gamma (Ifng)</t>
+          <t>Hair follicle (모낭)</t>
         </is>
       </c>
       <c r="B922" t="n">
@@ -20713,7 +20713,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>CCR5</t>
+          <t>Dermal delivery</t>
         </is>
       </c>
       <c r="B923" t="n">
@@ -20735,7 +20735,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>p38 MAP kinase</t>
+          <t>HMG-CoA reductase</t>
         </is>
       </c>
       <c r="B924" t="n">
@@ -20757,20 +20757,20 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>MK2</t>
+          <t>3α-Hydroxysteroid Dehydrogenase</t>
         </is>
       </c>
       <c r="B925" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C925" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D925" t="n">
         <v>1</v>
       </c>
       <c r="E925" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F925" t="n">
         <v>1.5</v>
@@ -20779,7 +20779,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>PRAK</t>
+          <t>Collagen synthesis</t>
         </is>
       </c>
       <c r="B926" t="n">
@@ -20801,7 +20801,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>HIF-P4H-2 (Hypoxia-inducible factor prolyl 4-hydroxylase 2)</t>
+          <t>Human dermal papilla cells</t>
         </is>
       </c>
       <c r="B927" t="n">
@@ -20823,7 +20823,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>HIF1α</t>
+          <t>Hair follicle differentiation</t>
         </is>
       </c>
       <c r="B928" t="n">
@@ -20845,7 +20845,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>HIF2α</t>
+          <t>T-box21 (Tbx21/T-bet)</t>
         </is>
       </c>
       <c r="B929" t="n">
@@ -20867,7 +20867,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Glutathione synthesis</t>
+          <t>Interferon-gamma (Ifng)</t>
         </is>
       </c>
       <c r="B930" t="n">
@@ -20889,7 +20889,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Superoxide dismutase (SOD)</t>
+          <t>CCR5</t>
         </is>
       </c>
       <c r="B931" t="n">
@@ -20911,7 +20911,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>ki67</t>
+          <t>p38 MAP kinase</t>
         </is>
       </c>
       <c r="B932" t="n">
@@ -20933,7 +20933,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Ki-67</t>
+          <t>MK2</t>
         </is>
       </c>
       <c r="B933" t="n">
@@ -20955,20 +20955,20 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>CD4+ T cells</t>
+          <t>PRAK</t>
         </is>
       </c>
       <c r="B934" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C934" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D934" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E934" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F934" t="n">
         <v>1.5</v>
@@ -20977,7 +20977,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>AR N-terminal domain (AR NTD)</t>
+          <t>HIF-P4H-2 (Hypoxia-inducible factor prolyl 4-hydroxylase 2)</t>
         </is>
       </c>
       <c r="B935" t="n">
@@ -20999,7 +20999,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>PPARγ (Peroxisome Proliferator-Activated Receptor gamma)</t>
+          <t>HIF1α</t>
         </is>
       </c>
       <c r="B936" t="n">
@@ -21021,7 +21021,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Peroxisome biogenesis</t>
+          <t>HIF2α</t>
         </is>
       </c>
       <c r="B937" t="n">
@@ -21043,7 +21043,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Inflammatory cytokines (TNF-α</t>
+          <t>Glutathione synthesis</t>
         </is>
       </c>
       <c r="B938" t="n">
@@ -21065,7 +21065,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>MHC class I</t>
+          <t>Superoxide dismutase (SOD)</t>
         </is>
       </c>
       <c r="B939" t="n">
@@ -21087,7 +21087,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 1</t>
+          <t>ki67</t>
         </is>
       </c>
       <c r="B940" t="n">
@@ -21109,7 +21109,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>SDF-1/CXCR4 signaling axis</t>
+          <t>Ki-67</t>
         </is>
       </c>
       <c r="B941" t="n">
@@ -21131,20 +21131,20 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>PI3K/Akt pathway</t>
+          <t>CD4+ T cells</t>
         </is>
       </c>
       <c r="B942" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C942" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D942" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E942" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F942" t="n">
         <v>1.5</v>
@@ -21153,7 +21153,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Dopamine D2 receptor</t>
+          <t>AR N-terminal domain (AR NTD)</t>
         </is>
       </c>
       <c r="B943" t="n">
@@ -21175,7 +21175,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>BECN1</t>
+          <t>PPARγ (Peroxisome Proliferator-Activated Receptor gamma)</t>
         </is>
       </c>
       <c r="B944" t="n">
@@ -21197,7 +21197,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>MAP1LC3B</t>
+          <t>Peroxisome biogenesis</t>
         </is>
       </c>
       <c r="B945" t="n">
@@ -21219,7 +21219,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>SQSTM1</t>
+          <t>Inflammatory cytokines (TNF-α</t>
         </is>
       </c>
       <c r="B946" t="n">
@@ -21241,7 +21241,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>ATG4B</t>
+          <t>MHC class I</t>
         </is>
       </c>
       <c r="B947" t="n">
@@ -21263,7 +21263,7 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>STX17</t>
+          <t>5a-Reductase Type 1</t>
         </is>
       </c>
       <c r="B948" t="n">
@@ -21285,7 +21285,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>CLEC16A</t>
+          <t>SDF-1/CXCR4 signaling axis</t>
         </is>
       </c>
       <c r="B949" t="n">
@@ -21307,7 +21307,7 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>BCL2L11/BIM</t>
+          <t>PI3K/Akt pathway</t>
         </is>
       </c>
       <c r="B950" t="n">
@@ -21329,7 +21329,7 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>JAK pathway</t>
+          <t>Dopamine D2 receptor</t>
         </is>
       </c>
       <c r="B951" t="n">
@@ -21351,7 +21351,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Short-chain fatty acids (SCFA) production</t>
+          <t>BECN1</t>
         </is>
       </c>
       <c r="B952" t="n">
@@ -21373,7 +21373,7 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Intestinal microecology</t>
+          <t>MAP1LC3B</t>
         </is>
       </c>
       <c r="B953" t="n">
@@ -21395,7 +21395,7 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>Laminin-511</t>
+          <t>SQSTM1</t>
         </is>
       </c>
       <c r="B954" t="n">
@@ -21417,7 +21417,7 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>α6β4 integrin</t>
+          <t>ATG4B</t>
         </is>
       </c>
       <c r="B955" t="n">
@@ -21439,7 +21439,7 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>α3 integrin</t>
+          <t>STX17</t>
         </is>
       </c>
       <c r="B956" t="n">
@@ -21461,7 +21461,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>Melanocortin-5 Receptor (MC5R)</t>
+          <t>CLEC16A</t>
         </is>
       </c>
       <c r="B957" t="n">
@@ -21483,7 +21483,7 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>Zdhhc13</t>
+          <t>BCL2L11/BIM</t>
         </is>
       </c>
       <c r="B958" t="n">
@@ -21505,7 +21505,7 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>Palmitoyl acyltransferase (PAT)</t>
+          <t>JAK pathway</t>
         </is>
       </c>
       <c r="B959" t="n">
@@ -21527,7 +21527,7 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>Protein palmitoylation</t>
+          <t>Short-chain fatty acids (SCFA) production</t>
         </is>
       </c>
       <c r="B960" t="n">
@@ -21549,7 +21549,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>Wnt3</t>
+          <t>Intestinal microecology</t>
         </is>
       </c>
       <c r="B961" t="n">
@@ -21571,7 +21571,7 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>Wnt10a</t>
+          <t>Laminin-511</t>
         </is>
       </c>
       <c r="B962" t="n">
@@ -21593,7 +21593,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>Cerberus 1 (Cer1)</t>
+          <t>α6β4 integrin</t>
         </is>
       </c>
       <c r="B963" t="n">
@@ -21615,7 +21615,7 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>Axin1</t>
+          <t>α3 integrin</t>
         </is>
       </c>
       <c r="B964" t="n">
@@ -21637,7 +21637,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>CYP21A2</t>
+          <t>Melanocortin-5 Receptor (MC5R)</t>
         </is>
       </c>
       <c r="B965" t="n">
@@ -21659,7 +21659,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>ACTH</t>
+          <t>Zdhhc13</t>
         </is>
       </c>
       <c r="B966" t="n">
@@ -21681,7 +21681,7 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>Prostaglandin F (PGF) receptors</t>
+          <t>Palmitoyl acyltransferase (PAT)</t>
         </is>
       </c>
       <c r="B967" t="n">
@@ -21703,7 +21703,7 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>IL-23</t>
+          <t>Protein palmitoylation</t>
         </is>
       </c>
       <c r="B968" t="n">
@@ -21725,7 +21725,7 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>VCAM-1</t>
+          <t>Wnt3</t>
         </is>
       </c>
       <c r="B969" t="n">
@@ -21747,7 +21747,7 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>Wnt3a</t>
+          <t>Wnt10a</t>
         </is>
       </c>
       <c r="B970" t="n">
@@ -21769,7 +21769,7 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>Inflammatory genes</t>
+          <t>Cerberus 1 (Cer1)</t>
         </is>
       </c>
       <c r="B971" t="n">
@@ -21791,7 +21791,7 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>Angiogenesis pathway</t>
+          <t>Axin1</t>
         </is>
       </c>
       <c r="B972" t="n">
@@ -21813,7 +21813,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>HSP70 (HSPA1A/B)</t>
+          <t>CYP21A2</t>
         </is>
       </c>
       <c r="B973" t="n">
@@ -21835,7 +21835,7 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>Alcohol dehydrogenase 4 (Adh4)</t>
+          <t>ACTH</t>
         </is>
       </c>
       <c r="B974" t="n">
@@ -21857,7 +21857,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>Epithelial retinol dehydrogenase (DHRS9)</t>
+          <t>Prostaglandin F (PGF) receptors</t>
         </is>
       </c>
       <c r="B975" t="n">
@@ -21879,7 +21879,7 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>Retinol metabolism</t>
+          <t>IL-23</t>
         </is>
       </c>
       <c r="B976" t="n">
@@ -21901,7 +21901,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>TGR5 (G-protein-coupled bile acid receptor)</t>
+          <t>VCAM-1</t>
         </is>
       </c>
       <c r="B977" t="n">
@@ -21923,7 +21923,7 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>Short-chain fatty acids production</t>
+          <t>Wnt3a</t>
         </is>
       </c>
       <c r="B978" t="n">
@@ -21945,7 +21945,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>Intestinal barrier function</t>
+          <t>Inflammatory genes</t>
         </is>
       </c>
       <c r="B979" t="n">
@@ -21967,7 +21967,7 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>Skin lipidome</t>
+          <t>Angiogenesis pathway</t>
         </is>
       </c>
       <c r="B980" t="n">
@@ -21989,7 +21989,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>Skin microbiota</t>
+          <t>HSP70 (HSPA1A/B)</t>
         </is>
       </c>
       <c r="B981" t="n">
@@ -22011,7 +22011,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>Fatty acyl CoA reductase 2 (FAR2)</t>
+          <t>Alcohol dehydrogenase 4 (Adh4)</t>
         </is>
       </c>
       <c r="B982" t="n">
@@ -22033,7 +22033,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>Sebaceous gland lipid metabolism</t>
+          <t>Epithelial retinol dehydrogenase (DHRS9)</t>
         </is>
       </c>
       <c r="B983" t="n">
@@ -22055,7 +22055,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>Wax ester biosynthesis</t>
+          <t>Retinol metabolism</t>
         </is>
       </c>
       <c r="B984" t="n">
@@ -22077,7 +22077,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>Sebaceous gland activity</t>
+          <t>TGR5 (G-protein-coupled bile acid receptor)</t>
         </is>
       </c>
       <c r="B985" t="n">
@@ -22099,7 +22099,7 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>Fatty acid synthesis (TOFA target)</t>
+          <t>Short-chain fatty acids production</t>
         </is>
       </c>
       <c r="B986" t="n">
@@ -22121,7 +22121,7 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>Hypothalamic-Pituitary Axis</t>
+          <t>Intestinal barrier function</t>
         </is>
       </c>
       <c r="B987" t="n">
@@ -22143,7 +22143,7 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>RIPK1 (Receptor-interacting serine/threonine kinase 1)</t>
+          <t>Skin lipidome</t>
         </is>
       </c>
       <c r="B988" t="n">
@@ -22165,7 +22165,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>Gasdermin D (GSDMD)</t>
+          <t>Skin microbiota</t>
         </is>
       </c>
       <c r="B989" t="n">
@@ -22187,7 +22187,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Interleukin-1 beta (IL-1β)</t>
+          <t>Fatty acyl CoA reductase 2 (FAR2)</t>
         </is>
       </c>
       <c r="B990" t="n">
@@ -22209,7 +22209,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>IL-1 receptor signaling</t>
+          <t>Sebaceous gland lipid metabolism</t>
         </is>
       </c>
       <c r="B991" t="n">
@@ -22231,7 +22231,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>Androgen steroids</t>
+          <t>Wax ester biosynthesis</t>
         </is>
       </c>
       <c r="B992" t="n">
@@ -22253,7 +22253,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>FGFR2</t>
+          <t>Sebaceous gland activity</t>
         </is>
       </c>
       <c r="B993" t="n">
@@ -22275,7 +22275,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>Artemis</t>
+          <t>Fatty acid synthesis (TOFA target)</t>
         </is>
       </c>
       <c r="B994" t="n">
@@ -22297,7 +22297,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>Hair follicle bulge area</t>
+          <t>Hypothalamic-Pituitary Axis</t>
         </is>
       </c>
       <c r="B995" t="n">
@@ -22319,7 +22319,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>Growth factor receptors</t>
+          <t>RIPK1 (Receptor-interacting serine/threonine kinase 1)</t>
         </is>
       </c>
       <c r="B996" t="n">
@@ -22341,7 +22341,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Lipoxygenase</t>
+          <t>Gasdermin D (GSDMD)</t>
         </is>
       </c>
       <c r="B997" t="n">
@@ -22363,7 +22363,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>Progesterone Receptor</t>
+          <t>Interleukin-1 beta (IL-1β)</t>
         </is>
       </c>
       <c r="B998" t="n">
@@ -22385,7 +22385,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>Androgenetic alopecia</t>
+          <t>IL-1 receptor signaling</t>
         </is>
       </c>
       <c r="B999" t="n">
@@ -22407,7 +22407,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>StAR</t>
+          <t>Androgen steroids</t>
         </is>
       </c>
       <c r="B1000" t="n">
@@ -22429,7 +22429,7 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>CYP11A1</t>
+          <t>FGFR2</t>
         </is>
       </c>
       <c r="B1001" t="n">
@@ -22451,7 +22451,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>3β-HSD</t>
+          <t>Artemis</t>
         </is>
       </c>
       <c r="B1002" t="n">
@@ -22473,7 +22473,7 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>17β-HSD3</t>
+          <t>Hair follicle bulge area</t>
         </is>
       </c>
       <c r="B1003" t="n">
@@ -22495,7 +22495,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>Sex hormone binding globulin</t>
+          <t>Growth factor receptors</t>
         </is>
       </c>
       <c r="B1004" t="n">
@@ -22517,7 +22517,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Progesterone receptor</t>
+          <t>Lipoxygenase</t>
         </is>
       </c>
       <c r="B1005" t="n">
@@ -22539,146 +22539,146 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>Natural antisense transcripts of SIRT</t>
+          <t>Progesterone Receptor</t>
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1006" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="D1006" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1006" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F1006" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>SIRT (Sirtuin)</t>
+          <t>Androgenetic alopecia</t>
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1007" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="D1007" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1007" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F1007" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>Epidermal Growth Factor Receptor (EGFR)</t>
+          <t>StAR</t>
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1008" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1008" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1008" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F1008" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>DNA methyltransferase (DNMT)</t>
+          <t>CYP11A1</t>
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1009" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1009" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1009" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F1009" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Parathyroid Hormone Receptor (PTH1R)</t>
+          <t>3β-HSD</t>
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1010" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1010" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1010" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F1010" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>Cereblon (CRBN)</t>
+          <t>17β-HSD3</t>
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1011" t="n">
-        <v>1.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="D1011" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1011" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F1011" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>Dermal blood vessels</t>
+          <t>Sex hormone binding globulin</t>
         </is>
       </c>
       <c r="B1012" t="n">
         <v>1</v>
       </c>
       <c r="C1012" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1012" t="n">
         <v>1</v>
@@ -22687,20 +22687,20 @@
         <v>0.5</v>
       </c>
       <c r="F1012" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>Alpha-adrenergic receptors</t>
+          <t>Progesterone receptor</t>
         </is>
       </c>
       <c r="B1013" t="n">
         <v>1</v>
       </c>
       <c r="C1013" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1013" t="n">
         <v>1</v>
@@ -22709,145 +22709,145 @@
         <v>0.5</v>
       </c>
       <c r="F1013" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>Testosterone synthesis</t>
+          <t>Natural antisense transcripts of SIRT</t>
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1014" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="D1014" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1014" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F1014" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>HSP90</t>
+          <t>SIRT (Sirtuin)</t>
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1015" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="D1015" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1015" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F1015" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>Chondroitin-4-sulfate (C4S) proteoglycan</t>
+          <t>Epidermal Growth Factor Receptor (EGFR)</t>
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1016" t="n">
         <v>2</v>
       </c>
       <c r="D1016" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1016" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1016" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>SHBG (Sex Hormone Binding Globulin)</t>
+          <t>DNA methyltransferase (DNMT)</t>
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1017" t="n">
         <v>2</v>
       </c>
       <c r="D1017" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1017" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1017" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>Nitric oxide (NO) synthesis</t>
+          <t>Parathyroid Hormone Receptor (PTH1R)</t>
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1018" t="n">
         <v>2</v>
       </c>
       <c r="D1018" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1018" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1018" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>Lipid peroxidation</t>
+          <t>Cereblon (CRBN)</t>
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1019" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D1019" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1019" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F1019" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>Constitutive Androstane Receptor (CAR)</t>
+          <t>Dermal blood vessels</t>
         </is>
       </c>
       <c r="B1020" t="n">
@@ -22869,7 +22869,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>Peroxisome Proliferator-Activated Receptor Gamma (PPARγ)</t>
+          <t>Alpha-adrenergic receptors</t>
         </is>
       </c>
       <c r="B1021" t="n">
@@ -22891,7 +22891,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>Pregnane X Receptor (PXR)</t>
+          <t>Testosterone synthesis</t>
         </is>
       </c>
       <c r="B1022" t="n">
@@ -22913,7 +22913,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette (ABC) Transporters</t>
+          <t>HSP90</t>
         </is>
       </c>
       <c r="B1023" t="n">
@@ -22935,7 +22935,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>FKBP (FK506 Binding Protein)</t>
+          <t>Chondroitin-4-sulfate (C4S) proteoglycan</t>
         </is>
       </c>
       <c r="B1024" t="n">
@@ -22957,7 +22957,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>FKBP-12</t>
+          <t>SHBG (Sex Hormone Binding Globulin)</t>
         </is>
       </c>
       <c r="B1025" t="n">
@@ -22979,7 +22979,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>Peptidyl-prolyl isomerase (Rotamase)</t>
+          <t>Nitric oxide (NO) synthesis</t>
         </is>
       </c>
       <c r="B1026" t="n">
@@ -23001,7 +23001,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>B7.1</t>
+          <t>Lipid peroxidation</t>
         </is>
       </c>
       <c r="B1027" t="n">
@@ -23023,7 +23023,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>B7.2</t>
+          <t>Constitutive Androstane Receptor (CAR)</t>
         </is>
       </c>
       <c r="B1028" t="n">
@@ -23045,7 +23045,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>CTLA-4</t>
+          <t>Peroxisome Proliferator-Activated Receptor Gamma (PPARγ)</t>
         </is>
       </c>
       <c r="B1029" t="n">
@@ -23067,7 +23067,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>Antigen-presenting cells</t>
+          <t>Pregnane X Receptor (PXR)</t>
         </is>
       </c>
       <c r="B1030" t="n">
@@ -23089,7 +23089,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>Iron chelation</t>
+          <t>ATP-Binding Cassette (ABC) Transporters</t>
         </is>
       </c>
       <c r="B1031" t="n">
@@ -23111,7 +23111,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>ROS (Reactive Oxygen Species)</t>
+          <t>FKBP (FK506 Binding Protein)</t>
         </is>
       </c>
       <c r="B1032" t="n">
@@ -23133,7 +23133,7 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>TSH receptor</t>
+          <t>FKBP-12</t>
         </is>
       </c>
       <c r="B1033" t="n">
@@ -23155,7 +23155,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>FSH receptor</t>
+          <t>Peptidyl-prolyl isomerase (Rotamase)</t>
         </is>
       </c>
       <c r="B1034" t="n">
@@ -23177,7 +23177,7 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>LH receptor</t>
+          <t>B7.1</t>
         </is>
       </c>
       <c r="B1035" t="n">
@@ -23199,7 +23199,7 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>CG receptor</t>
+          <t>B7.2</t>
         </is>
       </c>
       <c r="B1036" t="n">
@@ -23221,7 +23221,7 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>Glycoprotein hormone receptors</t>
+          <t>CTLA-4</t>
         </is>
       </c>
       <c r="B1037" t="n">
@@ -23243,7 +23243,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>Myeloid-Derived Suppressor Cells</t>
+          <t>Antigen-presenting cells</t>
         </is>
       </c>
       <c r="B1038" t="n">
@@ -23265,7 +23265,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>Regulatory T cells</t>
+          <t>Iron chelation</t>
         </is>
       </c>
       <c r="B1039" t="n">
@@ -23287,7 +23287,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>TH17 cells</t>
+          <t>ROS (Reactive Oxygen Species)</t>
         </is>
       </c>
       <c r="B1040" t="n">
@@ -23309,20 +23309,20 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>SALL4</t>
+          <t>TSH receptor</t>
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1041" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D1041" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1041" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F1041" t="n">
         <v>1</v>
@@ -23331,7 +23331,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>Ikaros (IKZF1)</t>
+          <t>FSH receptor</t>
         </is>
       </c>
       <c r="B1042" t="n">
@@ -23353,7 +23353,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>Aiolos (IKZF3)</t>
+          <t>LH receptor</t>
         </is>
       </c>
       <c r="B1043" t="n">
@@ -23375,7 +23375,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>BRD4 (Bromodomain-containing protein 4)</t>
+          <t>CG receptor</t>
         </is>
       </c>
       <c r="B1044" t="n">
@@ -23397,7 +23397,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>VEGFR (Vascular Endothelial Growth Factor Receptor)</t>
+          <t>Glycoprotein hormone receptors</t>
         </is>
       </c>
       <c r="B1045" t="n">
@@ -23419,7 +23419,7 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>CD80</t>
+          <t>Myeloid-Derived Suppressor Cells</t>
         </is>
       </c>
       <c r="B1046" t="n">
@@ -23441,7 +23441,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>CD86</t>
+          <t>Regulatory T cells</t>
         </is>
       </c>
       <c r="B1047" t="n">
@@ -23463,7 +23463,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>ULBP1</t>
+          <t>TH17 cells</t>
         </is>
       </c>
       <c r="B1048" t="n">
@@ -23485,20 +23485,20 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>T cell receptors</t>
+          <t>SALL4</t>
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1049" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D1049" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1049" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F1049" t="n">
         <v>1</v>
@@ -23507,7 +23507,7 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>Effector T cells</t>
+          <t>Ikaros (IKZF1)</t>
         </is>
       </c>
       <c r="B1050" t="n">
@@ -23529,7 +23529,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>IL-2</t>
+          <t>Aiolos (IKZF3)</t>
         </is>
       </c>
       <c r="B1051" t="n">
@@ -23551,7 +23551,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>Nuclear Receptor</t>
+          <t>BRD4 (Bromodomain-containing protein 4)</t>
         </is>
       </c>
       <c r="B1052" t="n">
@@ -23573,7 +23573,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>PTCH1</t>
+          <t>VEGFR (Vascular Endothelial Growth Factor Receptor)</t>
         </is>
       </c>
       <c r="B1053" t="n">
@@ -23595,7 +23595,7 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>Sonic hedgehog signaling</t>
+          <t>CD80</t>
         </is>
       </c>
       <c r="B1054" t="n">
@@ -23617,7 +23617,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>Collagen binding</t>
+          <t>CD86</t>
         </is>
       </c>
       <c r="B1055" t="n">
@@ -23639,7 +23639,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>Tal1 (T-cell acute lymphocytic leukemia 1)</t>
+          <t>ULBP1</t>
         </is>
       </c>
       <c r="B1056" t="n">
@@ -23661,7 +23661,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>IKZF2 (Helios)</t>
+          <t>T cell receptors</t>
         </is>
       </c>
       <c r="B1057" t="n">
@@ -23683,7 +23683,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>CRBN (Cereblon)</t>
+          <t>Effector T cells</t>
         </is>
       </c>
       <c r="B1058" t="n">
@@ -23705,7 +23705,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>IKZF1 (Ikaros)</t>
+          <t>IL-2</t>
         </is>
       </c>
       <c r="B1059" t="n">
@@ -23727,7 +23727,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>GSPT1</t>
+          <t>Nuclear Receptor</t>
         </is>
       </c>
       <c r="B1060" t="n">
@@ -23749,7 +23749,7 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>Steroid Receptors</t>
+          <t>PTCH1</t>
         </is>
       </c>
       <c r="B1061" t="n">
@@ -23771,7 +23771,7 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>SIRT (Sirtuins)</t>
+          <t>Sonic hedgehog signaling</t>
         </is>
       </c>
       <c r="B1062" t="n">
@@ -23793,7 +23793,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>SIRT7</t>
+          <t>Collagen binding</t>
         </is>
       </c>
       <c r="B1063" t="n">
@@ -23815,7 +23815,7 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>SIRT4 (Sirtuin 4)</t>
+          <t>Tal1 (T-cell acute lymphocytic leukemia 1)</t>
         </is>
       </c>
       <c r="B1064" t="n">
@@ -23837,7 +23837,7 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>SIRT3 (Sirtuin 3)</t>
+          <t>IKZF2 (Helios)</t>
         </is>
       </c>
       <c r="B1065" t="n">
@@ -23859,7 +23859,7 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>Natural antisense polynucleotides of SIRT</t>
+          <t>CRBN (Cereblon)</t>
         </is>
       </c>
       <c r="B1066" t="n">
@@ -23881,7 +23881,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>CCHCR1 (Coiled-coil alpha-helical rod protein 1)</t>
+          <t>IKZF1 (Ikaros)</t>
         </is>
       </c>
       <c r="B1067" t="n">
@@ -23903,7 +23903,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>Parathyroid hormone receptor</t>
+          <t>GSPT1</t>
         </is>
       </c>
       <c r="B1068" t="n">
@@ -23925,7 +23925,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>Collagen</t>
+          <t>Steroid Receptors</t>
         </is>
       </c>
       <c r="B1069" t="n">
@@ -23947,7 +23947,7 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>PTH/PTHrP receptor</t>
+          <t>SIRT (Sirtuins)</t>
         </is>
       </c>
       <c r="B1070" t="n">
@@ -23969,7 +23969,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>Hairless Gene (HR)</t>
+          <t>SIRT7</t>
         </is>
       </c>
       <c r="B1071" t="n">
@@ -23991,7 +23991,7 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>Osteoblasts</t>
+          <t>SIRT4 (Sirtuin 4)</t>
         </is>
       </c>
       <c r="B1072" t="n">
@@ -24013,7 +24013,7 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>Androgen pathway</t>
+          <t>SIRT3 (Sirtuin 3)</t>
         </is>
       </c>
       <c r="B1073" t="n">
@@ -24035,7 +24035,7 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>Hyperandrogenism</t>
+          <t>Natural antisense polynucleotides of SIRT</t>
         </is>
       </c>
       <c r="B1074" t="n">
@@ -24057,36 +24057,36 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>CD19</t>
+          <t>CCHCR1 (Coiled-coil alpha-helical rod protein 1)</t>
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1075" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1075" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1075" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F1075" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>IL-18</t>
+          <t>Parathyroid hormone receptor</t>
         </is>
       </c>
       <c r="B1076" t="n">
         <v>1</v>
       </c>
       <c r="C1076" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1076" t="n">
         <v>1</v>
@@ -24095,20 +24095,20 @@
         <v>0.5</v>
       </c>
       <c r="F1076" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>PI3K (Phosphoinositide 3-kinase)</t>
+          <t>Collagen</t>
         </is>
       </c>
       <c r="B1077" t="n">
         <v>1</v>
       </c>
       <c r="C1077" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1077" t="n">
         <v>1</v>
@@ -24117,20 +24117,20 @@
         <v>0.5</v>
       </c>
       <c r="F1077" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>CD25</t>
+          <t>PTH/PTHrP receptor</t>
         </is>
       </c>
       <c r="B1078" t="n">
         <v>1</v>
       </c>
       <c r="C1078" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1078" t="n">
         <v>1</v>
@@ -24139,20 +24139,20 @@
         <v>0.5</v>
       </c>
       <c r="F1078" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>BCL-2</t>
+          <t>Hairless Gene (HR)</t>
         </is>
       </c>
       <c r="B1079" t="n">
         <v>1</v>
       </c>
       <c r="C1079" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1079" t="n">
         <v>1</v>
@@ -24161,17 +24161,17 @@
         <v>0.5</v>
       </c>
       <c r="F1079" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>EGFR (Epidermal Growth Factor Receptor)</t>
+          <t>Osteoblasts</t>
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1080" t="n">
         <v>2</v>
@@ -24180,23 +24180,23 @@
         <v>1</v>
       </c>
       <c r="E1080" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F1080" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>IKZF2</t>
+          <t>Androgen pathway</t>
         </is>
       </c>
       <c r="B1081" t="n">
         <v>1</v>
       </c>
       <c r="C1081" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1081" t="n">
         <v>1</v>
@@ -24205,20 +24205,20 @@
         <v>0.5</v>
       </c>
       <c r="F1081" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>CK1α</t>
+          <t>Hyperandrogenism</t>
         </is>
       </c>
       <c r="B1082" t="n">
         <v>1</v>
       </c>
       <c r="C1082" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1082" t="n">
         <v>1</v>
@@ -24227,35 +24227,35 @@
         <v>0.5</v>
       </c>
       <c r="F1082" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>FAM83F</t>
+          <t>CD19</t>
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1083" t="n">
         <v>1</v>
       </c>
       <c r="D1083" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1083" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F1083" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>DTWD1</t>
+          <t>IL-18</t>
         </is>
       </c>
       <c r="B1084" t="n">
@@ -24277,7 +24277,7 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>ZFP91</t>
+          <t>PI3K (Phosphoinositide 3-kinase)</t>
         </is>
       </c>
       <c r="B1085" t="n">
@@ -24299,7 +24299,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>ZFP62</t>
+          <t>CD25</t>
         </is>
       </c>
       <c r="B1086" t="n">
@@ -24321,7 +24321,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>ZFP36L2</t>
+          <t>BCL-2</t>
         </is>
       </c>
       <c r="B1087" t="n">
@@ -24343,20 +24343,20 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>RNF166</t>
+          <t>EGFR (Epidermal Growth Factor Receptor)</t>
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1088" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1088" t="n">
         <v>1</v>
       </c>
       <c r="E1088" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F1088" t="n">
         <v>0.5</v>
@@ -24365,7 +24365,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>IKZF1</t>
+          <t>IKZF2</t>
         </is>
       </c>
       <c r="B1089" t="n">
@@ -24387,7 +24387,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>IKZF3</t>
+          <t>CK1α</t>
         </is>
       </c>
       <c r="B1090" t="n">
@@ -24409,7 +24409,7 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>IKZF4</t>
+          <t>FAM83F</t>
         </is>
       </c>
       <c r="B1091" t="n">
@@ -24431,7 +24431,7 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>IKZF5</t>
+          <t>DTWD1</t>
         </is>
       </c>
       <c r="B1092" t="n">
@@ -24453,7 +24453,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>RAB28</t>
+          <t>ZFP91</t>
         </is>
       </c>
       <c r="B1093" t="n">
@@ -24475,7 +24475,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>GSTP1</t>
+          <t>ZFP62</t>
         </is>
       </c>
       <c r="B1094" t="n">
@@ -24497,7 +24497,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>GSPT2</t>
+          <t>ZFP36L2</t>
         </is>
       </c>
       <c r="B1095" t="n">
@@ -24519,7 +24519,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>TIMM10</t>
+          <t>RNF166</t>
         </is>
       </c>
       <c r="B1096" t="n">
@@ -24541,7 +24541,7 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>GZF1</t>
+          <t>IKZF1</t>
         </is>
       </c>
       <c r="B1097" t="n">
@@ -24563,7 +24563,7 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>EGR1</t>
+          <t>IKZF3</t>
         </is>
       </c>
       <c r="B1098" t="n">
@@ -24585,7 +24585,7 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>HIC1</t>
+          <t>IKZF4</t>
         </is>
       </c>
       <c r="B1099" t="n">
@@ -24607,7 +24607,7 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>HIC2</t>
+          <t>IKZF5</t>
         </is>
       </c>
       <c r="B1100" t="n">
@@ -24629,7 +24629,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>INSM2</t>
+          <t>RAB28</t>
         </is>
       </c>
       <c r="B1101" t="n">
@@ -24651,7 +24651,7 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>OSR2</t>
+          <t>GSTP1</t>
         </is>
       </c>
       <c r="B1102" t="n">
@@ -24673,7 +24673,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>GSPT2</t>
         </is>
       </c>
       <c r="B1103" t="n">
@@ -24695,7 +24695,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>PRD15</t>
+          <t>TIMM10</t>
         </is>
       </c>
       <c r="B1104" t="n">
@@ -24717,7 +24717,7 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>SALL1</t>
+          <t>GZF1</t>
         </is>
       </c>
       <c r="B1105" t="n">
@@ -24739,7 +24739,7 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>SALL3</t>
+          <t>EGR1</t>
         </is>
       </c>
       <c r="B1106" t="n">
@@ -24761,7 +24761,7 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>WIZ</t>
+          <t>HIC1</t>
         </is>
       </c>
       <c r="B1107" t="n">
@@ -24783,7 +24783,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>ZBT17</t>
+          <t>HIC2</t>
         </is>
       </c>
       <c r="B1108" t="n">
@@ -24805,7 +24805,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>ZBT41</t>
+          <t>INSM2</t>
         </is>
       </c>
       <c r="B1109" t="n">
@@ -24827,7 +24827,7 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>ZBT49</t>
+          <t>OSR2</t>
         </is>
       </c>
       <c r="B1110" t="n">
@@ -24849,7 +24849,7 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>ZBT7A</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="B1111" t="n">
@@ -24871,7 +24871,7 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>ZBT7B</t>
+          <t>PRD15</t>
         </is>
       </c>
       <c r="B1112" t="n">
@@ -24893,7 +24893,7 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>ZBTB2</t>
+          <t>SALL1</t>
         </is>
       </c>
       <c r="B1113" t="n">
@@ -24915,7 +24915,7 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>ZBTB39</t>
+          <t>SALL3</t>
         </is>
       </c>
       <c r="B1114" t="n">
@@ -24937,7 +24937,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>ZIK1</t>
+          <t>WIZ</t>
         </is>
       </c>
       <c r="B1115" t="n">
@@ -24959,7 +24959,7 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>ZNF3</t>
+          <t>ZBT17</t>
         </is>
       </c>
       <c r="B1116" t="n">
@@ -24981,7 +24981,7 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>ZNF217</t>
+          <t>ZBT41</t>
         </is>
       </c>
       <c r="B1117" t="n">
@@ -25003,7 +25003,7 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>ZNF276</t>
+          <t>ZBT49</t>
         </is>
       </c>
       <c r="B1118" t="n">
@@ -25025,7 +25025,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>ZNF316</t>
+          <t>ZBT7A</t>
         </is>
       </c>
       <c r="B1119" t="n">
@@ -25047,7 +25047,7 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>ZNF324B</t>
+          <t>ZBT7B</t>
         </is>
       </c>
       <c r="B1120" t="n">
@@ -25069,7 +25069,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>ZNF335</t>
+          <t>ZBTB2</t>
         </is>
       </c>
       <c r="B1121" t="n">
@@ -25091,7 +25091,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>ZNF397</t>
+          <t>ZBTB39</t>
         </is>
       </c>
       <c r="B1122" t="n">
@@ -25113,7 +25113,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>ZNF407</t>
+          <t>ZIK1</t>
         </is>
       </c>
       <c r="B1123" t="n">
@@ -25135,7 +25135,7 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>ZNF408</t>
+          <t>ZNF3</t>
         </is>
       </c>
       <c r="B1124" t="n">
@@ -25157,7 +25157,7 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>ZNF462</t>
+          <t>ZNF217</t>
         </is>
       </c>
       <c r="B1125" t="n">
@@ -25179,7 +25179,7 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>ZNF483</t>
+          <t>ZNF276</t>
         </is>
       </c>
       <c r="B1126" t="n">
@@ -25201,7 +25201,7 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>SNF517</t>
+          <t>ZNF316</t>
         </is>
       </c>
       <c r="B1127" t="n">
@@ -25223,7 +25223,7 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>ZNF526</t>
+          <t>ZNF324B</t>
         </is>
       </c>
       <c r="B1128" t="n">
@@ -25245,7 +25245,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>ZNF581</t>
+          <t>ZNF335</t>
         </is>
       </c>
       <c r="B1129" t="n">
@@ -25267,7 +25267,7 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>ZNF587</t>
+          <t>ZNF397</t>
         </is>
       </c>
       <c r="B1130" t="n">
@@ -25289,7 +25289,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>ZNF589</t>
+          <t>ZNF407</t>
         </is>
       </c>
       <c r="B1131" t="n">
@@ -25311,7 +25311,7 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>ZNF618</t>
+          <t>ZNF408</t>
         </is>
       </c>
       <c r="B1132" t="n">
@@ -25333,7 +25333,7 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>ZNF644</t>
+          <t>ZNF462</t>
         </is>
       </c>
       <c r="B1133" t="n">
@@ -25355,7 +25355,7 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>ZNF646</t>
+          <t>ZNF483</t>
         </is>
       </c>
       <c r="B1134" t="n">
@@ -25377,7 +25377,7 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>ZNF653</t>
+          <t>SNF517</t>
         </is>
       </c>
       <c r="B1135" t="n">
@@ -25399,7 +25399,7 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>ZNF654</t>
+          <t>ZNF526</t>
         </is>
       </c>
       <c r="B1136" t="n">
@@ -25421,7 +25421,7 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>ZNF692</t>
+          <t>ZNF581</t>
         </is>
       </c>
       <c r="B1137" t="n">
@@ -25443,7 +25443,7 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>ZNF724</t>
+          <t>ZNF587</t>
         </is>
       </c>
       <c r="B1138" t="n">
@@ -25465,7 +25465,7 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>ZNF771</t>
+          <t>ZNF589</t>
         </is>
       </c>
       <c r="B1139" t="n">
@@ -25487,7 +25487,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>ZNF782</t>
+          <t>ZNF618</t>
         </is>
       </c>
       <c r="B1140" t="n">
@@ -25509,7 +25509,7 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>ZNF784</t>
+          <t>ZNF644</t>
         </is>
       </c>
       <c r="B1141" t="n">
@@ -25531,7 +25531,7 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>ZNF814</t>
+          <t>ZNF646</t>
         </is>
       </c>
       <c r="B1142" t="n">
@@ -25553,7 +25553,7 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>ZSC10</t>
+          <t>ZNF653</t>
         </is>
       </c>
       <c r="B1143" t="n">
@@ -25575,7 +25575,7 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>ZSC22</t>
+          <t>ZNF654</t>
         </is>
       </c>
       <c r="B1144" t="n">
@@ -25597,7 +25597,7 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>ZC827</t>
+          <t>ZNF692</t>
         </is>
       </c>
       <c r="B1145" t="n">
@@ -25619,7 +25619,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>ZUFSP</t>
+          <t>ZNF724</t>
         </is>
       </c>
       <c r="B1146" t="n">
@@ -25641,7 +25641,7 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>DNMT1</t>
+          <t>ZNF771</t>
         </is>
       </c>
       <c r="B1147" t="n">
@@ -25663,7 +25663,7 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>SIRT5 (Sirtuin 5)</t>
+          <t>ZNF782</t>
         </is>
       </c>
       <c r="B1148" t="n">
@@ -25685,7 +25685,7 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>VISTA (V-domain Ig suppressor of T cell activation)</t>
+          <t>ZNF784</t>
         </is>
       </c>
       <c r="B1149" t="n">
@@ -25707,7 +25707,7 @@
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>PD-L3</t>
+          <t>ZNF814</t>
         </is>
       </c>
       <c r="B1150" t="n">
@@ -25729,22 +25729,198 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
+          <t>ZSC10</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>ZSC22</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>ZC827</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>ZUFSP</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>DNMT1</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>SIRT5 (Sirtuin 5)</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>VISTA (V-domain Ig suppressor of T cell activation)</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>PD-L3</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
           <t>T cell activation pathway</t>
         </is>
       </c>
-      <c r="B1151" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1151" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1151" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F1151" t="n">
+      <c r="B1159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1159" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/AGA_Dark_Targets.xlsx
+++ b/output/AGA_Dark_Targets.xlsx
@@ -2849,29 +2849,29 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dermal papilla cell proliferation</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E111" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>3.022222222222222</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Growth factors in platelets</t>
+          <t>Dermal papilla cell proliferation</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2893,7 +2893,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IL2RA</t>
+          <t>Growth factors in platelets</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2915,20 +2915,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hair follicle miniaturization</t>
+          <t>IL2RA</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="F114" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PPAR-γ</t>
+          <t>Hair follicle miniaturization</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2959,7 +2959,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JAM-A (Junctional Adhesion Molecule A)</t>
+          <t>PPAR-γ</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2981,7 +2981,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Autophagy pathway</t>
+          <t>JAM-A (Junctional Adhesion Molecule A)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3003,7 +3003,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 (SRD5A2)</t>
+          <t>Autophagy pathway</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3025,7 +3025,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IL-7</t>
+          <t>5α-Reductase Type 2 (SRD5A2)</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3047,7 +3047,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IL-6 (Interleukin-6)</t>
+          <t>IL-7</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3069,20 +3069,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Bax (Bcl-2-associated X protein)</t>
+          <t>IL-6 (Interleukin-6)</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F121" t="n">
         <v>3</v>
@@ -3091,7 +3091,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hair growth promotion</t>
+          <t>Bax (Bcl-2-associated X protein)</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3113,20 +3113,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TGF-beta signaling</t>
+          <t>Hair growth promotion</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="F123" t="n">
         <v>3</v>
@@ -3135,20 +3135,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Hair follicle</t>
+          <t>TGF-beta signaling</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C124" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F124" t="n">
         <v>3</v>
@@ -3157,20 +3157,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STAT3</t>
+          <t>Hair follicle</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="F125" t="n">
         <v>3</v>
@@ -3179,20 +3179,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sebaceous gland</t>
+          <t>STAT3</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E126" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F126" t="n">
         <v>3</v>
@@ -3201,7 +3201,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Hair follicle regeneration</t>
+          <t>Sebaceous gland</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3223,7 +3223,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Caspase-1</t>
+          <t>Hair follicle regeneration</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3245,7 +3245,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hair dermal papilla cells</t>
+          <t>Caspase-1</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3267,20 +3267,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IL-4</t>
+          <t>Hair dermal papilla cells</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="F130" t="n">
         <v>3</v>
@@ -3289,7 +3289,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type II</t>
+          <t>IL-4</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3311,7 +3311,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Testosterone signaling</t>
+          <t>5-Alpha Reductase Type II</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3333,20 +3333,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5-alpha reductase Type 2</t>
+          <t>Testosterone signaling</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F133" t="n">
         <v>3</v>
@@ -3355,20 +3355,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KGF</t>
+          <t>5-alpha reductase Type 2</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="F134" t="n">
         <v>3</v>
@@ -3377,7 +3377,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EGFR</t>
+          <t>KGF</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3399,7 +3399,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dermal fibroblasts</t>
+          <t>EGFR</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3421,7 +3421,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Adipose-derived stem cells</t>
+          <t>Dermal fibroblasts</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3443,20 +3443,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Inflammatory pathways</t>
+          <t>Adipose-derived stem cells</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F138" t="n">
         <v>3</v>
@@ -3465,20 +3465,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Androgen signaling pathway</t>
+          <t>Inflammatory pathways</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C139" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="F139" t="n">
         <v>3</v>
@@ -3487,7 +3487,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NF-κB signaling pathway</t>
+          <t>Androgen signaling pathway</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3509,7 +3509,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AMPK</t>
+          <t>NF-κB signaling pathway</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3531,7 +3531,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JAK1/2</t>
+          <t>AMPK</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3553,7 +3553,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Oxidative stress/ROS</t>
+          <t>JAK1/2</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3575,7 +3575,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5-Alpha-Reductase Type 2</t>
+          <t>Oxidative stress/ROS</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3597,20 +3597,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Androgen metabolism</t>
+          <t>5-Alpha-Reductase Type 2</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C145" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F145" t="n">
         <v>3</v>
@@ -3619,20 +3619,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PDGF</t>
+          <t>Androgen metabolism</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C146" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="F146" t="n">
         <v>3</v>
@@ -3641,7 +3641,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Cellular senescence</t>
+          <t>PDGF</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3663,7 +3663,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ERK</t>
+          <t>Cellular senescence</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3685,20 +3685,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Apoptosis pathway</t>
+          <t>ERK</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F149" t="n">
         <v>3</v>
@@ -3707,20 +3707,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TGF-β</t>
+          <t>Apoptosis pathway</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C150" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="F150" t="n">
         <v>3</v>
@@ -3729,7 +3729,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SFRP2</t>
+          <t>TGF-β</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3751,7 +3751,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Transdermal delivery</t>
+          <t>SFRP2</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3773,45 +3773,45 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5-alpha reductase Type II</t>
+          <t>Transdermal delivery</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F153" t="n">
-        <v>2.933333333333334</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>5-alpha reductase Type II</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C154" t="n">
-        <v>3.625</v>
+        <v>4.4</v>
       </c>
       <c r="D154" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F154" t="n">
-        <v>2.819444444444444</v>
+        <v>2.933333333333334</v>
       </c>
     </row>
     <row r="155">
